--- a/운동프로그램_8일주기_v19.xlsx
+++ b/운동프로그램_8일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_AD191220E1AB09E8313BB3B3DC196F42CA207056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_AD191220E1AB09E8313BB3B3DC196F42CA207056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDA99C23-B7BB-451B-86B7-1EB9C7BFDDF3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1726,9 +1726,6 @@
     <t>가장 작은 근육군 — 절대값이 작아 2.25kg은 과함</t>
   </si>
   <si>
-    <t>날짜</t>
-  </si>
-  <si>
     <t>스쿼트 목표</t>
   </si>
   <si>
@@ -2351,6 +2348,10 @@
   </si>
   <si>
     <t>· 쌓는 시기와 지키는 시기는 다르게 설계해야 한다.</t>
+  </si>
+  <si>
+    <t>날짜 (1일차)</t>
+    <phoneticPr fontId="34" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2731,7 +2732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2968,6 +2969,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4847,7 +4851,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="52">
-        <f t="shared" ref="F39:F70" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
+        <f t="shared" ref="F39:F61" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
         <v>0</v>
       </c>
       <c r="G39" s="56" t="s">
@@ -6376,31 +6380,31 @@
         <v>98</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>563</v>
-      </c>
       <c r="J9" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>16</v>
@@ -6491,7 +6495,9 @@
       <c r="A13" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="4"/>
+      <c r="B13" s="96">
+        <v>46262</v>
+      </c>
       <c r="C13" s="16">
         <f t="shared" si="0"/>
         <v>52.5</v>
@@ -6732,17 +6738,17 @@
     </row>
     <row r="23" spans="1:11" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="120" customHeight="1">
@@ -6750,27 +6756,27 @@
     </row>
     <row r="27" spans="1:11" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -6791,23 +6797,23 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="71" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>575</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -6815,21 +6821,21 @@
         <v>507</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="C5" s="58" t="s">
         <v>577</v>
-      </c>
-      <c r="C5" s="58" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="C6" s="58" t="s">
         <v>579</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="C6" s="58" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -6837,80 +6843,80 @@
         <v>235</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="C7" s="58" t="s">
         <v>581</v>
-      </c>
-      <c r="C7" s="58" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="72" t="s">
+        <v>582</v>
+      </c>
+      <c r="B8" s="72" t="s">
         <v>583</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="C8" s="73" t="s">
         <v>584</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="72" t="s">
+        <v>585</v>
+      </c>
+      <c r="B9" s="72" t="s">
+        <v>583</v>
+      </c>
+      <c r="C9" s="73" t="s">
         <v>586</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>584</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="74" t="s">
         <v>589</v>
-      </c>
-      <c r="C10" s="74" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="58" t="s">
         <v>592</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>594</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="58" t="s">
         <v>595</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -6918,47 +6924,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -6982,48 +6988,48 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="75" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>614</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>615</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="76" t="s">
+        <v>616</v>
+      </c>
+      <c r="B6" s="77" t="s">
         <v>617</v>
       </c>
-      <c r="B6" s="77" t="s">
-        <v>618</v>
-      </c>
       <c r="C6" s="77" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D6" s="76" t="s">
         <v>134</v>
@@ -7032,39 +7038,39 @@
         <v>0</v>
       </c>
       <c r="F6" s="78" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D7" s="72" t="s">
         <v>620</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>621</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_화_상체밀기!$E$11</f>
         <v>22</v>
       </c>
       <c r="F7" s="74" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="76" t="s">
+        <v>622</v>
+      </c>
+      <c r="B8" s="77" t="s">
         <v>623</v>
       </c>
-      <c r="B8" s="77" t="s">
-        <v>624</v>
-      </c>
       <c r="C8" s="77" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D8" s="76" t="s">
         <v>134</v>
@@ -7073,18 +7079,18 @@
         <v>0</v>
       </c>
       <c r="F8" s="78" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="76" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B9" s="77" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C9" s="77" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D9" s="76" t="s">
         <v>134</v>
@@ -7093,18 +7099,18 @@
         <v>0</v>
       </c>
       <c r="F9" s="78" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="A10" s="76" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B10" s="77" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C10" s="77" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D10" s="76" t="s">
         <v>134</v>
@@ -7113,39 +7119,39 @@
         <v>0</v>
       </c>
       <c r="F10" s="78" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>630</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>631</v>
-      </c>
       <c r="C11" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D11" s="72" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E11" s="7">
         <f>복귀_토_하체!$E$12</f>
         <v>22</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>634</v>
-      </c>
       <c r="C12" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D12" s="72" t="s">
         <v>507</v>
@@ -7155,7 +7161,7 @@
         <v>22</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
@@ -7173,27 +7179,27 @@
     </row>
     <row r="15" spans="1:6" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
@@ -7201,32 +7207,32 @@
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
@@ -7234,37 +7240,37 @@
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="79" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -7291,12 +7297,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
@@ -7346,10 +7352,10 @@
         <v>20</v>
       </c>
       <c r="G5" s="73" t="s">
+        <v>655</v>
+      </c>
+      <c r="H5" s="73" t="s">
         <v>656</v>
-      </c>
-      <c r="H5" s="73" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7363,7 +7369,7 @@
         <v>249</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E6" s="7">
         <v>3</v>
@@ -7372,10 +7378,10 @@
         <v>25</v>
       </c>
       <c r="G6" s="58" t="s">
+        <v>658</v>
+      </c>
+      <c r="H6" s="58" t="s">
         <v>659</v>
-      </c>
-      <c r="H6" s="58" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
@@ -7389,7 +7395,7 @@
         <v>258</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E7" s="7">
         <v>3</v>
@@ -7398,10 +7404,10 @@
         <v>208</v>
       </c>
       <c r="G7" s="58" t="s">
+        <v>661</v>
+      </c>
+      <c r="H7" s="58" t="s">
         <v>662</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
@@ -7424,10 +7430,10 @@
         <v>25</v>
       </c>
       <c r="G8" s="58" t="s">
+        <v>663</v>
+      </c>
+      <c r="H8" s="58" t="s">
         <v>664</v>
-      </c>
-      <c r="H8" s="58" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
@@ -7450,10 +7456,10 @@
         <v>42</v>
       </c>
       <c r="G9" s="58" t="s">
+        <v>665</v>
+      </c>
+      <c r="H9" s="58" t="s">
         <v>666</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
@@ -7476,10 +7482,10 @@
         <v>42</v>
       </c>
       <c r="G10" s="58" t="s">
+        <v>667</v>
+      </c>
+      <c r="H10" s="58" t="s">
         <v>668</v>
-      </c>
-      <c r="H10" s="58" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7493,22 +7499,22 @@
     </row>
     <row r="13" spans="1:8" ht="32.25" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="278.25" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="237.75" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
   </sheetData>
@@ -7535,12 +7541,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
@@ -7590,10 +7596,10 @@
         <v>5</v>
       </c>
       <c r="G5" s="73" t="s">
+        <v>675</v>
+      </c>
+      <c r="H5" s="73" t="s">
         <v>676</v>
-      </c>
-      <c r="H5" s="73" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29.25" customHeight="1">
@@ -7616,10 +7622,10 @@
         <v>25</v>
       </c>
       <c r="G6" s="73" t="s">
+        <v>677</v>
+      </c>
+      <c r="H6" s="73" t="s">
         <v>678</v>
-      </c>
-      <c r="H6" s="73" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
@@ -7642,10 +7648,10 @@
         <v>37</v>
       </c>
       <c r="G7" s="58" t="s">
+        <v>679</v>
+      </c>
+      <c r="H7" s="58" t="s">
         <v>680</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
@@ -7668,10 +7674,10 @@
         <v>37</v>
       </c>
       <c r="G8" s="58" t="s">
+        <v>681</v>
+      </c>
+      <c r="H8" s="58" t="s">
         <v>682</v>
-      </c>
-      <c r="H8" s="58" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
@@ -7694,10 +7700,10 @@
         <v>10</v>
       </c>
       <c r="G9" s="58" t="s">
+        <v>683</v>
+      </c>
+      <c r="H9" s="58" t="s">
         <v>684</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
@@ -7720,10 +7726,10 @@
         <v>42</v>
       </c>
       <c r="G10" s="58" t="s">
+        <v>685</v>
+      </c>
+      <c r="H10" s="58" t="s">
         <v>686</v>
-      </c>
-      <c r="H10" s="58" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7731,7 +7737,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>313</v>
@@ -7747,10 +7753,10 @@
         <v>5</v>
       </c>
       <c r="G11" s="58" t="s">
+        <v>688</v>
+      </c>
+      <c r="H11" s="58" t="s">
         <v>689</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7764,22 +7770,22 @@
     </row>
     <row r="14" spans="1:8" ht="76.5" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="265.5" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -7806,12 +7812,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
@@ -7861,10 +7867,10 @@
         <v>5</v>
       </c>
       <c r="G5" s="73" t="s">
+        <v>696</v>
+      </c>
+      <c r="H5" s="73" t="s">
         <v>697</v>
-      </c>
-      <c r="H5" s="73" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7887,10 +7893,10 @@
         <v>208</v>
       </c>
       <c r="G6" s="58" t="s">
+        <v>698</v>
+      </c>
+      <c r="H6" s="58" t="s">
         <v>699</v>
-      </c>
-      <c r="H6" s="58" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
@@ -7913,10 +7919,10 @@
         <v>25</v>
       </c>
       <c r="G7" s="58" t="s">
+        <v>700</v>
+      </c>
+      <c r="H7" s="58" t="s">
         <v>701</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
@@ -7939,10 +7945,10 @@
         <v>200</v>
       </c>
       <c r="G8" s="58" t="s">
+        <v>702</v>
+      </c>
+      <c r="H8" s="58" t="s">
         <v>703</v>
-      </c>
-      <c r="H8" s="58" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
@@ -7965,10 +7971,10 @@
         <v>25</v>
       </c>
       <c r="G9" s="58" t="s">
+        <v>704</v>
+      </c>
+      <c r="H9" s="58" t="s">
         <v>705</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
@@ -7991,10 +7997,10 @@
         <v>42</v>
       </c>
       <c r="G10" s="58" t="s">
+        <v>706</v>
+      </c>
+      <c r="H10" s="58" t="s">
         <v>707</v>
-      </c>
-      <c r="H10" s="58" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8017,10 +8023,10 @@
         <v>25</v>
       </c>
       <c r="G11" s="58" t="s">
+        <v>708</v>
+      </c>
+      <c r="H11" s="58" t="s">
         <v>709</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8028,7 +8034,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>56</v>
@@ -8043,10 +8049,10 @@
         <v>12</v>
       </c>
       <c r="G12" s="58" t="s">
+        <v>711</v>
+      </c>
+      <c r="H12" s="58" t="s">
         <v>712</v>
-      </c>
-      <c r="H12" s="58" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
@@ -8060,22 +8066,22 @@
     </row>
     <row r="15" spans="1:8" ht="92.25" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="233.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="240" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
@@ -8083,12 +8089,12 @@
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
@@ -8096,7 +8102,7 @@
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -8118,96 +8124,96 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>724</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>725</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>726</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="74" t="s">
         <v>727</v>
-      </c>
-      <c r="D5" s="74" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="58" t="s">
         <v>731</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>734</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="58" t="s">
         <v>735</v>
-      </c>
-      <c r="D7" s="58" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>737</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>738</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="58" t="s">
         <v>739</v>
-      </c>
-      <c r="D8" s="58" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>741</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="58" t="s">
         <v>743</v>
-      </c>
-      <c r="D9" s="58" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
@@ -8215,13 +8221,13 @@
         <v>71</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>745</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="58" t="s">
         <v>746</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
@@ -8229,66 +8235,66 @@
         <v>69</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="58" t="s">
         <v>749</v>
-      </c>
-      <c r="D11" s="58" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="58" t="s">
         <v>753</v>
-      </c>
-      <c r="D12" s="58" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="84" t="s">
+        <v>754</v>
+      </c>
+      <c r="B13" s="85" t="s">
         <v>755</v>
       </c>
-      <c r="B13" s="85" t="s">
+      <c r="C13" s="85" t="s">
         <v>756</v>
       </c>
-      <c r="C13" s="85" t="s">
+      <c r="D13" s="84" t="s">
         <v>757</v>
-      </c>
-      <c r="D13" s="84" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="39" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
@@ -8296,12 +8302,12 @@
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
@@ -8309,12 +8315,12 @@
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_8일주기_v19.xlsx
+++ b/운동프로그램_8일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_AD191220E1AB09E8313BB3B3DC196F42CA207056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDA99C23-B7BB-451B-86B7-1EB9C7BFDDF3}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_AD191220E1AB09E8313BB3B3DC196F42CA207056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6C4A2A-567C-4197-B8FB-CADAF6883FC7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2958,6 +2958,9 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2969,9 +2972,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3144,6 +3144,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3888,28 +3892,28 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="94" t="s">
         <v>424</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="92" t="s">
         <v>425</v>
       </c>
-      <c r="B4" s="92"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="48" t="s">
@@ -5565,7 +5569,7 @@
       <c r="F5" s="58" t="s">
         <v>503</v>
       </c>
-      <c r="G5" s="94" t="s">
+      <c r="G5" s="95" t="s">
         <v>504</v>
       </c>
       <c r="H5" s="61">
@@ -5604,7 +5608,7 @@
       <c r="F6" s="58" t="s">
         <v>505</v>
       </c>
-      <c r="G6" s="95"/>
+      <c r="G6" s="96"/>
       <c r="J6" s="60">
         <f t="shared" ca="1" si="2"/>
         <v>14</v>
@@ -5633,7 +5637,7 @@
       <c r="F7" s="58" t="s">
         <v>506</v>
       </c>
-      <c r="G7" s="94" t="s">
+      <c r="G7" s="95" t="s">
         <v>507</v>
       </c>
       <c r="H7" s="61">
@@ -5668,7 +5672,7 @@
       <c r="F8" s="58" t="s">
         <v>508</v>
       </c>
-      <c r="G8" s="95"/>
+      <c r="G8" s="96"/>
       <c r="J8" s="60">
         <f t="shared" ca="1" si="2"/>
         <v>4.8</v>
@@ -5697,7 +5701,7 @@
       <c r="F9" s="58" t="s">
         <v>509</v>
       </c>
-      <c r="G9" s="95"/>
+      <c r="G9" s="96"/>
       <c r="J9" s="60">
         <f t="shared" ca="1" si="2"/>
         <v>3.9</v>
@@ -5726,7 +5730,7 @@
       <c r="F10" s="58" t="s">
         <v>510</v>
       </c>
-      <c r="G10" s="95"/>
+      <c r="G10" s="96"/>
       <c r="J10" s="60">
         <f t="shared" ca="1" si="2"/>
         <v>13.6</v>
@@ -5936,7 +5940,7 @@
       <c r="F17" s="58" t="s">
         <v>517</v>
       </c>
-      <c r="G17" s="94" t="s">
+      <c r="G17" s="95" t="s">
         <v>26</v>
       </c>
       <c r="H17" s="61">
@@ -5971,7 +5975,7 @@
       <c r="F18" s="58" t="s">
         <v>518</v>
       </c>
-      <c r="G18" s="95"/>
+      <c r="G18" s="96"/>
       <c r="J18" s="60">
         <f t="shared" ca="1" si="2"/>
         <v>3.9</v>
@@ -6495,8 +6499,8 @@
       <c r="A13" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="96">
-        <v>46262</v>
+      <c r="B13" s="91">
+        <v>46258</v>
       </c>
       <c r="C13" s="16">
         <f t="shared" si="0"/>

--- a/운동프로그램_8일주기_v19.xlsx
+++ b/운동프로그램_8일주기_v19.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_AD191220E1AB09E8313BB3B3DC196F42CA207056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6C4A2A-567C-4197-B8FB-CADAF6883FC7}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_AD191220E1AB09E8313BB3B3DC196F42CA207056" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65B96979-EEB9-480D-AA61-6D7A1BF1F8C0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="770">
   <si>
     <t>3일차 — 하체 A (무릎 지배)</t>
   </si>
@@ -673,9 +673,6 @@
     <t>뉴트럴 그립 랫풀다운 / 원암 랫풀다운 (좌우 독립) / 케이블 풀오버 (이두 개입 최소)</t>
   </si>
   <si>
-    <t>바벨 로우</t>
-  </si>
-  <si>
     <t>8~10</t>
   </si>
   <si>
@@ -901,9 +898,6 @@
     <t>원암 케이블 로우 (좌우 독립) / 덤벨 로우 / 머신 로우</t>
   </si>
   <si>
-    <t>시티드 케이블 로우 스캡 슈러그</t>
-  </si>
-  <si>
     <t>후면 삼각근</t>
   </si>
   <si>
@@ -2351,6 +2345,255 @@
   </si>
   <si>
     <t>날짜 (1일차)</t>
+    <phoneticPr fontId="34" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이스풀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(로프)</t>
+    </r>
+    <phoneticPr fontId="34" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바벨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(스미스)</t>
+    </r>
+    <phoneticPr fontId="34" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해머</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스트랭스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(오버그립)</t>
+    </r>
+    <phoneticPr fontId="34" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시티드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>케이블</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로우</t>
+    </r>
+    <phoneticPr fontId="34" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시티드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>케이블</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스캡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슈러그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(두번째 크기 바)</t>
+    </r>
     <phoneticPr fontId="34" type="noConversion"/>
   </si>
 </sst>
@@ -2361,7 +2604,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2634,6 +2877,11 @@
       <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -3888,12 +4136,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="94" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B2" s="93"/>
       <c r="C2" s="93"/>
@@ -3905,7 +4153,7 @@
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
       <c r="A4" s="92" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B4" s="93"/>
       <c r="C4" s="93"/>
@@ -3917,33 +4165,33 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>425</v>
+      </c>
+      <c r="C6" s="48" t="s">
         <v>426</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="D6" s="48" t="s">
         <v>427</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="E6" s="48" t="s">
         <v>428</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="F6" s="48" t="s">
         <v>429</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="G6" s="48" t="s">
         <v>430</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="H6" s="48" t="s">
         <v>431</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>432</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B7" s="49" t="s">
         <v>198</v>
@@ -3963,15 +4211,15 @@
         <v>2</v>
       </c>
       <c r="G7" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H7" s="54" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="49" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B8" s="49" t="s">
         <v>204</v>
@@ -3991,18 +4239,18 @@
         <v>1.5</v>
       </c>
       <c r="G8" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="H8" s="54" t="s">
         <v>435</v>
-      </c>
-      <c r="H8" s="54" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C9" s="49" t="s">
         <v>201</v>
@@ -4010,27 +4258,27 @@
       <c r="D9" s="50">
         <v>0.5</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>?</v>
       </c>
       <c r="F9" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H9" s="54" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C10" s="49" t="s">
         <v>201</v>
@@ -4047,21 +4295,21 @@
         <v>2</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="49" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D11" s="50">
         <v>0.5</v>
@@ -4075,21 +4323,21 @@
         <v>2.5</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H11" s="54" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="49" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D12" s="50">
         <v>0.5</v>
@@ -4103,21 +4351,21 @@
         <v>2</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D13" s="50">
         <v>0.5</v>
@@ -4131,21 +4379,21 @@
         <v>1.5</v>
       </c>
       <c r="G13" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H13" s="54" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D14" s="50">
         <v>0.5</v>
@@ -4159,21 +4407,21 @@
         <v>2</v>
       </c>
       <c r="G14" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="49" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D15" s="50">
         <v>0.33</v>
@@ -4187,21 +4435,21 @@
         <v>1.32</v>
       </c>
       <c r="G15" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H15" s="54" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D16" s="50">
         <v>0.33</v>
@@ -4215,21 +4463,21 @@
         <v>1.32</v>
       </c>
       <c r="G16" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D17" s="50">
         <v>0</v>
@@ -4243,21 +4491,21 @@
         <v>0</v>
       </c>
       <c r="G17" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H17" s="54" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="49" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D18" s="50">
         <v>0.5</v>
@@ -4271,21 +4519,21 @@
         <v>2.5</v>
       </c>
       <c r="G18" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D19" s="50">
         <v>0.5</v>
@@ -4299,21 +4547,21 @@
         <v>2</v>
       </c>
       <c r="G19" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H19" s="54" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D20" s="50">
         <v>0.5</v>
@@ -4327,49 +4575,49 @@
         <v>1.5</v>
       </c>
       <c r="G20" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="49" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D21" s="50">
         <v>0.5</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>?</v>
       </c>
       <c r="F21" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G21" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H21" s="54" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D22" s="50">
         <v>0.5</v>
@@ -4383,49 +4631,49 @@
         <v>0</v>
       </c>
       <c r="G22" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H22" s="55" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D23" s="50">
         <v>0.5</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>?</v>
       </c>
       <c r="F23" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H23" s="54" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D24" s="50">
         <v>0.5</v>
@@ -4439,21 +4687,21 @@
         <v>2</v>
       </c>
       <c r="G24" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H24" s="54" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D25" s="50">
         <v>0.5</v>
@@ -4467,18 +4715,18 @@
         <v>0</v>
       </c>
       <c r="G25" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H25" s="54" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C26" s="49" t="s">
         <v>36</v>
@@ -4495,18 +4743,18 @@
         <v>2</v>
       </c>
       <c r="G26" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H26" s="54" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C27" s="49" t="s">
         <v>36</v>
@@ -4523,18 +4771,18 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H27" s="54" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="49" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C28" s="49" t="s">
         <v>36</v>
@@ -4551,15 +4799,15 @@
         <v>1.5</v>
       </c>
       <c r="G28" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H28" s="54" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B29" s="49" t="s">
         <v>18</v>
@@ -4579,15 +4827,15 @@
         <v>2.5</v>
       </c>
       <c r="G29" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H29" s="54" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B30" s="49" t="s">
         <v>24</v>
@@ -4607,18 +4855,18 @@
         <v>0.99</v>
       </c>
       <c r="G30" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H30" s="54" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C31" s="49" t="s">
         <v>26</v>
@@ -4635,18 +4883,18 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H31" s="54" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C32" s="49" t="s">
         <v>26</v>
@@ -4663,18 +4911,18 @@
         <v>1.5</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="49" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C33" s="49" t="s">
         <v>26</v>
@@ -4691,21 +4939,21 @@
         <v>1.5</v>
       </c>
       <c r="G33" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H33" s="54" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B34" s="49" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D34" s="50">
         <v>0.2</v>
@@ -4719,21 +4967,21 @@
         <v>1</v>
       </c>
       <c r="G34" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H34" s="54" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C35" s="49" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D35" s="50">
         <v>0.2</v>
@@ -4747,21 +4995,21 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G35" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H35" s="54" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C36" s="49" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D36" s="50">
         <v>0.5</v>
@@ -4775,15 +5023,15 @@
         <v>1.5</v>
       </c>
       <c r="G36" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H36" s="55" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B37" s="49" t="s">
         <v>29</v>
@@ -4803,15 +5051,15 @@
         <v>2</v>
       </c>
       <c r="G37" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H37" s="54" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
       <c r="A38" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B38" s="49" t="s">
         <v>29</v>
@@ -4831,18 +5079,18 @@
         <v>1.32</v>
       </c>
       <c r="G38" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H38" s="54" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C39" s="49" t="s">
         <v>199</v>
@@ -4859,15 +5107,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H39" s="54" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B40" s="49" t="s">
         <v>18</v>
@@ -4887,15 +5135,15 @@
         <v>2.5</v>
       </c>
       <c r="G40" s="56" t="s">
+        <v>468</v>
+      </c>
+      <c r="H40" s="54" t="s">
         <v>470</v>
-      </c>
-      <c r="H40" s="54" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B41" s="49" t="s">
         <v>24</v>
@@ -4915,15 +5163,15 @@
         <v>0.99</v>
       </c>
       <c r="G41" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H41" s="54" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
       <c r="A42" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B42" s="49" t="s">
         <v>29</v>
@@ -4943,21 +5191,21 @@
         <v>1.32</v>
       </c>
       <c r="G42" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H42" s="54" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="49" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D43" s="50">
         <v>0.2</v>
@@ -4971,21 +5219,21 @@
         <v>1</v>
       </c>
       <c r="G43" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H43" s="54" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
       <c r="A44" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D44" s="50">
         <v>0.2</v>
@@ -4999,49 +5247,49 @@
         <v>0.8</v>
       </c>
       <c r="G44" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D45" s="50">
         <v>0.2</v>
       </c>
-      <c r="E45" s="51">
+      <c r="E45" s="51" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>?</v>
       </c>
       <c r="F45" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G45" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H45" s="54" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
       <c r="A46" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D46" s="50">
         <v>0.2</v>
@@ -5055,21 +5303,21 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G46" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H46" s="54" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C47" s="49" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D47" s="50">
         <v>0.2</v>
@@ -5083,21 +5331,21 @@
         <v>0.2</v>
       </c>
       <c r="G47" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H47" s="54" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="49" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B48" s="49" t="s">
         <v>198</v>
       </c>
       <c r="C48" s="49" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D48" s="50">
         <v>0.2</v>
@@ -5111,49 +5359,49 @@
         <v>0.8</v>
       </c>
       <c r="G48" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H48" s="54" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C49" s="49" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D49" s="50">
         <v>0.2</v>
       </c>
-      <c r="E49" s="51">
+      <c r="E49" s="51" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>?</v>
       </c>
       <c r="F49" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G49" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H49" s="54" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="49" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D50" s="50">
         <v>0.33</v>
@@ -5167,15 +5415,15 @@
         <v>1.32</v>
       </c>
       <c r="G50" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H50" s="54" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B51" s="49" t="s">
         <v>24</v>
@@ -5195,15 +5443,15 @@
         <v>0.99</v>
       </c>
       <c r="G51" s="56" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H51" s="54" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B52" s="49" t="s">
         <v>24</v>
@@ -5223,21 +5471,21 @@
         <v>0.99</v>
       </c>
       <c r="G52" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H52" s="54" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D53" s="50">
         <v>0.5</v>
@@ -5251,21 +5499,21 @@
         <v>1.5</v>
       </c>
       <c r="G53" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H53" s="54" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D54" s="50">
         <v>0.5</v>
@@ -5279,21 +5527,21 @@
         <v>1.5</v>
       </c>
       <c r="G54" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H54" s="54" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="49" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B55" s="49" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D55" s="50">
         <v>0.2</v>
@@ -5307,21 +5555,21 @@
         <v>0.8</v>
       </c>
       <c r="G55" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H55" s="54" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D56" s="50">
         <v>0.5</v>
@@ -5335,18 +5583,18 @@
         <v>1.5</v>
       </c>
       <c r="G56" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H56" s="54" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="49" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C57" s="49" t="s">
         <v>201</v>
@@ -5363,21 +5611,21 @@
         <v>1.32</v>
       </c>
       <c r="G57" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H57" s="54" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="49" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B58" s="49" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D58" s="50">
         <v>0.5</v>
@@ -5391,21 +5639,21 @@
         <v>1.5</v>
       </c>
       <c r="G58" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H58" s="54" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="49" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D59" s="50">
         <v>0.33</v>
@@ -5419,21 +5667,21 @@
         <v>0.66</v>
       </c>
       <c r="G59" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H59" s="54" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
       <c r="A60" s="49" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D60" s="50">
         <v>0.5</v>
@@ -5447,21 +5695,21 @@
         <v>1.5</v>
       </c>
       <c r="G60" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H60" s="54" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="49" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B61" s="49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D61" s="50">
         <v>0.33</v>
@@ -5475,19 +5723,19 @@
         <v>0.99</v>
       </c>
       <c r="G61" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H61" s="54" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="E62" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F62" s="57">
         <f ca="1">SUM(F7:F61)</f>
-        <v>71.429999999999993</v>
+        <v>64.33</v>
       </c>
     </row>
   </sheetData>
@@ -5515,12 +5763,12 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1">
@@ -5528,27 +5776,27 @@
         <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>500</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
       <c r="A5" s="58" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B5" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A5)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A5)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A5)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A5)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A5)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A5)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A5)</f>
@@ -5567,10 +5815,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G5" s="95" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H5" s="61">
         <f ca="1">SUM(D5:D6)</f>
@@ -5587,7 +5835,7 @@
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1">
       <c r="A6" s="58" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B6" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A6)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A6)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A6)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A6)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A6)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A6)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A6)</f>
@@ -5606,7 +5854,7 @@
         <v>충분</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G6" s="96"/>
       <c r="J6" s="60">
@@ -5635,14 +5883,14 @@
         <v>충분</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G7" s="95" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H7" s="61">
         <f ca="1">SUM(D7:D10)</f>
-        <v>43.5</v>
+        <v>40</v>
       </c>
       <c r="J7" s="60">
         <f t="shared" ca="1" si="2"/>
@@ -5651,7 +5899,7 @@
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1">
       <c r="A8" s="58" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B8" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A8)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A8)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A8)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A8)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A8)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A8)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A8)</f>
@@ -5659,28 +5907,28 @@
       </c>
       <c r="C8" s="59">
         <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$61,간접계수맵!$C$7:$C$61,$A8),0.5)</f>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D8" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="E8" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G8" s="96"/>
       <c r="J8" s="60">
         <f t="shared" ca="1" si="2"/>
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1">
       <c r="A9" s="58" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B9" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A9)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A9)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A9)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A9)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A9)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A9)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A9)</f>
@@ -5688,28 +5936,28 @@
       </c>
       <c r="C9" s="59">
         <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$61,간접계수맵!$C$7:$C$61,$A9),0.5)</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>보완 필요</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G9" s="96"/>
       <c r="J9" s="60">
         <f t="shared" ca="1" si="2"/>
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1">
       <c r="A10" s="58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B10" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A10)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A10)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A10)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A10)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A10)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A10)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A10)</f>
@@ -5717,28 +5965,28 @@
       </c>
       <c r="C10" s="59">
         <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$61,간접계수맵!$C$7:$C$61,$A10),0.5)</f>
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="D10" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="E10" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G10" s="96"/>
       <c r="J10" s="60">
         <f t="shared" ca="1" si="2"/>
-        <v>13.6</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1">
       <c r="A11" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B11" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A11)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A11)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A11)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A11)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A11)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A11)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A11)</f>
@@ -5757,7 +6005,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G11" s="62"/>
       <c r="J11" s="60">
@@ -5767,7 +6015,7 @@
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1">
       <c r="A12" s="58" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B12" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A12)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A12)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A12)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A12)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A12)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A12)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A12)</f>
@@ -5786,7 +6034,7 @@
         <v>충분</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G12" s="62"/>
       <c r="J12" s="60">
@@ -5796,7 +6044,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1">
       <c r="A13" s="58" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B13" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A13)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A13)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A13)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A13)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A13)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A13)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A13)</f>
@@ -5815,7 +6063,7 @@
         <v>충분</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G13" s="62"/>
       <c r="J13" s="60">
@@ -5825,7 +6073,7 @@
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1">
       <c r="A14" s="58" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B14" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A14)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A14)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A14)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A14)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A14)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A14)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A14)</f>
@@ -5833,24 +6081,24 @@
       </c>
       <c r="C14" s="59">
         <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$61,간접계수맵!$C$7:$C$61,$A14),0.5)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="E14" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G14" s="62"/>
       <c r="H14" s="61"/>
       <c r="J14" s="60">
         <f t="shared" ca="1" si="2"/>
-        <v>15.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1">
@@ -5877,7 +6125,7 @@
         <v>29</v>
       </c>
       <c r="G15" s="63" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H15" s="61">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -5909,7 +6157,7 @@
         <v>충분</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G16" s="62"/>
       <c r="J16" s="60">
@@ -5938,7 +6186,7 @@
         <v>충분</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G17" s="95" t="s">
         <v>26</v>
@@ -5973,7 +6221,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G18" s="96"/>
       <c r="J18" s="60">
@@ -6002,7 +6250,7 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G19" s="62"/>
       <c r="J19" s="60">
@@ -6020,28 +6268,28 @@
       </c>
       <c r="C20" s="59">
         <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$61,간접계수맵!$C$7:$C$61,$A20),0.5)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" s="60">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>충분</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G20" s="62"/>
       <c r="J20" s="60">
         <f t="shared" ca="1" si="2"/>
-        <v>17.5</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1">
       <c r="A21" s="58" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B21" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A21)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A21)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A21)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A21)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A21)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A21)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A21)</f>
@@ -6060,7 +6308,7 @@
         <v>충분</v>
       </c>
       <c r="F21" s="58" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G21" s="62"/>
       <c r="J21" s="60">
@@ -6070,7 +6318,7 @@
     </row>
     <row r="22" spans="1:10" ht="16.5" customHeight="1">
       <c r="A22" s="58" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A22)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A22)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A22)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A22)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A22)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A22)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A22)</f>
@@ -6089,7 +6337,7 @@
         <v>충분</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G22" s="62"/>
       <c r="J22" s="60">
@@ -6118,7 +6366,7 @@
         <v>하한</v>
       </c>
       <c r="F23" s="58" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G23" s="62"/>
       <c r="J23" s="60">
@@ -6147,7 +6395,7 @@
         <v>하한</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G24" s="62"/>
       <c r="J24" s="60">
@@ -6157,7 +6405,7 @@
     </row>
     <row r="25" spans="1:10" ht="36" customHeight="1">
       <c r="A25" s="65" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B5:B24)</f>
@@ -6166,33 +6414,33 @@
       <c r="C25" s="66"/>
       <c r="D25" s="67">
         <f ca="1">SUM(D5:D24)</f>
-        <v>256.5</v>
+        <v>249.5</v>
       </c>
       <c r="E25" s="66"/>
       <c r="F25" s="66"/>
       <c r="J25" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>224.4</v>
+        <v>218.3</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="16.5" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="36" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="48" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="48" customHeight="1">
@@ -6200,22 +6448,22 @@
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.5" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="48" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="48" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1">
@@ -6223,67 +6471,67 @@
     </row>
     <row r="36" spans="1:1" ht="48" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="77.25" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="48" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="39" customHeight="1">
       <c r="A39" s="68" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="45" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="48" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="48" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="48" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="48" customHeight="1">
       <c r="A44" s="11" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="51.75" customHeight="1">
       <c r="A45" s="11" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="90" customHeight="1">
       <c r="A46" s="11" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="51.75" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="48" customHeight="1">
       <c r="A48" s="11" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -6318,50 +6566,50 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="69" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="68" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="69" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="69" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -6370,13 +6618,13 @@
     </row>
     <row r="8" spans="1:11" ht="84" customHeight="1">
       <c r="A8" s="69" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
@@ -6384,31 +6632,31 @@
         <v>98</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="F9" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="H9" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>562</v>
-      </c>
       <c r="J9" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>16</v>
@@ -6742,17 +6990,17 @@
     </row>
     <row r="23" spans="1:11" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="120" customHeight="1">
@@ -6760,27 +7008,27 @@
     </row>
     <row r="27" spans="1:11" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -6801,126 +7049,126 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="71" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>573</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="72" t="s">
+        <v>580</v>
+      </c>
+      <c r="B8" s="72" t="s">
+        <v>581</v>
+      </c>
+      <c r="C8" s="73" t="s">
         <v>582</v>
-      </c>
-      <c r="B8" s="72" t="s">
-        <v>583</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="72" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B9" s="72" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C9" s="73" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="C10" s="74" t="s">
         <v>587</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="C10" s="74" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="C11" s="58" t="s">
         <v>590</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="C12" s="58" t="s">
         <v>593</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -6928,47 +7176,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -6992,48 +7240,48 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="75" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>612</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>614</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="76" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B6" s="77" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C6" s="77" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D6" s="76" t="s">
         <v>134</v>
@@ -7042,39 +7290,39 @@
         <v>0</v>
       </c>
       <c r="F6" s="78" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D7" s="72" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_화_상체밀기!$E$11</f>
         <v>22</v>
       </c>
       <c r="F7" s="74" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
       <c r="A8" s="76" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B8" s="77" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C8" s="77" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D8" s="76" t="s">
         <v>134</v>
@@ -7083,18 +7331,18 @@
         <v>0</v>
       </c>
       <c r="F8" s="78" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="76" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B9" s="77" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C9" s="77" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D9" s="76" t="s">
         <v>134</v>
@@ -7103,18 +7351,18 @@
         <v>0</v>
       </c>
       <c r="F9" s="78" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="A10" s="76" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B10" s="77" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C10" s="77" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D10" s="76" t="s">
         <v>134</v>
@@ -7123,49 +7371,49 @@
         <v>0</v>
       </c>
       <c r="F10" s="78" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D11" s="72" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E11" s="7">
         <f>복귀_토_하체!$E$12</f>
         <v>22</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D12" s="72" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E12" s="7">
         <f>복귀_일_등!$E$13</f>
         <v>22</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
@@ -7183,27 +7431,27 @@
     </row>
     <row r="15" spans="1:6" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
@@ -7211,32 +7459,32 @@
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
@@ -7244,37 +7492,37 @@
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="79" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -7301,12 +7549,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
@@ -7343,7 +7591,7 @@
         <v>73</v>
       </c>
       <c r="C5" s="72" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D5" s="80">
         <f>시작중량_설정!$E$9</f>
@@ -7356,10 +7604,10 @@
         <v>20</v>
       </c>
       <c r="G5" s="73" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H5" s="73" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7367,13 +7615,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E6" s="7">
         <v>3</v>
@@ -7382,10 +7630,10 @@
         <v>25</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
@@ -7393,25 +7641,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E7" s="7">
         <v>3</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
@@ -7419,13 +7667,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E8" s="7">
         <v>3</v>
@@ -7434,10 +7682,10 @@
         <v>25</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
@@ -7445,13 +7693,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="58" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>265</v>
-      </c>
       <c r="D9" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E9" s="7">
         <v>4</v>
@@ -7460,10 +7708,10 @@
         <v>42</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
@@ -7471,13 +7719,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
@@ -7486,10 +7734,10 @@
         <v>42</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7503,22 +7751,22 @@
     </row>
     <row r="13" spans="1:8" ht="32.25" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="278.25" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="237.75" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -7545,12 +7793,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
@@ -7600,10 +7848,10 @@
         <v>5</v>
       </c>
       <c r="G5" s="73" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="H5" s="73" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29.25" customHeight="1">
@@ -7626,10 +7874,10 @@
         <v>25</v>
       </c>
       <c r="G6" s="73" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H6" s="73" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
@@ -7637,7 +7885,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
@@ -7652,10 +7900,10 @@
         <v>37</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
@@ -7678,10 +7926,10 @@
         <v>37</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
@@ -7689,7 +7937,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>36</v>
@@ -7704,10 +7952,10 @@
         <v>10</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
@@ -7715,7 +7963,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>52</v>
@@ -7730,10 +7978,10 @@
         <v>42</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -7741,10 +7989,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D11" s="82">
         <f>시작중량_설정!$E$10</f>
@@ -7757,10 +8005,10 @@
         <v>5</v>
       </c>
       <c r="G11" s="58" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -7774,22 +8022,22 @@
     </row>
     <row r="14" spans="1:8" ht="76.5" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="265.5" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -7816,12 +8064,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
@@ -7858,7 +8106,7 @@
         <v>71</v>
       </c>
       <c r="C5" s="72" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D5" s="83">
         <f>시작중량_설정!$E$8</f>
@@ -7871,10 +8119,10 @@
         <v>5</v>
       </c>
       <c r="G5" s="73" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H5" s="73" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -7882,7 +8130,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>199</v>
@@ -7894,13 +8142,13 @@
         <v>3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
@@ -7908,7 +8156,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>199</v>
@@ -7923,10 +8171,10 @@
         <v>25</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
@@ -7949,10 +8197,10 @@
         <v>200</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
@@ -7975,10 +8223,10 @@
         <v>25</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
@@ -7986,13 +8234,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -8001,10 +8249,10 @@
         <v>42</v>
       </c>
       <c r="G10" s="58" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
@@ -8012,13 +8260,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>201</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E11" s="7">
         <v>3</v>
@@ -8027,10 +8275,10 @@
         <v>25</v>
       </c>
       <c r="G11" s="58" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
@@ -8038,7 +8286,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>56</v>
@@ -8053,10 +8301,10 @@
         <v>12</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
@@ -8070,22 +8318,22 @@
     </row>
     <row r="15" spans="1:8" ht="92.25" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="233.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="240" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
@@ -8093,12 +8341,12 @@
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
@@ -8106,7 +8354,7 @@
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -8128,96 +8376,96 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>723</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>724</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="D5" s="74" t="s">
         <v>725</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="D5" s="74" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>728</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="D6" s="58" t="s">
         <v>729</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>730</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="58" t="s">
         <v>733</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>734</v>
-      </c>
-      <c r="D7" s="58" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="58" t="s">
         <v>737</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>738</v>
-      </c>
-      <c r="D8" s="58" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="D9" s="58" t="s">
         <v>741</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="D9" s="58" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
@@ -8225,13 +8473,13 @@
         <v>71</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="D10" s="58" t="s">
         <v>744</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
@@ -8239,66 +8487,66 @@
         <v>69</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="D11" s="58" t="s">
         <v>747</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="D11" s="58" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="D12" s="58" t="s">
         <v>751</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>752</v>
-      </c>
-      <c r="D12" s="58" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="84" t="s">
+        <v>752</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>753</v>
+      </c>
+      <c r="C13" s="85" t="s">
         <v>754</v>
       </c>
-      <c r="B13" s="85" t="s">
+      <c r="D13" s="84" t="s">
         <v>755</v>
-      </c>
-      <c r="C13" s="85" t="s">
-        <v>756</v>
-      </c>
-      <c r="D13" s="84" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="39" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
@@ -8306,12 +8554,12 @@
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
@@ -8319,12 +8567,12 @@
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
   </sheetData>
@@ -8937,8 +9185,8 @@
       <c r="A8" s="20">
         <v>3</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>207</v>
+      <c r="B8" s="36" t="s">
+        <v>766</v>
       </c>
       <c r="C8" s="44" t="s">
         <v>199</v>
@@ -8950,7 +9198,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G8" s="26">
         <v>40</v>
@@ -8963,24 +9211,24 @@
         <v>8</v>
       </c>
       <c r="J8" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="K8" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="L8" s="21" t="s">
         <v>210</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.5" customHeight="1">
       <c r="A9" s="20">
         <v>4</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="36" t="s">
+        <v>765</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>212</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>213</v>
       </c>
       <c r="D9" s="20">
         <v>12.5</v>
@@ -9002,13 +9250,13 @@
         <v>5.3</v>
       </c>
       <c r="J9" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="K9" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="L9" s="21" t="s">
         <v>215</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="16.5" customHeight="1">
@@ -9016,13 +9264,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>201</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E10" s="20">
         <v>0</v>
@@ -9041,13 +9289,13 @@
         <v>0</v>
       </c>
       <c r="J10" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="K10" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="K10" s="21" t="s">
+      <c r="L10" s="22" t="s">
         <v>220</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="16.5" customHeight="1">
@@ -9055,10 +9303,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>222</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>223</v>
       </c>
       <c r="D11" s="26">
         <v>20</v>
@@ -9067,7 +9315,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G11" s="26">
         <v>40</v>
@@ -9081,10 +9329,10 @@
       </c>
       <c r="J11" s="21"/>
       <c r="K11" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="L11" s="21" t="s">
         <v>225</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1">
@@ -9092,10 +9340,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D12" s="20">
         <v>10</v>
@@ -9104,7 +9352,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G12" s="26">
         <v>40</v>
@@ -9118,10 +9366,10 @@
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="L12" s="21" t="s">
         <v>229</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1">
@@ -9129,7 +9377,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>56</v>
@@ -9155,10 +9403,10 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="L13" s="87" t="s">
         <v>232</v>
-      </c>
-      <c r="L13" s="87" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1">
@@ -9166,10 +9414,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>234</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>235</v>
       </c>
       <c r="D14" s="20">
         <v>20</v>
@@ -9178,7 +9426,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G14" s="26">
         <v>45</v>
@@ -9191,13 +9439,13 @@
         <v>6.8</v>
       </c>
       <c r="J14" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="K14" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="K14" s="36" t="s">
+      <c r="L14" s="36" t="s">
         <v>238</v>
-      </c>
-      <c r="L14" s="36" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1">
@@ -9218,7 +9466,7 @@
     </row>
     <row r="33" spans="10:10">
       <c r="J33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -9258,17 +9506,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
@@ -9349,22 +9597,22 @@
     </row>
     <row r="13" spans="1:3" ht="16.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.5" customHeight="1">
       <c r="A14" s="31" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" customHeight="1">
       <c r="A15" s="31" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.5" customHeight="1">
       <c r="A16" s="31" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1">
@@ -9415,10 +9663,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C20" s="42" t="s">
         <v>248</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>249</v>
       </c>
       <c r="D20" s="43">
         <f>시작중량_설정!$E$9</f>
@@ -9441,13 +9689,13 @@
         <v>17.5</v>
       </c>
       <c r="J20" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="K20" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="K20" s="41" t="s">
+      <c r="L20" s="41" t="s">
         <v>251</v>
-      </c>
-      <c r="L20" s="41" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1">
@@ -9455,19 +9703,19 @@
         <v>2</v>
       </c>
       <c r="B21" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="44" t="s">
         <v>253</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="D21" s="44" t="s">
-        <v>254</v>
       </c>
       <c r="E21" s="20">
         <v>4</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G21" s="26">
         <v>40</v>
@@ -9480,13 +9728,13 @@
         <v>12.7</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K21" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="L21" s="21" t="s">
         <v>255</v>
-      </c>
-      <c r="L21" s="21" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1">
@@ -9494,10 +9742,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>257</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>258</v>
       </c>
       <c r="D22" s="26">
         <v>8</v>
@@ -9520,10 +9768,10 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="L22" s="21" t="s">
         <v>259</v>
-      </c>
-      <c r="L22" s="21" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1">
@@ -9531,10 +9779,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D23" s="26">
         <v>10</v>
@@ -9557,10 +9805,10 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="L23" s="21" t="s">
         <v>262</v>
-      </c>
-      <c r="L23" s="21" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="16.5" customHeight="1">
@@ -9568,10 +9816,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>264</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>265</v>
       </c>
       <c r="D24" s="26">
         <v>6</v>
@@ -9594,10 +9842,10 @@
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="L24" s="21" t="s">
         <v>266</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="16.5" customHeight="1">
@@ -9605,10 +9853,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="C25" s="45" t="s">
         <v>268</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>269</v>
       </c>
       <c r="D25" s="26">
         <v>20</v>
@@ -9638,13 +9886,13 @@
         <v>7</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C26" s="45" t="s">
         <v>201</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E26" s="20">
         <v>3</v>
@@ -9663,13 +9911,13 @@
         <v>5.5</v>
       </c>
       <c r="J26" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K26" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="L26" s="21" t="s">
         <v>271</v>
-      </c>
-      <c r="L26" s="21" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -10196,17 +10444,17 @@
   <sheetData>
     <row r="1" spans="1:12" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
@@ -10256,8 +10504,8 @@
       <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>276</v>
+      <c r="B6" s="36" t="s">
+        <v>767</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>199</v>
@@ -10269,7 +10517,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G6" s="26">
         <v>40</v>
@@ -10282,21 +10530,21 @@
         <v>12.7</v>
       </c>
       <c r="J6" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="K6" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="L6" s="21" t="s">
         <v>278</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.5" customHeight="1">
       <c r="A7" s="20">
         <v>2</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>280</v>
+      <c r="B7" s="36" t="s">
+        <v>768</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>199</v>
@@ -10321,24 +10569,24 @@
         <v>12.7</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K7" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="L7" s="21" t="s">
         <v>281</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.5" customHeight="1">
       <c r="A8" s="20">
         <v>3</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>283</v>
+      <c r="B8" s="36" t="s">
+        <v>769</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D8" s="20">
         <v>25</v>
@@ -10360,13 +10608,13 @@
         <v>6.7</v>
       </c>
       <c r="J8" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="L8" s="21" t="s">
         <v>284</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.5" customHeight="1">
@@ -10374,10 +10622,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D9" s="26" t="s">
         <v>42</v>
@@ -10386,7 +10634,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G9" s="26">
         <v>40</v>
@@ -10399,13 +10647,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="L9" s="21" t="s">
         <v>288</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="16.5" customHeight="1">
@@ -10413,7 +10661,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>201</v>
@@ -10438,13 +10686,13 @@
         <v>7.3</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="16.5" customHeight="1">
@@ -10452,10 +10700,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D11" s="20">
         <v>15</v>
@@ -10464,7 +10712,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G11" s="26">
         <v>40</v>
@@ -10478,10 +10726,10 @@
       </c>
       <c r="J11" s="21"/>
       <c r="K11" s="21" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1">
@@ -10489,10 +10737,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D12" s="20">
         <v>15</v>
@@ -10501,7 +10749,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G12" s="26">
         <v>40</v>
@@ -10514,13 +10762,13 @@
         <v>7.3</v>
       </c>
       <c r="J12" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="L12" s="21" t="s">
         <v>298</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.5" customHeight="1">
@@ -10528,10 +10776,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D13" s="20">
         <v>15</v>
@@ -10553,13 +10801,13 @@
         <v>6.5</v>
       </c>
       <c r="J13" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="L13" s="21" t="s">
         <v>303</v>
-      </c>
-      <c r="K13" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="L13" s="21" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1">
@@ -10567,7 +10815,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="90" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>56</v>
@@ -10579,7 +10827,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G14" s="26">
         <v>40</v>
@@ -10593,10 +10841,10 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1">
@@ -10644,17 +10892,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
@@ -10735,22 +10983,22 @@
     </row>
     <row r="13" spans="1:3" ht="16.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.5" customHeight="1">
       <c r="A14" s="31" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" customHeight="1">
       <c r="A15" s="31" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.5" customHeight="1">
       <c r="A16" s="31" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1">
@@ -10801,10 +11049,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D20" s="43">
         <f>시작중량_설정!$E$10</f>
@@ -10827,13 +11075,13 @@
         <v>10.5</v>
       </c>
       <c r="J20" s="41" t="s">
+        <v>312</v>
+      </c>
+      <c r="K20" s="41" t="s">
+        <v>313</v>
+      </c>
+      <c r="L20" s="41" t="s">
         <v>314</v>
-      </c>
-      <c r="K20" s="41" t="s">
-        <v>315</v>
-      </c>
-      <c r="L20" s="41" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1">
@@ -10841,10 +11089,10 @@
         <v>2</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D21" s="20">
         <v>15</v>
@@ -10853,7 +11101,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G21" s="26">
         <v>40</v>
@@ -10866,13 +11114,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="L21" s="21" t="s">
         <v>318</v>
-      </c>
-      <c r="K21" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="L21" s="21" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1">
@@ -10880,10 +11128,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D22" s="20">
         <v>10</v>
@@ -10905,13 +11153,13 @@
         <v>5</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1">
@@ -10919,10 +11167,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D23" s="26">
         <v>15</v>
@@ -10944,13 +11192,13 @@
         <v>9.5</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="16.5" customHeight="1">
@@ -10958,10 +11206,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D24" s="26">
         <v>30</v>
@@ -10970,7 +11218,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G24" s="26">
         <v>40</v>
@@ -10983,13 +11231,13 @@
         <v>12.7</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="16.5" customHeight="1">
@@ -10997,10 +11245,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D25" s="26">
         <v>10</v>
@@ -11023,10 +11271,10 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="16.5" customHeight="1">
@@ -11034,10 +11282,10 @@
         <v>7</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D26" s="26">
         <v>5</v>
@@ -11060,10 +11308,10 @@
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
@@ -11071,13 +11319,13 @@
         <v>8</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E27" s="20">
         <v>0</v>
@@ -11096,13 +11344,13 @@
         <v>0</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1">
@@ -11110,10 +11358,10 @@
         <v>9</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D28" s="26">
         <v>15</v>
@@ -11136,10 +11384,10 @@
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="L28" s="21" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1">
@@ -11157,42 +11405,42 @@
     </row>
     <row r="31" spans="1:12" ht="16.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -11224,17 +11472,17 @@
   <sheetData>
     <row r="1" spans="1:12" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.5" customHeight="1">
@@ -11361,10 +11609,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D15" s="43">
         <f>시작중량_설정!$E$8</f>
@@ -11387,13 +11635,13 @@
         <v>3.6</v>
       </c>
       <c r="J15" s="41" t="s">
+        <v>354</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>355</v>
+      </c>
+      <c r="L15" s="41" t="s">
         <v>356</v>
-      </c>
-      <c r="K15" s="41" t="s">
-        <v>357</v>
-      </c>
-      <c r="L15" s="41" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.5" customHeight="1">
@@ -11401,7 +11649,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>26</v>
@@ -11429,10 +11677,10 @@
         <v>36</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1">
@@ -11440,7 +11688,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>36</v>
@@ -11468,10 +11716,10 @@
         <v>21</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1">
@@ -11479,7 +11727,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>36</v>
@@ -11491,7 +11739,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G18" s="26">
         <v>80</v>
@@ -11505,10 +11753,10 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="16.5" customHeight="1">
@@ -11516,7 +11764,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>19</v>
@@ -11542,10 +11790,10 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="16.5" customHeight="1">
@@ -11581,10 +11829,10 @@
         <v>26</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1">
@@ -11592,7 +11840,7 @@
         <v>7</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>52</v>
@@ -11618,10 +11866,10 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1">
@@ -11655,7 +11903,7 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L22" s="21" t="s">
         <v>50</v>
@@ -11707,17 +11955,17 @@
   <sheetData>
     <row r="1" spans="1:12" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1">
       <c r="A3" s="33" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
@@ -11768,10 +12016,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D6" s="20">
         <v>10</v>
@@ -11794,10 +12042,10 @@
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.5" customHeight="1">
@@ -11805,10 +12053,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D7" s="20">
         <v>5</v>
@@ -11831,10 +12079,10 @@
       </c>
       <c r="J7" s="21"/>
       <c r="K7" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.5" customHeight="1">
@@ -11842,10 +12090,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D8" s="20">
         <v>15</v>
@@ -11867,13 +12115,13 @@
         <v>3.8</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.5" customHeight="1">
@@ -11881,10 +12129,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>42</v>
@@ -11906,13 +12154,13 @@
         <v>5.5</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="16.5" customHeight="1">
@@ -11920,10 +12168,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D10" s="20">
         <v>5</v>
@@ -11946,10 +12194,10 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="16.5" customHeight="1">
@@ -11957,10 +12205,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D11" s="20">
         <v>20</v>
@@ -11982,13 +12230,13 @@
         <v>6</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1">
@@ -11996,7 +12244,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>201</v>
@@ -12021,13 +12269,13 @@
         <v>7.3</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.5" customHeight="1">
@@ -12046,112 +12294,112 @@
     <row r="14" spans="1:12" ht="16.5" customHeight="1"/>
     <row r="15" spans="1:12" ht="16.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.5" customHeight="1">
       <c r="A16" s="31" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="16.5" customHeight="1">
       <c r="A17" s="31" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="16.5" customHeight="1">
       <c r="A18" s="31" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="16.5" customHeight="1">
       <c r="A19" s="31" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="16.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="16.5" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="16.5" customHeight="1">
       <c r="A22" s="31" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="16.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="31" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" s="31" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" s="31" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" s="31" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="16.5" customHeight="1">
       <c r="A29" s="31" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" s="31" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="16.5" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="16.5" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="31" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_8일주기_v19.xlsx
+++ b/운동프로그램_8일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_0244F1E7E71FFD0688994FB4BAC4DFC2B67FF777" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_53439C92D81B8BFF5380EBF22EA9297E41140D36" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="1000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1001">
   <si>
     <t>근육군별 주간 세트 — 검산</t>
   </si>
@@ -139,7 +139,7 @@
     <t>삼각근(측면)</t>
   </si>
   <si>
-    <t>밀리터리 0.33(2026-09-04 0.5에서 하향, 5×5 본세트라 측면삼각이 자기 실패 근처에 못 간다). 같은 오버헤드인 머신 숄더 프레스는 측면 행이 아직 없다 — 일관성 구멍으로 남아 있다. 직접 세트가 두터워 판정에는 영향 없음.</t>
+    <t>오버헤드 프레스 두 종목 모두 0.33 — 밀리터리 본세트(2026-09-04 0.5에서 하향, 5×5라 측면삼각이 자기 실패 근처에 못 간다)와 머신 숄더 프레스(2026-09-04 신설). 머신 숄더만 행이 없었는데, 제외 사유였던 '직접 전면삼각 분류'는 밀리터리에도 똑같이 해당돼 성립하지 않았다 — 보조 종목이라 실패에 더 가까이 가는 쪽이 오히려 0이던 것을 바로잡았다. 직접 세트가 두터워 판정에는 영향 없음.</t>
   </si>
   <si>
     <t>삼각근(후면)</t>
@@ -1639,6 +1639,12 @@
     <t>오버헤드 프레스 측면삼각 관여 — 5×5 본세트라 측면삼각이 자기 실패 근처에 못 간다 (2026-09-04 0.5→0.33)</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>오버헤드 프레스 측면삼각 관여 — 밀리터리 본세트(0.33)와 같은 등급. 이전에는 이 행이 없었는데 제외 사유였던 '직접 전면삼각 분류'는 밀리터리에도 똑같이 해당돼 성립하지 않았다. 보조 종목이라 오히려 실패에 더 가깝다 (2026-09-04 신설)</t>
+  </si>
+  <si>
     <t>페이스풀 중 후면삼각 능동 수축</t>
   </si>
   <si>
@@ -1691,9 +1697,6 @@
   </si>
   <si>
     <t>관상면 안정화 부하 — 부분 관여</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
   <si>
     <t>고장력 등척성 — 바를 몸쪽에 고정(길이변화 작음)</t>
@@ -4596,7 +4599,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4630,7 +4633,7 @@
         <v>499</v>
       </c>
       <c r="F3">
-        <f ca="1">COUNTIF($E$7:$E$64,"?")</f>
+        <f ca="1">COUNTIF($E$7:$E$65,"?")</f>
         <v>0</v>
       </c>
     </row>
@@ -5066,16 +5069,16 @@
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="49" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>253</v>
+        <v>387</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D21" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E21" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5083,21 +5086,21 @@
       </c>
       <c r="F21" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="G21" s="53" t="s">
-        <v>510</v>
+        <v>0.99</v>
+      </c>
+      <c r="G21" s="56" t="s">
+        <v>528</v>
       </c>
       <c r="H21" s="54" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="49" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>406</v>
+        <v>253</v>
       </c>
       <c r="C22" s="49" t="s">
         <v>29</v>
@@ -5107,45 +5110,45 @@
       </c>
       <c r="E22" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G22" s="53" t="s">
         <v>510</v>
       </c>
-      <c r="H22" s="55" t="s">
-        <v>529</v>
+      <c r="H22" s="54" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="49" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>347</v>
+        <v>406</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D23" s="50">
         <v>0.5</v>
       </c>
       <c r="E23" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F23" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="53" t="s">
         <v>510</v>
       </c>
-      <c r="H23" s="54" t="s">
-        <v>530</v>
+      <c r="H23" s="55" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
@@ -5153,7 +5156,7 @@
         <v>513</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C24" s="49" t="s">
         <v>21</v>
@@ -5173,7 +5176,7 @@
         <v>510</v>
       </c>
       <c r="H24" s="54" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
@@ -5181,7 +5184,7 @@
         <v>513</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C25" s="49" t="s">
         <v>21</v>
@@ -5191,39 +5194,39 @@
       </c>
       <c r="E25" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F25" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="53" t="s">
         <v>510</v>
       </c>
       <c r="H25" s="54" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="49" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>430</v>
+        <v>358</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D26" s="50">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E26" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F26" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G26" s="53" t="s">
         <v>510</v>
@@ -5234,80 +5237,80 @@
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C27" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D27" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E27" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="G27" s="53" t="s">
         <v>510</v>
       </c>
       <c r="H27" s="54" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="49" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>273</v>
+        <v>424</v>
       </c>
       <c r="C28" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E28" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.33</v>
       </c>
       <c r="G28" s="53" t="s">
         <v>510</v>
       </c>
       <c r="H28" s="54" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="49" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D29" s="50">
         <v>0.5</v>
       </c>
       <c r="E29" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G29" s="53" t="s">
         <v>510</v>
@@ -5318,66 +5321,66 @@
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="49" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C30" s="49" t="s">
         <v>36</v>
       </c>
       <c r="D30" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E30" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>2.5</v>
       </c>
       <c r="G30" s="53" t="s">
         <v>510</v>
       </c>
       <c r="H30" s="54" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="49" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>424</v>
+        <v>321</v>
       </c>
       <c r="C31" s="49" t="s">
         <v>36</v>
       </c>
       <c r="D31" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E31" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.5</v>
+        <v>0.99</v>
       </c>
       <c r="G31" s="53" t="s">
         <v>510</v>
       </c>
       <c r="H31" s="54" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C32" s="49" t="s">
         <v>36</v>
@@ -5387,25 +5390,25 @@
       </c>
       <c r="E32" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G32" s="53" t="s">
         <v>510</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="49" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>273</v>
+        <v>433</v>
       </c>
       <c r="C33" s="49" t="s">
         <v>36</v>
@@ -5425,43 +5428,43 @@
         <v>510</v>
       </c>
       <c r="H33" s="54" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="49" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D34" s="50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F34" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G34" s="53" t="s">
         <v>510</v>
       </c>
       <c r="H34" s="54" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="49" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>372</v>
+        <v>316</v>
       </c>
       <c r="C35" s="49" t="s">
         <v>23</v>
@@ -5471,7 +5474,7 @@
       </c>
       <c r="E35" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F35" s="52">
         <f t="shared" ca="1" si="1"/>
@@ -5481,21 +5484,21 @@
         <v>510</v>
       </c>
       <c r="H35" s="54" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="49" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>433</v>
+        <v>372</v>
       </c>
       <c r="C36" s="49" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E36" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5503,24 +5506,24 @@
       </c>
       <c r="F36" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G36" s="53" t="s">
         <v>510</v>
       </c>
-      <c r="H36" s="55" t="s">
-        <v>543</v>
+      <c r="H36" s="54" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="49" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>32</v>
+        <v>433</v>
       </c>
       <c r="C37" s="49" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D37" s="50">
         <v>0.5</v>
@@ -5536,22 +5539,22 @@
       <c r="G37" s="53" t="s">
         <v>510</v>
       </c>
-      <c r="H37" s="54" t="s">
-        <v>544</v>
+      <c r="H37" s="55" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
       <c r="A38" s="49" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B38" s="49" t="s">
         <v>32</v>
       </c>
       <c r="C38" s="49" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D38" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E38" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5559,38 +5562,38 @@
       </c>
       <c r="F38" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G38" s="53" t="s">
         <v>510</v>
       </c>
       <c r="H38" s="54" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="49" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>424</v>
+        <v>32</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D39" s="50">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E39" s="51">
-        <f t="shared" ref="E39:E64" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
-        <v>1</v>
+        <f t="shared" ref="E39:E65" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
+        <v>3</v>
       </c>
       <c r="F39" s="52">
         <f t="shared" ref="F39:F70" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G39" s="56" t="s">
-        <v>546</v>
+        <v>0.99</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>510</v>
       </c>
       <c r="H39" s="54" t="s">
         <v>547</v>
@@ -5598,27 +5601,27 @@
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="49" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>316</v>
+        <v>424</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D40" s="50">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="E40" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F40" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6500000000000001</v>
+        <v>0</v>
       </c>
       <c r="G40" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H40" s="54" t="s">
         <v>548</v>
@@ -5626,10 +5629,10 @@
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="49" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C41" s="49" t="s">
         <v>50</v>
@@ -5639,14 +5642,14 @@
       </c>
       <c r="E41" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F41" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G41" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H41" s="54" t="s">
         <v>549</v>
@@ -5654,10 +5657,10 @@
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
       <c r="A42" s="49" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>32</v>
+        <v>321</v>
       </c>
       <c r="C42" s="49" t="s">
         <v>50</v>
@@ -5674,7 +5677,7 @@
         <v>0.99</v>
       </c>
       <c r="G42" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H42" s="54" t="s">
         <v>550</v>
@@ -5682,27 +5685,27 @@
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="49" t="s">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>289</v>
+        <v>32</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D43" s="50">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E43" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F43" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G43" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H43" s="54" t="s">
         <v>551</v>
@@ -5710,27 +5713,27 @@
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
       <c r="A44" s="49" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>397</v>
+        <v>289</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" s="50">
         <v>0</v>
       </c>
       <c r="E44" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F44" s="52">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="G44" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H44" s="54" t="s">
         <v>552</v>
@@ -5738,13 +5741,13 @@
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="49" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>347</v>
+        <v>397</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D45" s="50">
         <v>0</v>
@@ -5758,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H45" s="54" t="s">
         <v>553</v>
@@ -5766,27 +5769,27 @@
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
       <c r="A46" s="49" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="C46" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="50">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E46" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G46" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H46" s="54" t="s">
         <v>554</v>
@@ -5794,27 +5797,27 @@
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="49" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>424</v>
+        <v>382</v>
       </c>
       <c r="C47" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D47" s="50">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E47" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G47" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H47" s="54" t="s">
         <v>555</v>
@@ -5822,27 +5825,27 @@
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="49" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>238</v>
+        <v>424</v>
       </c>
       <c r="C48" s="49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D48" s="50">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F48" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G48" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H48" s="54" t="s">
         <v>556</v>
@@ -5850,10 +5853,10 @@
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="49" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>347</v>
+        <v>238</v>
       </c>
       <c r="C49" s="49" t="s">
         <v>19</v>
@@ -5870,7 +5873,7 @@
         <v>0.8</v>
       </c>
       <c r="G49" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H49" s="54" t="s">
         <v>557</v>
@@ -5878,27 +5881,27 @@
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="49" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D50" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E50" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6500000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G50" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H50" s="54" t="s">
         <v>558</v>
@@ -5906,27 +5909,27 @@
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="49" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="C51" s="49" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D51" s="50">
         <v>0.33</v>
       </c>
       <c r="E51" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F51" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G51" s="56" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="H51" s="54" t="s">
         <v>559</v>
@@ -5934,13 +5937,13 @@
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B52" s="49" t="s">
         <v>321</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D52" s="50">
         <v>0.33</v>
@@ -5954,7 +5957,7 @@
         <v>0.99</v>
       </c>
       <c r="G52" s="56" t="s">
-        <v>546</v>
+        <v>510</v>
       </c>
       <c r="H52" s="54" t="s">
         <v>560</v>
@@ -5962,16 +5965,16 @@
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="49" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>387</v>
+        <v>321</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D53" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E53" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -5979,10 +5982,10 @@
       </c>
       <c r="F53" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>0.99</v>
       </c>
       <c r="G53" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H53" s="54" t="s">
         <v>561</v>
@@ -5993,7 +5996,7 @@
         <v>518</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C54" s="49" t="s">
         <v>44</v>
@@ -6010,7 +6013,7 @@
         <v>1.5</v>
       </c>
       <c r="G54" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H54" s="54" t="s">
         <v>562</v>
@@ -6018,27 +6021,27 @@
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="49" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B55" s="49" t="s">
-        <v>294</v>
+        <v>394</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D55" s="50">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E55" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F55" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G55" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H55" s="54" t="s">
         <v>563</v>
@@ -6046,27 +6049,27 @@
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="49" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>394</v>
+        <v>294</v>
       </c>
       <c r="C56" s="49" t="s">
         <v>25</v>
       </c>
       <c r="D56" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E56" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G56" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H56" s="54" t="s">
         <v>564</v>
@@ -6074,27 +6077,27 @@
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="49" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D57" s="50">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="E57" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="G57" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H57" s="54" t="s">
         <v>565</v>
@@ -6102,27 +6105,27 @@
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="49" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="B58" s="49" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D58" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E58" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G58" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H58" s="54" t="s">
         <v>566</v>
@@ -6133,10 +6136,10 @@
         <v>521</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>461</v>
+        <v>358</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D59" s="50">
         <v>0.33</v>
@@ -6150,7 +6153,7 @@
         <v>0.99</v>
       </c>
       <c r="G59" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H59" s="54" t="s">
         <v>567</v>
@@ -6161,10 +6164,10 @@
         <v>521</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D60" s="50">
         <v>0.33</v>
@@ -6178,7 +6181,7 @@
         <v>0.99</v>
       </c>
       <c r="G60" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H60" s="54" t="s">
         <v>568</v>
@@ -6186,13 +6189,13 @@
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="49" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B61" s="49" t="s">
-        <v>258</v>
+        <v>469</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D61" s="50">
         <v>0.33</v>
@@ -6206,7 +6209,7 @@
         <v>0.99</v>
       </c>
       <c r="G61" s="56" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H61" s="54" t="s">
         <v>569</v>
@@ -6214,44 +6217,44 @@
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="49" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="B62" s="49" t="s">
-        <v>428</v>
+        <v>258</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D62" s="50">
         <v>0.33</v>
       </c>
       <c r="E62" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.66</v>
-      </c>
-      <c r="G62" s="53" t="s">
-        <v>510</v>
+        <v>0.99</v>
+      </c>
+      <c r="G62" s="56" t="s">
+        <v>528</v>
       </c>
       <c r="H62" s="54" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" ht="15" customHeight="1">
       <c r="A63" s="49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B63" s="49" t="s">
         <v>428</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D63" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E63" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -6259,7 +6262,7 @@
       </c>
       <c r="F63" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="G63" s="53" t="s">
         <v>510</v>
@@ -6270,16 +6273,16 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B64" s="49" t="s">
         <v>428</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D64" s="50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E64" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -6287,13 +6290,41 @@
       </c>
       <c r="F64" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" s="53" t="s">
-        <v>546</v>
+        <v>510</v>
       </c>
       <c r="H64" s="54" t="s">
         <v>572</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="49" t="s">
+        <v>533</v>
+      </c>
+      <c r="B65" s="49" t="s">
+        <v>428</v>
+      </c>
+      <c r="C65" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" s="50">
+        <v>0</v>
+      </c>
+      <c r="E65" s="51">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F65" s="52">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="53" t="s">
+        <v>528</v>
+      </c>
+      <c r="H65" s="54" t="s">
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -6361,7 +6392,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A5),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A5),0.5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="59">
@@ -6400,7 +6431,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A6),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A6),0.5)</f>
         <v>0</v>
       </c>
       <c r="D6" s="59">
@@ -6429,7 +6460,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A7),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A7),0.5)</f>
         <v>0</v>
       </c>
       <c r="D7" s="59">
@@ -6464,7 +6495,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A8),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A8),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D8" s="59">
@@ -6493,7 +6524,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A9),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A9),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D9" s="59">
@@ -6522,7 +6553,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A10),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A10),0.5)</f>
         <v>7.5</v>
       </c>
       <c r="D10" s="59">
@@ -6551,7 +6582,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A11),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A11),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D11" s="59">
@@ -6580,7 +6611,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A12),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A12),0.5)</f>
         <v>5.5</v>
       </c>
       <c r="D12" s="59">
@@ -6609,12 +6640,12 @@
         <v>18</v>
       </c>
       <c r="C13" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A13),0.5)</f>
-        <v>1</v>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A13),0.5)</f>
+        <v>2</v>
       </c>
       <c r="D13" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6626,7 +6657,7 @@
       <c r="G13" s="61"/>
       <c r="J13" s="59">
         <f t="shared" ca="1" si="2"/>
-        <v>16.600000000000001</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1">
@@ -6638,7 +6669,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A14),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A14),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D14" s="59">
@@ -6668,7 +6699,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A15),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A15),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D15" s="59">
@@ -6703,7 +6734,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A16),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A16),0.5)</f>
         <v>3.5</v>
       </c>
       <c r="D16" s="59">
@@ -6732,7 +6763,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A17),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A17),0.5)</f>
         <v>9</v>
       </c>
       <c r="D17" s="59">
@@ -6767,7 +6798,7 @@
         <v>7</v>
       </c>
       <c r="C18" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A18),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A18),0.5)</f>
         <v>1</v>
       </c>
       <c r="D18" s="59">
@@ -6796,7 +6827,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="58">
-        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A19),0.5)</f>
+        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A19),0.5)</f>
         <v>0</v>
       </c>
       <c r="D19" s="59">
@@ -6825,7 +6856,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A20),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A20),0.5)</f>
         <v>9</v>
       </c>
       <c r="D20" s="59">
@@ -6854,7 +6885,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A21),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A21),0.5)</f>
         <v>9.5</v>
       </c>
       <c r="D21" s="59">
@@ -6883,7 +6914,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A22),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A22),0.5)</f>
         <v>3.5</v>
       </c>
       <c r="D22" s="59">
@@ -6912,7 +6943,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="58">
-        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A23),0.5)</f>
+        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A23),0.5)</f>
         <v>0</v>
       </c>
       <c r="D23" s="59">
@@ -6941,7 +6972,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$64,간접계수맵!$C$7:$C$64,$A24),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$65,간접계수맵!$C$7:$C$65,$A24),0.5)</f>
         <v>4.5</v>
       </c>
       <c r="D24" s="59">
@@ -6972,13 +7003,13 @@
       <c r="C25" s="65"/>
       <c r="D25" s="66">
         <f ca="1">SUM(D5:D24)</f>
-        <v>255.5</v>
+        <v>256.5</v>
       </c>
       <c r="E25" s="65"/>
       <c r="F25" s="65"/>
       <c r="J25" s="66">
         <f t="shared" ca="1" si="2"/>
-        <v>223.6</v>
+        <v>224.4</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1">
@@ -7129,50 +7160,50 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="68" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="67" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="68" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="68" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -7181,13 +7212,13 @@
     </row>
     <row r="8" spans="1:11" ht="84" customHeight="1">
       <c r="A8" s="68" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="67" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
@@ -7195,31 +7226,31 @@
         <v>114</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>586</v>
-      </c>
       <c r="G9" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>234</v>
@@ -7553,17 +7584,17 @@
     </row>
     <row r="23" spans="1:11" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="120" customHeight="1">
@@ -7571,27 +7602,27 @@
     </row>
     <row r="27" spans="1:11" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -7612,23 +7643,23 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="70" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -7636,21 +7667,21 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -7658,80 +7689,80 @@
         <v>23</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="71" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="71" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C10" s="73" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -7739,47 +7770,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
   </sheetData>
@@ -7805,31 +7836,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="74" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>134</v>
@@ -7838,111 +7869,111 @@
         <v>135</v>
       </c>
       <c r="G5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="75" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E6" s="75">
         <f>복귀_평일A_가슴!$E$12</f>
         <v>28</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$15</f>
         <v>35</v>
       </c>
       <c r="F7" s="73" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="75" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E8" s="75">
         <f>복귀_토_하체!$E$14</f>
         <v>32</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G8" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="75" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E9" s="75">
         <f>복귀_일_등!$E$16</f>
         <v>33</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G9" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="75" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C10" s="76" t="s">
         <v>138</v>
@@ -7957,7 +7988,7 @@
         <v>138</v>
       </c>
       <c r="G10" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
@@ -7972,7 +8003,7 @@
         <v>128</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -7993,32 +8024,32 @@
     </row>
     <row r="15" spans="1:7" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -8026,22 +8057,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -8049,32 +8080,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="67" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -8082,47 +8113,47 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="78" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -8132,27 +8163,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -8183,12 +8214,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -8263,10 +8294,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="K5" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L5" s="72" t="s">
         <v>293</v>
@@ -8277,7 +8308,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C6" s="71" t="s">
         <v>25</v>
@@ -8303,10 +8334,10 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="K6" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L6" s="72" t="s">
         <v>386</v>
@@ -8342,10 +8373,10 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K7" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -8378,10 +8409,10 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="K8" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -8414,10 +8445,10 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="K9" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -8431,7 +8462,7 @@
         <v>50</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
@@ -8450,10 +8481,10 @@
         <v>10.7</v>
       </c>
       <c r="J10" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K10" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -8486,10 +8517,10 @@
         <v>5.8</v>
       </c>
       <c r="J11" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="K11" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -8497,13 +8528,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="80" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E12" s="28">
         <v>3</v>
@@ -8522,10 +8553,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="K12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -8558,10 +8589,10 @@
         <v>6.7</v>
       </c>
       <c r="J13" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="K13" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="76.5" customHeight="1">
@@ -8584,72 +8615,72 @@
     </row>
     <row r="16" spans="1:13" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
   </sheetData>
@@ -8680,12 +8711,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -8760,10 +8791,10 @@
         <v>3.5</v>
       </c>
       <c r="J5" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="K5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -8771,13 +8802,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
@@ -8796,13 +8827,13 @@
         <v>12.7</v>
       </c>
       <c r="J6" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="K6" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="L6" s="57" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -8810,7 +8841,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="93" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>14</v>
@@ -8835,10 +8866,10 @@
         <v>12.7</v>
       </c>
       <c r="J7" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K7" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -8871,13 +8902,13 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J8" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="K8" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="L8" s="57" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="29.25" customHeight="1">
@@ -8891,7 +8922,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -8910,10 +8941,10 @@
         <v>5.8</v>
       </c>
       <c r="J9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="K9" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -8927,7 +8958,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -8946,10 +8977,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="K10" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -8982,13 +9013,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="K11" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="L11" s="57" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -9021,10 +9052,10 @@
         <v>7.3</v>
       </c>
       <c r="J12" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="K12" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
@@ -9057,10 +9088,10 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="K13" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -9068,7 +9099,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -9093,10 +9124,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="K14" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1">
@@ -9129,10 +9160,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="K15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="23.25" customHeight="1">
@@ -9155,112 +9186,112 @@
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="67" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
   </sheetData>
@@ -9291,12 +9322,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -9370,10 +9401,10 @@
         <v>10.7</v>
       </c>
       <c r="J5" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="K5" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -9406,10 +9437,10 @@
         <v>6.7</v>
       </c>
       <c r="J6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="K6" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -9417,13 +9448,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
@@ -9442,10 +9473,10 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="K7" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -9478,10 +9509,10 @@
         <v>6.7</v>
       </c>
       <c r="J8" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -9495,7 +9526,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -9514,10 +9545,10 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="K9" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9550,10 +9581,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="K10" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -9567,7 +9598,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="80" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -9586,10 +9617,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="K11" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -9622,10 +9653,10 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K12" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
@@ -9658,10 +9689,10 @@
         <v>10.7</v>
       </c>
       <c r="J13" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K13" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
@@ -9694,10 +9725,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="K14" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="25.5" customHeight="1">
@@ -9716,72 +9747,72 @@
     </row>
     <row r="16" spans="1:13" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -9812,12 +9843,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -9892,10 +9923,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="K5" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="L5" s="72" t="s">
         <v>293</v>
@@ -9912,7 +9943,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E6" s="7">
         <v>5</v>
@@ -9931,10 +9962,10 @@
         <v>15.8</v>
       </c>
       <c r="J6" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K6" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -9942,7 +9973,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>9</v>
@@ -9967,10 +9998,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J7" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="K7" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10003,10 +10034,10 @@
         <v>12.7</v>
       </c>
       <c r="J8" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="K8" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -10014,7 +10045,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="93" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>14</v>
@@ -10039,10 +10070,10 @@
         <v>10.7</v>
       </c>
       <c r="J9" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="K9" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10075,10 +10106,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K10" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10092,7 +10123,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="80" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -10111,10 +10142,10 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="K11" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -10146,27 +10177,27 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="C27" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -10188,166 +10219,166 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D5" s="73" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>138</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="83" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B13" s="84" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C13" s="84" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D13" s="83" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B14" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C14" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D14" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -10358,22 +10389,22 @@
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
@@ -10381,137 +10412,137 @@
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
       <c r="A23" s="67" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -11078,12 +11109,12 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -11097,12 +11128,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B6" t="s">
         <v>502</v>
@@ -11128,7 +11159,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B7" t="s">
         <v>347</v>
@@ -11148,18 +11179,18 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H7" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B8" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
@@ -11176,7 +11207,7 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H8" t="s">
         <v>512</v>
@@ -11184,10 +11215,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B9" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -11204,7 +11235,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H9" t="s">
         <v>514</v>
@@ -11212,10 +11243,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B10" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
@@ -11232,7 +11263,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H10" t="s">
         <v>514</v>
@@ -11240,7 +11271,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B11" t="s">
         <v>238</v>
@@ -11260,7 +11291,7 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H11" t="s">
         <v>512</v>
@@ -11268,7 +11299,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B12" t="s">
         <v>89</v>
@@ -11288,15 +11319,15 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H12" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B13" t="s">
         <v>397</v>
@@ -11316,15 +11347,15 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H13" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B15" t="s">
         <v>387</v>
@@ -11344,18 +11375,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H15" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B16" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -11372,15 +11403,15 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H16" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B17" t="s">
         <v>294</v>
@@ -11400,15 +11431,15 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H17" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B18" t="s">
         <v>89</v>
@@ -11428,15 +11459,15 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H18" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B19" t="s">
         <v>397</v>
@@ -11456,15 +11487,15 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H19" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B20" t="s">
         <v>294</v>
@@ -11484,18 +11515,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G20" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H20" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B21" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -11512,15 +11543,15 @@
         <v>1.5</v>
       </c>
       <c r="G21" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H21" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B22" t="s">
         <v>347</v>
@@ -11540,18 +11571,18 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H22" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B23" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C23" t="s">
         <v>21</v>
@@ -11568,18 +11599,18 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H23" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B24" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
@@ -11596,15 +11627,15 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H24" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B25" t="s">
         <v>358</v>
@@ -11624,15 +11655,15 @@
         <v>1.5</v>
       </c>
       <c r="G25" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H25" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B26" t="s">
         <v>400</v>
@@ -11652,18 +11683,18 @@
         <v>1.32</v>
       </c>
       <c r="G26" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H26" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B27" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
@@ -11680,18 +11711,18 @@
         <v>0.99</v>
       </c>
       <c r="G27" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H27" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B28" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -11708,18 +11739,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H28" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B29" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
@@ -11736,15 +11767,15 @@
         <v>0.8</v>
       </c>
       <c r="G29" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H29" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B30" t="s">
         <v>87</v>
@@ -11764,15 +11795,15 @@
         <v>0.2</v>
       </c>
       <c r="G30" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H30" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B31" t="s">
         <v>238</v>
@@ -11792,18 +11823,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G31" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H31" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B32" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
@@ -11820,15 +11851,15 @@
         <v>0.8</v>
       </c>
       <c r="G32" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H32" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B33" t="s">
         <v>85</v>
@@ -11848,18 +11879,18 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H33" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B34" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C34" t="s">
         <v>23</v>
@@ -11876,15 +11907,15 @@
         <v>0.8</v>
       </c>
       <c r="G34" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H34" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B35" t="s">
         <v>391</v>
@@ -11904,15 +11935,15 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G35" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H35" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B36" t="s">
         <v>85</v>
@@ -11932,15 +11963,15 @@
         <v>2.5</v>
       </c>
       <c r="G36" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H36" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B37" t="s">
         <v>87</v>
@@ -11960,15 +11991,15 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H37" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B38" t="s">
         <v>321</v>
@@ -11988,15 +12019,15 @@
         <v>1.32</v>
       </c>
       <c r="G38" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H38" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B39" t="s">
         <v>430</v>
@@ -12016,15 +12047,15 @@
         <v>1.5</v>
       </c>
       <c r="G39" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H39" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B40" t="s">
         <v>87</v>
@@ -12044,15 +12075,15 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H40" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B41" t="s">
         <v>85</v>
@@ -12072,15 +12103,15 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H41" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B42" t="s">
         <v>321</v>
@@ -12100,15 +12131,15 @@
         <v>0.8</v>
       </c>
       <c r="G42" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H42" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B43" t="s">
         <v>472</v>
@@ -12128,7 +12159,7 @@
         <v>0.99</v>
       </c>
       <c r="G43" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H43" t="s">
         <v>522</v>
@@ -12136,7 +12167,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B44" t="s">
         <v>362</v>
@@ -12156,7 +12187,7 @@
         <v>0.99</v>
       </c>
       <c r="G44" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H44" t="s">
         <v>522</v>
@@ -12164,7 +12195,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B45" t="s">
         <v>89</v>
@@ -12184,15 +12215,15 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H45" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B46" t="s">
         <v>397</v>
@@ -12212,15 +12243,15 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H46" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B47" t="s">
         <v>87</v>
@@ -12240,15 +12271,15 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H47" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B48" t="s">
         <v>85</v>
@@ -12268,15 +12299,15 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H48" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B49" t="s">
         <v>445</v>
@@ -12296,18 +12327,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H49" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B50" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -12324,18 +12355,18 @@
         <v>0.8</v>
       </c>
       <c r="G50" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H50" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B51" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C51" t="s">
         <v>25</v>
@@ -12352,10 +12383,10 @@
         <v>0.8</v>
       </c>
       <c r="G51" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="H51" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
   </sheetData>
@@ -12381,12 +12412,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -12409,7 +12440,7 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -12433,10 +12464,10 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="G5" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -12467,10 +12498,10 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
+        <v>966</v>
+      </c>
+      <c r="G6" t="s">
         <v>965</v>
-      </c>
-      <c r="G6" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -12494,13 +12525,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="G7" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H7" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -12528,10 +12559,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G8" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -12555,10 +12586,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G9" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -12582,10 +12613,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
+        <v>973</v>
+      </c>
+      <c r="G10" t="s">
         <v>972</v>
-      </c>
-      <c r="G10" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -12609,10 +12640,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G11" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -12636,10 +12667,10 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G12" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -12663,10 +12694,10 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G13" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -12690,10 +12721,10 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G14" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -12717,13 +12748,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G15" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H15" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -12751,10 +12782,10 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G16" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -12778,10 +12809,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G17" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -12805,10 +12836,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="G18" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -12832,10 +12863,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G19" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -12859,10 +12890,10 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G20" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -12886,10 +12917,10 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="G21" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -12913,10 +12944,10 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G22" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -12940,10 +12971,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="G23" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -12967,10 +12998,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G24" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -12993,62 +13024,62 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_8일주기_v19.xlsx
+++ b/운동프로그램_8일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A828C9CFB0A4A9ADCC26E7390CA5DAC974D7B2FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_A24B24B3FC0402CFCC26E73951A515A1BBC1D131" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="1021">
   <si>
     <t>근육군별 주간 세트 — 검산</t>
   </si>
@@ -133,7 +133,7 @@
     <t>삼각근(전면)</t>
   </si>
   <si>
-    <t>인클라인 머신 0.5(전면삼각 편향 큼) · 벤치 0.33 · 헤머 체스트 0.33 · 딥스 0.2. 2026-09-04에 수평 프레스를 0.5→0.33으로 내렸다. 주당 환산이 10 경계에 붙어 있어 계수 선택에 판정이 흔들린다 — 표보다 몸으로 판단할 자리. [2026-09-04 9일 주기 전환으로 주당 10.1 → 9.7이 되어 '하한'으로 표시된다. 쫓지 않기로 한 항목이다 — 2026-08-28에 확인했듯 RP 랜드마크 표에 전면 삼각근 행 자체가 없다(프레스로 자동 충족). 지금도 프레스 6종목이 간접 6.5를 얹고 있다. 이 줄의 '하한'은 무시한다.]</t>
+    <t>인클라인 머신 0.5(전면삼각 편향 큼) · 벤치 0.33 · 헤머 체스트 0.33 · 딥스 0.2. 2026-09-04에 수평 프레스를 0.5→0.33으로 내렸다. [2026-09-04 8일차 머신 숄더 프레스 3세트 신설 — 직접 6→9] 처음에는 2026-08-28 판단(RP 표에 전면 삼각근 행이 없다 · 프레스로 자동 충족)을 근거로 안 넣었는데, 같은 날 벤치·헤머 체스트의 전면삼각 계수를 0.5→0.33으로 내려놓고 그렇게 줄어든 간접을 근거로 직접을 생략한 것이라 앞뒤가 안 맞았다. 나머지 여섯 부위에는 안 쓴 잣대를 여기만 쓴 셈이기도 하다.</t>
   </si>
   <si>
     <t>삼각근(측면)</t>
@@ -1492,6 +1492,15 @@
     <t>와이드 그립 시티드 케이블 로우 (팔꿈치 벌려) / 페이스풀 (외회전까지 포함) / 머신 로우 와이드 그립</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 전면삼각 직접이 6세트(6일차 밀리터리 3 + 머신 숄더 3)뿐이라 측면 18 · 후면 17에 견주면 얇았다. 9일 주기 전환으로 주당 9.7까지 내려와 이 자리를 만들었다. 레터럴·리어 6종목 뒤에 두는 이유: 앞에 두면 프레스 피로로 레이즈 중량이 눌린다. 여기 목적은 근력이 아니라 볼륨이므로 중량이 6일차보다 낮아도 된다.</t>
+  </si>
+  <si>
+    <t>덤벨 숄더 프레스 / 스미스 오버헤드 프레스</t>
+  </si>
+  <si>
     <t>[2026-09-04 신설] 승모 하부 세 번째 자리. 6일차에서 0세트로 꺼져 있던 종목을 그쪽에서 켜고 여기에도 뒀다. 견갑 하강 + 상방회전. 엎드려 팔을 Y자로 — 중량보다 견갑이 먼저 움직이는지가 중요하다.</t>
   </si>
   <si>
@@ -1693,6 +1702,9 @@
     <t>오버헤드 프레스 측면삼각 관여 — 밀리터리 본세트(0.33)와 같은 등급. 이전에는 이 행이 없었는데 제외 사유였던 '직접 전면삼각 분류'는 밀리터리에도 똑같이 해당돼 성립하지 않았다. 보조 종목이라 오히려 실패에 더 가깝다 (2026-09-04 신설)</t>
   </si>
   <si>
+    <t>오버헤드 프레스 측면삼각 관여 — 6일차 같은 종목(0.33)과 동일 등급 (2026-09-04 신설)</t>
+  </si>
+  <si>
     <t>페이스풀 중 후면삼각 능동 수축</t>
   </si>
   <si>
@@ -1795,6 +1807,9 @@
     <t>오버헤드 프레스 삼두 신전 — 기존 프레스 삼두 엣지(0.5)와 일관</t>
   </si>
   <si>
+    <t>오버헤드 프레스 삼두 신전 — 6일차 같은 종목(0.5)과 동일 등급 (2026-09-04 신설)</t>
+  </si>
+  <si>
     <t>체스트 프레스 삼두 신전 — 기존 프레스 삼두 엣지(0.5)와 일관</t>
   </si>
   <si>
@@ -2480,9 +2495,6 @@
   </si>
   <si>
     <t>궤도 고정이라 안정화 부담이 없다. 토요일 오버헤드 프레스와 각도를 나눈다. 더블 프로그레션 — 전 세트가 목표 반복 상단에 닿으면 다음 주에 중량을 올린다</t>
-  </si>
-  <si>
-    <t>덤벨 숄더 프레스 / 스미스 오버헤드 프레스</t>
   </si>
   <si>
     <t>간접 자극이 0인 부위 — 직접 세트로만 채워진다. 더블 프로그레션 — 전 세트가 목표 반복 상단에 닿으면 다음 주에 중량을 올린다</t>
@@ -4653,7 +4665,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4667,12 +4679,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="101" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B2" s="100"/>
       <c r="C2" s="100"/>
@@ -4684,16 +4696,16 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F3">
-        <f ca="1">COUNTIF($E$7:$E$66,"?")</f>
+        <f ca="1">COUNTIF($E$7:$E$68,"?")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
       <c r="A4" s="99" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B4" s="100"/>
       <c r="C4" s="100"/>
@@ -4705,33 +4717,33 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="48" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G6" s="48" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B7" s="49" t="s">
         <v>240</v>
@@ -4751,15 +4763,15 @@
         <v>2</v>
       </c>
       <c r="G7" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H7" s="54" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="49" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B8" s="49" t="s">
         <v>245</v>
@@ -4779,15 +4791,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H8" s="54" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="49" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B9" s="49" t="s">
         <v>352</v>
@@ -4807,15 +4819,15 @@
         <v>2</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H9" s="54" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B10" s="49" t="s">
         <v>356</v>
@@ -4835,15 +4847,15 @@
         <v>2</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="49" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B11" s="49" t="s">
         <v>295</v>
@@ -4863,15 +4875,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H11" s="54" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="49" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B12" s="49" t="s">
         <v>300</v>
@@ -4891,15 +4903,15 @@
         <v>2</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B13" s="49" t="s">
         <v>391</v>
@@ -4919,15 +4931,15 @@
         <v>0.99</v>
       </c>
       <c r="G13" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H13" s="54" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B14" s="49" t="s">
         <v>405</v>
@@ -4947,18 +4959,18 @@
         <v>3</v>
       </c>
       <c r="G14" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C15" s="49" t="s">
         <v>46</v>
@@ -4975,15 +4987,15 @@
         <v>1.32</v>
       </c>
       <c r="G15" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H15" s="54" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="49" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B16" s="49" t="s">
         <v>367</v>
@@ -5003,15 +5015,15 @@
         <v>1.32</v>
       </c>
       <c r="G16" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="49" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B17" s="49" t="s">
         <v>377</v>
@@ -5031,15 +5043,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H17" s="54" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="49" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B18" s="49" t="s">
         <v>295</v>
@@ -5059,15 +5071,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G18" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B19" s="49" t="s">
         <v>405</v>
@@ -5087,15 +5099,15 @@
         <v>3</v>
       </c>
       <c r="G19" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H19" s="54" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B20" s="49" t="s">
         <v>391</v>
@@ -5115,15 +5127,15 @@
         <v>0.99</v>
       </c>
       <c r="G20" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B21" s="49" t="s">
         <v>396</v>
@@ -5143,24 +5155,24 @@
         <v>0.99</v>
       </c>
       <c r="G21" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H21" s="54" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="49" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>255</v>
+        <v>396</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D22" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E22" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5168,21 +5180,21 @@
       </c>
       <c r="F22" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="G22" s="53" t="s">
-        <v>526</v>
+        <v>0.99</v>
+      </c>
+      <c r="G22" s="56" t="s">
+        <v>547</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="49" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>414</v>
+        <v>255</v>
       </c>
       <c r="C23" s="49" t="s">
         <v>29</v>
@@ -5198,16 +5210,16 @@
         <f t="shared" ca="1" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G23" s="56" t="s">
-        <v>544</v>
+      <c r="G23" s="53" t="s">
+        <v>529</v>
       </c>
       <c r="H23" s="54" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="49" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B24" s="49" t="s">
         <v>414</v>
@@ -5226,47 +5238,47 @@
         <f t="shared" ca="1" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="G24" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="H24" s="55" t="s">
-        <v>548</v>
+      <c r="G24" s="56" t="s">
+        <v>547</v>
+      </c>
+      <c r="H24" s="54" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="49" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>352</v>
+        <v>414</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D25" s="50">
         <v>0.5</v>
       </c>
       <c r="E25" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G25" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="H25" s="54" t="s">
-        <v>549</v>
+        <v>529</v>
+      </c>
+      <c r="H25" s="55" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="49" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C26" s="49" t="s">
         <v>21</v>
@@ -5283,18 +5295,18 @@
         <v>2</v>
       </c>
       <c r="G26" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H26" s="54" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="49" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C27" s="49" t="s">
         <v>21</v>
@@ -5304,193 +5316,193 @@
       </c>
       <c r="E27" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F27" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H27" s="54" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="49" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>438</v>
+        <v>363</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D28" s="50">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E28" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G28" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H28" s="54" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="49" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C29" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E29" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="G29" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H29" s="54" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="49" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>279</v>
+        <v>432</v>
       </c>
       <c r="C30" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D30" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E30" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F30" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>0.33</v>
       </c>
       <c r="G30" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H30" s="54" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="49" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="C31" s="49" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D31" s="50">
         <v>0.5</v>
       </c>
       <c r="E31" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G31" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H31" s="54" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="49" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C32" s="49" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E32" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>2.5</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="49" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>432</v>
+        <v>327</v>
       </c>
       <c r="C33" s="49" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E33" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.5</v>
+        <v>0.99</v>
       </c>
       <c r="G33" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H33" s="54" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="49" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C34" s="49" t="s">
         <v>36</v>
@@ -5500,25 +5512,25 @@
       </c>
       <c r="E34" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G34" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H34" s="54" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="49" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="C35" s="49" t="s">
         <v>36</v>
@@ -5528,53 +5540,53 @@
       </c>
       <c r="E35" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F35" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G35" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H35" s="54" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="49" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="C36" s="49" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D36" s="50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E36" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H36" s="54" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="49" t="s">
-        <v>529</v>
+        <v>558</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>377</v>
+        <v>322</v>
       </c>
       <c r="C37" s="49" t="s">
         <v>23</v>
@@ -5584,31 +5596,31 @@
       </c>
       <c r="E37" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F37" s="52">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="G37" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H37" s="54" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
       <c r="A38" s="49" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>441</v>
+        <v>377</v>
       </c>
       <c r="C38" s="49" t="s">
         <v>23</v>
       </c>
       <c r="D38" s="50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E38" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5616,13 +5628,13 @@
       </c>
       <c r="F38" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G38" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="H38" s="55" t="s">
-        <v>562</v>
+        <v>529</v>
+      </c>
+      <c r="H38" s="54" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
@@ -5630,16 +5642,16 @@
         <v>554</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>32</v>
+        <v>441</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D39" s="50">
         <v>0.5</v>
       </c>
       <c r="E39" s="51">
-        <f t="shared" ref="E39:E66" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
+        <f t="shared" ref="E39:E68" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
         <v>3</v>
       </c>
       <c r="F39" s="52">
@@ -5647,24 +5659,24 @@
         <v>1.5</v>
       </c>
       <c r="G39" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="H39" s="54" t="s">
-        <v>563</v>
+        <v>529</v>
+      </c>
+      <c r="H39" s="55" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="49" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B40" s="49" t="s">
         <v>32</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D40" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E40" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -5672,41 +5684,41 @@
       </c>
       <c r="F40" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G40" s="53" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H40" s="54" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="49" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>432</v>
+        <v>32</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D41" s="50">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E41" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G41" s="56" t="s">
-        <v>544</v>
+        <v>0.99</v>
+      </c>
+      <c r="G41" s="53" t="s">
+        <v>529</v>
       </c>
       <c r="H41" s="54" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
@@ -5714,35 +5726,35 @@
         <v>554</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>322</v>
+        <v>432</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D42" s="50">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="E42" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F42" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6500000000000001</v>
+        <v>0</v>
       </c>
       <c r="G42" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H42" s="54" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="49" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C43" s="49" t="s">
         <v>50</v>
@@ -5752,25 +5764,25 @@
       </c>
       <c r="E43" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F43" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G43" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H43" s="54" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
       <c r="A44" s="49" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>32</v>
+        <v>327</v>
       </c>
       <c r="C44" s="49" t="s">
         <v>50</v>
@@ -5787,38 +5799,38 @@
         <v>0.99</v>
       </c>
       <c r="G44" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="49" t="s">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>295</v>
+        <v>32</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D45" s="50">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E45" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F45" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G45" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H45" s="54" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
@@ -5826,147 +5838,147 @@
         <v>534</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>405</v>
+        <v>295</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D46" s="50">
         <v>0</v>
       </c>
       <c r="E46" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F46" s="52">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="G46" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H46" s="54" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="49" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>352</v>
+        <v>405</v>
       </c>
       <c r="C47" s="49" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D47" s="50">
         <v>0</v>
       </c>
       <c r="E47" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F47" s="52">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="G47" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H47" s="54" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="49" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>391</v>
+        <v>352</v>
       </c>
       <c r="C48" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="50">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G48" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H48" s="54" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="49" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>432</v>
+        <v>391</v>
       </c>
       <c r="C49" s="49" t="s">
         <v>17</v>
       </c>
       <c r="D49" s="50">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E49" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G49" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H49" s="54" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="49" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>240</v>
+        <v>432</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D50" s="50">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G50" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H50" s="54" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="49" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>352</v>
+        <v>240</v>
       </c>
       <c r="C51" s="49" t="s">
         <v>19</v>
@@ -5983,77 +5995,77 @@
         <v>0.8</v>
       </c>
       <c r="G51" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H51" s="54" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="49" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D52" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E52" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F52" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6500000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G52" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H52" s="54" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="49" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D53" s="50">
         <v>0.33</v>
       </c>
       <c r="E53" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F53" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G53" s="56" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="H53" s="54" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="49" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B54" s="49" t="s">
         <v>327</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D54" s="50">
         <v>0.33</v>
@@ -6067,24 +6079,24 @@
         <v>0.99</v>
       </c>
       <c r="G54" s="56" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="H54" s="54" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="49" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="B55" s="49" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D55" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E55" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -6092,21 +6104,21 @@
       </c>
       <c r="F55" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>0.99</v>
       </c>
       <c r="G55" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H55" s="54" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C56" s="49" t="s">
         <v>44</v>
@@ -6123,52 +6135,52 @@
         <v>1.5</v>
       </c>
       <c r="G56" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H56" s="54" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="49" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>300</v>
+        <v>396</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D57" s="50">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E57" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G57" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H57" s="54" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B58" s="49" t="s">
         <v>402</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D58" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E58" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -6176,24 +6188,24 @@
       </c>
       <c r="F58" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G58" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H58" s="54" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="49" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>373</v>
+        <v>300</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D59" s="50">
         <v>0.2</v>
@@ -6207,10 +6219,10 @@
         <v>0.8</v>
       </c>
       <c r="G59" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H59" s="54" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
@@ -6218,10 +6230,10 @@
         <v>537</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D60" s="50">
         <v>0.33</v>
@@ -6235,46 +6247,46 @@
         <v>0.99</v>
       </c>
       <c r="G60" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H60" s="54" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="49" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B61" s="49" t="s">
-        <v>468</v>
+        <v>373</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D61" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E61" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G61" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H61" s="54" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B62" s="49" t="s">
-        <v>476</v>
+        <v>363</v>
       </c>
       <c r="C62" s="49" t="s">
         <v>21</v>
@@ -6291,21 +6303,21 @@
         <v>0.99</v>
       </c>
       <c r="G62" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H62" s="54" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1">
       <c r="A63" s="49" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="B63" s="49" t="s">
-        <v>260</v>
+        <v>468</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D63" s="50">
         <v>0.33</v>
@@ -6319,80 +6331,80 @@
         <v>0.99</v>
       </c>
       <c r="G63" s="56" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H63" s="54" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15" customHeight="1">
       <c r="A64" s="49" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D64" s="50">
         <v>0.33</v>
       </c>
       <c r="E64" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.66</v>
-      </c>
-      <c r="G64" s="53" t="s">
-        <v>526</v>
+        <v>0.99</v>
+      </c>
+      <c r="G64" s="56" t="s">
+        <v>547</v>
       </c>
       <c r="H64" s="54" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15" customHeight="1">
       <c r="A65" s="49" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="B65" s="49" t="s">
-        <v>436</v>
+        <v>260</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D65" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E65" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G65" s="53" t="s">
-        <v>526</v>
+        <v>0.99</v>
+      </c>
+      <c r="G65" s="56" t="s">
+        <v>547</v>
       </c>
       <c r="H65" s="54" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15" customHeight="1">
       <c r="A66" s="49" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B66" s="49" t="s">
         <v>436</v>
       </c>
       <c r="C66" s="49" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D66" s="50">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E66" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -6400,13 +6412,69 @@
       </c>
       <c r="F66" s="52">
         <f t="shared" ca="1" si="3"/>
+        <v>0.66</v>
+      </c>
+      <c r="G66" s="53" t="s">
+        <v>529</v>
+      </c>
+      <c r="H66" s="54" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="49" t="s">
+        <v>554</v>
+      </c>
+      <c r="B67" s="49" t="s">
+        <v>436</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E67" s="51">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F67" s="52">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G67" s="53" t="s">
+        <v>529</v>
+      </c>
+      <c r="H67" s="54" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="49" t="s">
+        <v>554</v>
+      </c>
+      <c r="B68" s="49" t="s">
+        <v>436</v>
+      </c>
+      <c r="C68" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="50">
         <v>0</v>
       </c>
-      <c r="G66" s="53" t="s">
-        <v>544</v>
-      </c>
-      <c r="H66" s="54" t="s">
-        <v>590</v>
+      <c r="E68" s="51">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F68" s="52">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G68" s="53" t="s">
+        <v>547</v>
+      </c>
+      <c r="H68" s="54" t="s">
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -6474,7 +6542,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A5),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A5),0.5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="59">
@@ -6513,7 +6581,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A6),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A6),0.5)</f>
         <v>0</v>
       </c>
       <c r="D6" s="59">
@@ -6542,7 +6610,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A7),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A7),0.5)</f>
         <v>0</v>
       </c>
       <c r="D7" s="59">
@@ -6577,7 +6645,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A8),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A8),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D8" s="59">
@@ -6606,7 +6674,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A9),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A9),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D9" s="59">
@@ -6635,7 +6703,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A10),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A10),0.5)</f>
         <v>7.5</v>
       </c>
       <c r="D10" s="59">
@@ -6664,7 +6732,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A11),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A11),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D11" s="59">
@@ -6690,19 +6758,19 @@
       </c>
       <c r="B12" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A12)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A12)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A12)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A12)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A12)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A12)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A12)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C12" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A12),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A12),0.5)</f>
         <v>6.5</v>
       </c>
       <c r="D12" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="E12" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>하한</v>
+        <v>충분</v>
       </c>
       <c r="F12" s="57" t="s">
         <v>26</v>
@@ -6710,7 +6778,7 @@
       <c r="G12" s="61"/>
       <c r="J12" s="59">
         <f t="shared" ca="1" si="2"/>
-        <v>9.6999999999999993</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1">
@@ -6722,12 +6790,12 @@
         <v>18</v>
       </c>
       <c r="C13" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A13),0.5)</f>
-        <v>2</v>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A13),0.5)</f>
+        <v>3</v>
       </c>
       <c r="D13" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6739,7 +6807,7 @@
       <c r="G13" s="61"/>
       <c r="J13" s="59">
         <f t="shared" ca="1" si="2"/>
-        <v>15.6</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1">
@@ -6751,7 +6819,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A14),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A14),0.5)</f>
         <v>4.5</v>
       </c>
       <c r="D14" s="59">
@@ -6781,7 +6849,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A15),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A15),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D15" s="59">
@@ -6816,7 +6884,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A16),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A16),0.5)</f>
         <v>5</v>
       </c>
       <c r="D16" s="59">
@@ -6845,7 +6913,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A17),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A17),0.5)</f>
         <v>10.5</v>
       </c>
       <c r="D17" s="59">
@@ -6880,7 +6948,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A18),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A18),0.5)</f>
         <v>1</v>
       </c>
       <c r="D18" s="59">
@@ -6909,7 +6977,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="58">
-        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A19),0.5)</f>
+        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A19),0.5)</f>
         <v>0</v>
       </c>
       <c r="D19" s="59">
@@ -6938,7 +7006,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A20),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A20),0.5)</f>
         <v>9</v>
       </c>
       <c r="D20" s="59">
@@ -6967,12 +7035,12 @@
         <v>8</v>
       </c>
       <c r="C21" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A21),0.5)</f>
-        <v>10.5</v>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A21),0.5)</f>
+        <v>12</v>
       </c>
       <c r="D21" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="E21" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6984,7 +7052,7 @@
       <c r="G21" s="61"/>
       <c r="J21" s="59">
         <f t="shared" ca="1" si="2"/>
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.5" customHeight="1">
@@ -6996,7 +7064,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A22),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A22),0.5)</f>
         <v>3.5</v>
       </c>
       <c r="D22" s="59">
@@ -7025,7 +7093,7 @@
         <v>13</v>
       </c>
       <c r="C23" s="58">
-        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A23),0.5)</f>
+        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A23),0.5)</f>
         <v>0</v>
       </c>
       <c r="D23" s="59">
@@ -7054,7 +7122,7 @@
         <v>9</v>
       </c>
       <c r="C24" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$66,간접계수맵!$C$7:$C$66,$A24),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A24),0.5)</f>
         <v>4.5</v>
       </c>
       <c r="D24" s="59">
@@ -7080,18 +7148,18 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(B5:B24)</f>
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C25" s="65"/>
       <c r="D25" s="66">
         <f ca="1">SUM(D5:D24)</f>
-        <v>299.5</v>
+        <v>305</v>
       </c>
       <c r="E25" s="65"/>
       <c r="F25" s="65"/>
       <c r="J25" s="66">
         <f t="shared" ca="1" si="2"/>
-        <v>232.9</v>
+        <v>237.2</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1">
@@ -7247,50 +7315,50 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="68" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="67" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="68" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="68" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -7299,13 +7367,13 @@
     </row>
     <row r="8" spans="1:11" ht="84" customHeight="1">
       <c r="A8" s="68" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="67" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
@@ -7313,31 +7381,31 @@
         <v>115</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>236</v>
@@ -7671,17 +7739,17 @@
     </row>
     <row r="23" spans="1:11" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="120" customHeight="1">
@@ -7689,27 +7757,27 @@
     </row>
     <row r="27" spans="1:11" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -7730,23 +7798,23 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="70" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -7754,21 +7822,21 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -7776,80 +7844,80 @@
         <v>23</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="71" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="71" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C10" s="73" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -7857,47 +7925,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -7923,31 +7991,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="74" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>135</v>
@@ -7956,111 +8024,111 @@
         <v>136</v>
       </c>
       <c r="G5" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="75" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="E6" s="75">
         <f>복귀_평일A_가슴!$E$12</f>
         <v>28</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="G6" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>667</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>662</v>
-      </c>
       <c r="C7" s="8" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$15</f>
         <v>35</v>
       </c>
       <c r="F7" s="73" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="G7" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="75" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="E8" s="75">
         <f>복귀_토_하체!$E$14</f>
         <v>32</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="G8" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="75" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="E9" s="75">
         <f>복귀_일_등!$E$16</f>
         <v>33</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="G9" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="75" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C10" s="76" t="s">
         <v>139</v>
@@ -8075,7 +8143,7 @@
         <v>139</v>
       </c>
       <c r="G10" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
@@ -8090,7 +8158,7 @@
         <v>128</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -8111,32 +8179,32 @@
     </row>
     <row r="15" spans="1:7" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -8144,22 +8212,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -8167,32 +8235,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="67" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -8200,47 +8268,47 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="78" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -8250,27 +8318,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -8301,12 +8369,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -8381,10 +8449,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="K5" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="L5" s="72" t="s">
         <v>299</v>
@@ -8395,7 +8463,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C6" s="71" t="s">
         <v>25</v>
@@ -8421,10 +8489,10 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="K6" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="L6" s="72" t="s">
         <v>395</v>
@@ -8460,10 +8528,10 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="K7" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -8496,10 +8564,10 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="K8" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -8532,10 +8600,10 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="K9" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -8549,7 +8617,7 @@
         <v>50</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
@@ -8568,10 +8636,10 @@
         <v>10.7</v>
       </c>
       <c r="J10" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="K10" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -8604,10 +8672,10 @@
         <v>5.8</v>
       </c>
       <c r="J11" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="K11" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -8615,13 +8683,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="80" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="E12" s="28">
         <v>3</v>
@@ -8640,10 +8708,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="K12" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -8676,10 +8744,10 @@
         <v>6.7</v>
       </c>
       <c r="J13" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="K13" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="76.5" customHeight="1">
@@ -8702,72 +8770,72 @@
     </row>
     <row r="16" spans="1:13" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
     </row>
   </sheetData>
@@ -8798,12 +8866,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -8878,10 +8946,10 @@
         <v>3.5</v>
       </c>
       <c r="J5" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="K5" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -8889,13 +8957,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
@@ -8914,13 +8982,13 @@
         <v>12.7</v>
       </c>
       <c r="J6" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="K6" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="L6" s="57" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -8928,7 +8996,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="93" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>14</v>
@@ -8953,10 +9021,10 @@
         <v>12.7</v>
       </c>
       <c r="J7" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="K7" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -8989,13 +9057,13 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J8" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="K8" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="L8" s="57" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="29.25" customHeight="1">
@@ -9009,7 +9077,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -9028,10 +9096,10 @@
         <v>5.8</v>
       </c>
       <c r="J9" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="K9" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9045,7 +9113,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -9064,10 +9132,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="K10" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -9100,13 +9168,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="K11" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="L11" s="57" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -9139,10 +9207,10 @@
         <v>7.3</v>
       </c>
       <c r="J12" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="K12" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
@@ -9175,10 +9243,10 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="K13" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -9186,7 +9254,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -9211,10 +9279,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="K14" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1">
@@ -9247,10 +9315,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="K15" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="23.25" customHeight="1">
@@ -9273,112 +9341,112 @@
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="67" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
     </row>
   </sheetData>
@@ -9409,12 +9477,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -9488,10 +9556,10 @@
         <v>10.7</v>
       </c>
       <c r="J5" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="K5" t="s">
-        <v>809</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -9524,10 +9592,10 @@
         <v>6.7</v>
       </c>
       <c r="J6" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="K6" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -9535,13 +9603,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
@@ -9560,10 +9628,10 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="K7" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -9596,10 +9664,10 @@
         <v>6.7</v>
       </c>
       <c r="J8" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="K8" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -9613,7 +9681,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -9632,10 +9700,10 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K9" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9643,7 +9711,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>42</v>
@@ -9668,10 +9736,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="K10" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -9685,7 +9753,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="80" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -9704,10 +9772,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="K11" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -9740,10 +9808,10 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="K12" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
@@ -9776,10 +9844,10 @@
         <v>10.7</v>
       </c>
       <c r="J13" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="K13" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
@@ -9812,10 +9880,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="K14" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="25.5" customHeight="1">
@@ -9834,72 +9902,72 @@
     </row>
     <row r="16" spans="1:13" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
     </row>
   </sheetData>
@@ -9930,12 +9998,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -10010,10 +10078,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="K5" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="L5" s="72" t="s">
         <v>299</v>
@@ -10030,7 +10098,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="E6" s="7">
         <v>5</v>
@@ -10049,10 +10117,10 @@
         <v>15.8</v>
       </c>
       <c r="J6" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="K6" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10060,7 +10128,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>9</v>
@@ -10085,10 +10153,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J7" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="K7" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10121,10 +10189,10 @@
         <v>12.7</v>
       </c>
       <c r="J8" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="K8" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -10132,7 +10200,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="93" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>14</v>
@@ -10157,10 +10225,10 @@
         <v>10.7</v>
       </c>
       <c r="J9" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="K9" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10193,10 +10261,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="K10" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10229,10 +10297,10 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="K11" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -10264,27 +10332,27 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="C27" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
     </row>
   </sheetData>
@@ -10306,166 +10374,166 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D5" s="73" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>139</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="83" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B13" s="84" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C13" s="84" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="D13" s="83" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B14" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C14" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="D14" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -10476,22 +10544,22 @@
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
@@ -10499,137 +10567,137 @@
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
       <c r="A23" s="67" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
     </row>
   </sheetData>
@@ -10846,12 +10914,12 @@
         <v>164</v>
       </c>
       <c r="E12" s="23">
-        <f>D8_어깨!$E$17</f>
-        <v>37</v>
+        <f>D8_어깨!$E$18</f>
+        <v>40</v>
       </c>
       <c r="F12" s="26" t="str">
-        <f>"약 "&amp;D8_어깨!$I$17&amp;"분"</f>
-        <v>약 68분</v>
+        <f>"약 "&amp;D8_어깨!$I$18&amp;"분"</f>
+        <v>약 76분</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
@@ -10881,11 +10949,11 @@
       <c r="D14" s="28"/>
       <c r="E14" s="27">
         <f>SUM(E5:E13)</f>
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F14" t="str">
-        <f>"약 "&amp;(D1_당기기A!$I$16+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$16+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$17)&amp;"분 ("&amp;INT((D1_당기기A!$I$16+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$16+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$17)/60)&amp;"시간 "&amp;MOD((D1_당기기A!$I$16+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$16+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$17),60)&amp;"분)"</f>
-        <v>약 535분 (8시간 55분)</v>
+        <f>"약 "&amp;(D1_당기기A!$I$16+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$16+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)&amp;"분 ("&amp;INT((D1_당기기A!$I$16+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$16+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)/60)&amp;"시간 "&amp;MOD((D1_당기기A!$I$16+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$16+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18),60)&amp;"분)"</f>
+        <v>약 543분 (9시간 3분)</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.5" customHeight="1"/>
@@ -11214,17 +11282,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$51,"?")</f>
@@ -11233,38 +11301,38 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B6" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C6" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D6" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F6" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G6" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="H6" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B7" t="s">
         <v>352</v>
@@ -11284,18 +11352,18 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H7" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B8" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
@@ -11312,18 +11380,18 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H8" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B9" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -11340,18 +11408,18 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H9" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B10" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
@@ -11368,15 +11436,15 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H10" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B11" t="s">
         <v>240</v>
@@ -11396,15 +11464,15 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H11" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B12" t="s">
         <v>90</v>
@@ -11424,15 +11492,15 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H12" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B13" t="s">
         <v>405</v>
@@ -11452,15 +11520,15 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H13" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B15" t="s">
         <v>396</v>
@@ -11480,18 +11548,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H15" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B16" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -11508,15 +11576,15 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H16" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B17" t="s">
         <v>300</v>
@@ -11536,15 +11604,15 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H17" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B18" t="s">
         <v>90</v>
@@ -11564,15 +11632,15 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H18" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B19" t="s">
         <v>405</v>
@@ -11592,15 +11660,15 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H19" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B20" t="s">
         <v>300</v>
@@ -11620,18 +11688,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G20" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H20" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B21" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -11648,15 +11716,15 @@
         <v>1.5</v>
       </c>
       <c r="G21" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H21" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B22" t="s">
         <v>352</v>
@@ -11676,18 +11744,18 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H22" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B23" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C23" t="s">
         <v>21</v>
@@ -11704,18 +11772,18 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H23" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B24" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
@@ -11732,15 +11800,15 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H24" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B25" t="s">
         <v>363</v>
@@ -11760,15 +11828,15 @@
         <v>1.5</v>
       </c>
       <c r="G25" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H25" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B26" t="s">
         <v>408</v>
@@ -11788,18 +11856,18 @@
         <v>1.32</v>
       </c>
       <c r="G26" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H26" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B27" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
@@ -11816,18 +11884,18 @@
         <v>0.99</v>
       </c>
       <c r="G27" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H27" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B28" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -11844,18 +11912,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H28" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B29" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
@@ -11872,15 +11940,15 @@
         <v>0.8</v>
       </c>
       <c r="G29" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H29" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B30" t="s">
         <v>88</v>
@@ -11900,15 +11968,15 @@
         <v>0.2</v>
       </c>
       <c r="G30" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H30" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B31" t="s">
         <v>240</v>
@@ -11928,18 +11996,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G31" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H31" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B32" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
@@ -11956,15 +12024,15 @@
         <v>0.8</v>
       </c>
       <c r="G32" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H32" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B33" t="s">
         <v>86</v>
@@ -11984,18 +12052,18 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H33" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B34" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C34" t="s">
         <v>23</v>
@@ -12012,15 +12080,15 @@
         <v>0.8</v>
       </c>
       <c r="G34" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H34" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B35" t="s">
         <v>381</v>
@@ -12040,15 +12108,15 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G35" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H35" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B36" t="s">
         <v>86</v>
@@ -12068,15 +12136,15 @@
         <v>2.5</v>
       </c>
       <c r="G36" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H36" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B37" t="s">
         <v>88</v>
@@ -12096,15 +12164,15 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H37" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B38" t="s">
         <v>327</v>
@@ -12124,15 +12192,15 @@
         <v>1.32</v>
       </c>
       <c r="G38" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H38" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B39" t="s">
         <v>438</v>
@@ -12152,15 +12220,15 @@
         <v>1.5</v>
       </c>
       <c r="G39" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H39" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B40" t="s">
         <v>88</v>
@@ -12180,15 +12248,15 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H40" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B41" t="s">
         <v>86</v>
@@ -12208,15 +12276,15 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H41" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B42" t="s">
         <v>327</v>
@@ -12236,18 +12304,18 @@
         <v>0.8</v>
       </c>
       <c r="G42" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H42" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B43" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C43" t="s">
         <v>46</v>
@@ -12264,15 +12332,15 @@
         <v>0.99</v>
       </c>
       <c r="G43" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H43" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B44" t="s">
         <v>367</v>
@@ -12292,15 +12360,15 @@
         <v>0.99</v>
       </c>
       <c r="G44" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H44" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B45" t="s">
         <v>90</v>
@@ -12320,15 +12388,15 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H45" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B46" t="s">
         <v>405</v>
@@ -12348,15 +12416,15 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H46" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B47" t="s">
         <v>88</v>
@@ -12376,15 +12444,15 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H47" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B48" t="s">
         <v>86</v>
@@ -12404,15 +12472,15 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H48" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B49" t="s">
         <v>452</v>
@@ -12432,18 +12500,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H49" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B50" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -12460,18 +12528,18 @@
         <v>0.8</v>
       </c>
       <c r="G50" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H50" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B51" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C51" t="s">
         <v>25</v>
@@ -12488,10 +12556,10 @@
         <v>0.8</v>
       </c>
       <c r="G51" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H51" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
     </row>
   </sheetData>
@@ -12517,12 +12585,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -12545,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -12569,10 +12637,10 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="G5" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -12603,10 +12671,10 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="G6" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -12630,13 +12698,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="G7" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H7" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -12664,10 +12732,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="G8" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -12691,10 +12759,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="G9" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -12718,10 +12786,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="G10" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -12745,10 +12813,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="G11" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -12772,10 +12840,10 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="G12" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -12799,10 +12867,10 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="G13" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -12826,10 +12894,10 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="G14" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -12853,13 +12921,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="G15" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H15" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -12887,10 +12955,10 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="G16" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -12914,10 +12982,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="G17" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -12941,10 +13009,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="G18" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -12968,10 +13036,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="G19" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -12995,10 +13063,10 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="G20" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -13022,10 +13090,10 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="G21" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -13049,10 +13117,10 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="G22" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -13076,10 +13144,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="G23" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -13103,10 +13171,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="G24" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -13129,62 +13197,62 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
     </row>
   </sheetData>
@@ -16291,7 +16359,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -16396,7 +16464,7 @@
         <v>70</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I16" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I17" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
         <v>5.5</v>
       </c>
       <c r="J6" s="21"/>
@@ -16603,38 +16671,38 @@
         <v>7</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>415</v>
+        <v>479</v>
       </c>
       <c r="E12" s="20">
         <v>3</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="G12" s="26">
         <v>40</v>
       </c>
       <c r="H12" s="26">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I12" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>29</v>
+        <v>392</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
@@ -16642,16 +16710,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>337</v>
+        <v>414</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="E13" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F13" s="26" t="s">
         <v>256</v>
@@ -16660,21 +16728,20 @@
         <v>40</v>
       </c>
       <c r="H13" s="26">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I13" s="26">
         <f t="shared" si="0"/>
-        <v>4.2</v>
-      </c>
-      <c r="J13" s="21"/>
+        <v>5</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>29</v>
+      </c>
       <c r="K13" s="21" t="s">
         <v>482</v>
       </c>
       <c r="L13" s="21" t="s">
         <v>483</v>
-      </c>
-      <c r="N13" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
@@ -16682,13 +16749,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>261</v>
+        <v>484</v>
       </c>
       <c r="E14" s="20">
         <v>5</v>
@@ -16700,18 +16767,18 @@
         <v>40</v>
       </c>
       <c r="H14" s="26">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="I14" s="26">
         <f t="shared" si="0"/>
-        <v>12.1</v>
+        <v>4.2</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N14" t="s">
         <v>340</v>
@@ -16722,16 +16789,16 @@
         <v>10</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>452</v>
+        <v>341</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>162</v>
+        <v>261</v>
       </c>
       <c r="E15" s="20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F15" s="26" t="s">
         <v>256</v>
@@ -16740,18 +16807,21 @@
         <v>40</v>
       </c>
       <c r="H15" s="26">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="I15" s="26">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>12.1</v>
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>487</v>
+        <v>488</v>
+      </c>
+      <c r="N15" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -16759,33 +16829,31 @@
         <v>11</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>488</v>
+        <v>452</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="20">
-        <v>6</v>
+        <v>40</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>162</v>
       </c>
       <c r="E16" s="20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="G16" s="26">
         <v>40</v>
       </c>
       <c r="H16" s="26">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I16" s="26">
         <f t="shared" si="0"/>
-        <v>7.3</v>
-      </c>
-      <c r="J16" s="21" t="s">
-        <v>46</v>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
         <v>489</v>
       </c>
@@ -16793,133 +16861,172 @@
         <v>490</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="16.5" customHeight="1">
-      <c r="D17" s="3" t="s">
+    <row r="17" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A17" s="20">
+        <v>12</v>
+      </c>
+      <c r="B17" s="85" t="s">
+        <v>491</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="20">
+        <v>6</v>
+      </c>
+      <c r="E17" s="20">
+        <v>4</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="G17" s="26">
+        <v>40</v>
+      </c>
+      <c r="H17" s="26">
+        <v>70</v>
+      </c>
+      <c r="I17" s="26">
+        <f t="shared" si="0"/>
+        <v>7.3</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="16.5" customHeight="1">
+      <c r="D18" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E17" s="27">
-        <f>SUM(E6:E16)</f>
-        <v>37</v>
-      </c>
-      <c r="I17">
-        <f>ROUND(SUM(I6:I16),0)</f>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="19" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A20" s="31" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16.5" customHeight="1">
+      <c r="E18" s="27">
+        <f>SUM(E6:E17)</f>
+        <v>40</v>
+      </c>
+      <c r="I18">
+        <f>ROUND(SUM(I6:I17),0)</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="16.5" customHeight="1"/>
+    <row r="20" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="16.5" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16.5" customHeight="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="16.5" customHeight="1">
       <c r="A22" s="31" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16.5" customHeight="1">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="16.5" customHeight="1">
       <c r="A23" s="31" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A25" s="31" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="16.5" customHeight="1">
+    <row r="24" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A24" s="31" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="16.5" customHeight="1">
       <c r="A26" s="31" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A28" s="31" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="16.5" customHeight="1">
+    <row r="27" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A27" s="31" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="16.5" customHeight="1">
       <c r="A29" s="31" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="16.5" customHeight="1">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="16.5" customHeight="1">
       <c r="A30" s="31" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="16.5" customHeight="1">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16.5" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A32" s="31" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A33" s="31" t="s">
-        <v>505</v>
+      <c r="A33" s="3" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>509</v>
+      <c r="A37" s="31" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A38" s="31" t="s">
-        <v>510</v>
+      <c r="A38" s="3" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1">
       <c r="A39" s="31" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="16.5" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="31" t="s">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="34" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N16">
+  <conditionalFormatting sqref="A6:N17">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E6=0</formula>
     </cfRule>

--- a/운동프로그램_8일주기_v19.xlsx
+++ b/운동프로그램_8일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A24B24B3FC0402CFCC26E73951A515A1BBC1D131" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_BAE21613F2167B2C6F9578C214A933A87AF2AA1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="1021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2034" uniqueCount="1024">
   <si>
     <t>근육군별 주간 세트 — 검산</t>
   </si>
@@ -268,7 +268,7 @@
     <t>· 9일 주기 전환 · 약점 보강 (2026-09-04): 8일차 뒤에 휴식을 넣어 9일 주기가 됐다. 이유는 D8을 키우려서가 아니라 5→6→7→8→1→2→3으로 7일 연속 훈련이었기 때문이다(휴식이 4일차 하나뿐이었다). 이제 3연속·휴식·4연속·휴식이다. 대신 판정 분모가 ×7/8에서 ×7/9로 바뀌어 모든 부위가 11% 내려가므로, 부족했던 7개를 성장 구간(주당 10)까지 올렸다 — 흉근(상부)·승모(하부)·중둔근·종아리·복부·내전근 여섯은 도달, 기립근은 하한권에 남았다(아래 참조). 배치 원칙: 하체날(3·7일차)은 이미 가장 긴 세션(77분·80분)이라 한 세트도 얹지 않았다. 추가분은 전부 고립 종목(실측 1.9분/세트)이라 시간이 싸고, 가장 가벼웠던 8일차(41분)가 절반을 흡수했다. 세션 상한도 세트 수(26)가 아니라 시간 80분으로 바꿔 읽는다 — 8일차는 35세트지만 66분으로 7일차 27세트 80분보다 가볍다.</t>
   </si>
   <si>
-    <t>· 기립근은 성장까지 못 갔다 (2026-09-04): 고립 종목이 없다. 1일차 메모대로 백 익스텐션을 덤벨 RDL로 대체해 뒀고, 동적 힌지 말고는 기립근을 키울 수단이 없다. 3→6세트로 올려 실질 10.5(주당 8.2, 하한)까지가 한계였다. 성장까지 채우려면 힌지를 사이클당 3일로 늘려야 하는데 그건 고립 추가와 성격이 다르다(척추 부하 · 회복 비용). 백 익스텐션이나 45도 하이퍼익스텐션 기구를 쓸 수 있으면 3세트로 싸게 해결된다.</t>
+    <t>· 기립근 해결 (2026-09-04): 고립 종목이 없어 1일차 덤벨 RDL 3→6으로 버티다가 하한(주당 8.2)에 그쳤었다. 백 익스텐션(45도)을 쓸 수 있다는 확인을 받고 1일차·5일차에 3세트씩 넣고 덤벨 RDL은 3으로 되돌렸다. 직접 12 · 주당 10.5로 성장 구간. 힌지를 늘리는 대신 전용 종목을 둔 것이라 척추 부하는 오히려 줄었다. 수행은 척추 신전 강조 — 힌지식으로 하면 주동근이 둔근·햄스트링으로 바뀐다.</t>
   </si>
   <si>
     <t>· 견갑 프라이밍 웜업 — 1일차 스캡 풀업 2 (하강) · 2·6일차 케이블 외회전 2씩 · 5일차 밴드 풀 어파트 2 (후인). 네 상체일 전부 그날 패턴의 웜업 보유. (1일차 페이스풀은 실제 부하 카운트 세트이므로 여기서 제외)</t>
@@ -892,6 +892,15 @@
     <t>레그 프레스 카프 (기계가 비었을 때) / 스미스 카프 레이즈</t>
   </si>
   <si>
+    <t>백 익스텐션 (45도)</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 45도 백 익스텐션. 이 프로그램의 원래 설계 종목이었는데 기구를 못 써서 덤벨 RDL로 대체해 뒀던 것을 되돌렸다. **척추 신전을 강조해서 한다** — 등을 편 채 고관절만 접는 힌지식으로 하면 둔근·햄스트링이 주동근이 되고 기립근은 버티기만 하게 되어 이 칸의 뜻이 달라진다. 그래서 간접계수맵에 둔근·햄스트링 행을 달지 않았다: 척추 신전식에서 고관절 신근은 등척성이고, 등척성은 계수 0이 이 표의 규칙이다.</t>
+  </si>
+  <si>
+    <t>원판 5~10kg 안고 (맨몸이 쉬워지면) / 굿모닝(스미스) / 덤벨 루마니안 데드리프트</t>
+  </si>
+  <si>
     <t>덤벨 루마니안 데드리프트</t>
   </si>
   <si>
@@ -901,7 +910,7 @@
     <t>둔근·햄스트링</t>
   </si>
   <si>
-    <t>(원래는 백 익스텐션)기립근 보조. 20kg으로 가볍게 — 무게를 올리면 햄스트링 종목이 되고 척추 부하도 같이 올라간다. 데드(7일차)와 이틀 간격이라 이 자리가 맞다 [2026-09-04 3→6] 기립근 보강. 백 익스텐션을 이 종목으로 대체해 뒀으므로 기립근을 늘릴 수단이 이것뿐이다. 동적 힌지만 기립근을 키운다 — 스쿼트·데드의 버티기는 계수 0으로 내렸다.</t>
+    <t>(원래는 백 익스텐션)기립근 보조. 20kg으로 가볍게 — 무게를 올리면 햄스트링 종목이 되고 척추 부하도 같이 올라간다. 데드(7일차)와 이틀 간격이라 이 자리가 맞다 [2026-09-04 3→6→3] 백 익스텐션이 없던 동안 기립근을 늘릴 수단이 이것뿐이라 6으로 올렸다가, 기구를 쓸 수 있다는 확인을 받고 3으로 되돌렸다. 힌지를 두 배로 하는 것보다 기립근 전용 종목을 따로 두는 편이 척추 부하도 낮고 자극도 곧다.</t>
   </si>
   <si>
     <t>케이블 풀스루 (척추 압박 최소) / 굿모닝 (빈 봉~40kg, 가볍게) / 45도 하이퍼익스텐션 벤치 (있는 경우) / 스티프 레그드 데드리프트. 어느 쪽이든 가볍게 — 성장이 아니라 자세 유지가 목적</t>
@@ -4679,12 +4688,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="101" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B2" s="100"/>
       <c r="C2" s="100"/>
@@ -4696,7 +4705,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$68,"?")</f>
@@ -4705,7 +4714,7 @@
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
       <c r="A4" s="99" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B4" s="100"/>
       <c r="C4" s="100"/>
@@ -4717,33 +4726,33 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="48" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G6" s="48" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B7" s="49" t="s">
         <v>240</v>
@@ -4763,15 +4772,15 @@
         <v>2</v>
       </c>
       <c r="G7" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H7" s="54" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="49" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B8" s="49" t="s">
         <v>245</v>
@@ -4791,18 +4800,18 @@
         <v>2</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H8" s="54" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C9" s="49" t="s">
         <v>42</v>
@@ -4819,18 +4828,18 @@
         <v>2</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H9" s="54" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C10" s="49" t="s">
         <v>42</v>
@@ -4847,18 +4856,18 @@
         <v>2</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C11" s="49" t="s">
         <v>44</v>
@@ -4875,18 +4884,18 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H11" s="54" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C12" s="49" t="s">
         <v>44</v>
@@ -4903,18 +4912,18 @@
         <v>2</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C13" s="49" t="s">
         <v>44</v>
@@ -4931,18 +4940,18 @@
         <v>0.99</v>
       </c>
       <c r="G13" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H13" s="54" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C14" s="49" t="s">
         <v>44</v>
@@ -4959,18 +4968,18 @@
         <v>3</v>
       </c>
       <c r="G14" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="49" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C15" s="49" t="s">
         <v>46</v>
@@ -4987,18 +4996,18 @@
         <v>1.32</v>
       </c>
       <c r="G15" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H15" s="54" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C16" s="49" t="s">
         <v>46</v>
@@ -5015,18 +5024,18 @@
         <v>1.32</v>
       </c>
       <c r="G16" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C17" s="49" t="s">
         <v>46</v>
@@ -5043,18 +5052,18 @@
         <v>0</v>
       </c>
       <c r="G17" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H17" s="54" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C18" s="49" t="s">
         <v>25</v>
@@ -5071,18 +5080,18 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G18" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C19" s="49" t="s">
         <v>25</v>
@@ -5099,18 +5108,18 @@
         <v>3</v>
       </c>
       <c r="G19" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H19" s="54" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C20" s="49" t="s">
         <v>27</v>
@@ -5127,18 +5136,18 @@
         <v>0.99</v>
       </c>
       <c r="G20" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C21" s="49" t="s">
         <v>27</v>
@@ -5155,18 +5164,18 @@
         <v>0.99</v>
       </c>
       <c r="G21" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H21" s="54" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="49" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C22" s="49" t="s">
         <v>27</v>
@@ -5183,15 +5192,15 @@
         <v>0.99</v>
       </c>
       <c r="G22" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="49" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B23" s="49" t="s">
         <v>255</v>
@@ -5211,18 +5220,18 @@
         <v>1.5</v>
       </c>
       <c r="G23" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H23" s="54" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="49" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C24" s="49" t="s">
         <v>29</v>
@@ -5239,18 +5248,18 @@
         <v>1.5</v>
       </c>
       <c r="G24" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H24" s="54" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C25" s="49" t="s">
         <v>29</v>
@@ -5267,18 +5276,18 @@
         <v>1.5</v>
       </c>
       <c r="G25" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H25" s="55" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C26" s="49" t="s">
         <v>21</v>
@@ -5295,18 +5304,18 @@
         <v>2</v>
       </c>
       <c r="G26" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H26" s="54" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C27" s="49" t="s">
         <v>21</v>
@@ -5323,18 +5332,18 @@
         <v>2</v>
       </c>
       <c r="G27" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H27" s="54" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C28" s="49" t="s">
         <v>21</v>
@@ -5351,18 +5360,18 @@
         <v>0</v>
       </c>
       <c r="G28" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H28" s="54" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C29" s="49" t="s">
         <v>34</v>
@@ -5379,18 +5388,18 @@
         <v>0.8</v>
       </c>
       <c r="G29" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H29" s="54" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C30" s="49" t="s">
         <v>34</v>
@@ -5407,18 +5416,18 @@
         <v>0.33</v>
       </c>
       <c r="G30" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H30" s="54" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="49" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C31" s="49" t="s">
         <v>34</v>
@@ -5428,25 +5437,25 @@
       </c>
       <c r="E31" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F31" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G31" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H31" s="54" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="49" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C32" s="49" t="s">
         <v>36</v>
@@ -5463,18 +5472,18 @@
         <v>2.5</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="49" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C33" s="49" t="s">
         <v>36</v>
@@ -5491,18 +5500,18 @@
         <v>0.99</v>
       </c>
       <c r="G33" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H33" s="54" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C34" s="49" t="s">
         <v>36</v>
@@ -5519,18 +5528,18 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H34" s="54" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C35" s="49" t="s">
         <v>36</v>
@@ -5547,18 +5556,18 @@
         <v>1.5</v>
       </c>
       <c r="G35" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H35" s="54" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="49" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C36" s="49" t="s">
         <v>36</v>
@@ -5568,25 +5577,25 @@
       </c>
       <c r="E36" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F36" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G36" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H36" s="54" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="49" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C37" s="49" t="s">
         <v>23</v>
@@ -5603,18 +5612,18 @@
         <v>0</v>
       </c>
       <c r="G37" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H37" s="54" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
       <c r="A38" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C38" s="49" t="s">
         <v>23</v>
@@ -5631,18 +5640,18 @@
         <v>0</v>
       </c>
       <c r="G38" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H38" s="54" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C39" s="49" t="s">
         <v>23</v>
@@ -5659,15 +5668,15 @@
         <v>1.5</v>
       </c>
       <c r="G39" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H39" s="55" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="49" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B40" s="49" t="s">
         <v>32</v>
@@ -5687,15 +5696,15 @@
         <v>1.5</v>
       </c>
       <c r="G40" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H40" s="54" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="49" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B41" s="49" t="s">
         <v>32</v>
@@ -5715,18 +5724,18 @@
         <v>0.99</v>
       </c>
       <c r="G41" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H41" s="54" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
       <c r="A42" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C42" s="49" t="s">
         <v>14</v>
@@ -5743,18 +5752,18 @@
         <v>0</v>
       </c>
       <c r="G42" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H42" s="54" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="49" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C43" s="49" t="s">
         <v>50</v>
@@ -5771,18 +5780,18 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G43" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H43" s="54" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
       <c r="A44" s="49" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C44" s="49" t="s">
         <v>50</v>
@@ -5799,15 +5808,15 @@
         <v>0.99</v>
       </c>
       <c r="G44" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="49" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B45" s="49" t="s">
         <v>32</v>
@@ -5827,18 +5836,18 @@
         <v>0.99</v>
       </c>
       <c r="G45" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H45" s="54" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
       <c r="A46" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C46" s="49" t="s">
         <v>9</v>
@@ -5855,18 +5864,18 @@
         <v>0</v>
       </c>
       <c r="G46" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H46" s="54" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C47" s="49" t="s">
         <v>12</v>
@@ -5883,18 +5892,18 @@
         <v>0</v>
       </c>
       <c r="G47" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H47" s="54" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C48" s="49" t="s">
         <v>17</v>
@@ -5911,18 +5920,18 @@
         <v>0</v>
       </c>
       <c r="G48" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H48" s="54" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C49" s="49" t="s">
         <v>17</v>
@@ -5939,18 +5948,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G49" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H49" s="54" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C50" s="49" t="s">
         <v>17</v>
@@ -5967,15 +5976,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H50" s="54" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="49" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B51" s="49" t="s">
         <v>240</v>
@@ -5995,18 +6004,18 @@
         <v>0.8</v>
       </c>
       <c r="G51" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H51" s="54" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C52" s="49" t="s">
         <v>19</v>
@@ -6023,18 +6032,18 @@
         <v>0.8</v>
       </c>
       <c r="G52" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H52" s="54" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C53" s="49" t="s">
         <v>21</v>
@@ -6051,18 +6060,18 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G53" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H53" s="54" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C54" s="49" t="s">
         <v>36</v>
@@ -6079,18 +6088,18 @@
         <v>0.99</v>
       </c>
       <c r="G54" s="56" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H54" s="54" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B55" s="49" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C55" s="49" t="s">
         <v>50</v>
@@ -6107,18 +6116,18 @@
         <v>0.99</v>
       </c>
       <c r="G55" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H55" s="54" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C56" s="49" t="s">
         <v>44</v>
@@ -6135,18 +6144,18 @@
         <v>1.5</v>
       </c>
       <c r="G56" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H56" s="54" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="49" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C57" s="49" t="s">
         <v>44</v>
@@ -6163,18 +6172,18 @@
         <v>1.5</v>
       </c>
       <c r="G57" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H57" s="54" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B58" s="49" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C58" s="49" t="s">
         <v>44</v>
@@ -6191,18 +6200,18 @@
         <v>1.5</v>
       </c>
       <c r="G58" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H58" s="54" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C59" s="49" t="s">
         <v>25</v>
@@ -6219,18 +6228,18 @@
         <v>0.8</v>
       </c>
       <c r="G59" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H59" s="54" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
       <c r="A60" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C60" s="49" t="s">
         <v>25</v>
@@ -6247,18 +6256,18 @@
         <v>0.99</v>
       </c>
       <c r="G60" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H60" s="54" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="49" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B61" s="49" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C61" s="49" t="s">
         <v>42</v>
@@ -6275,18 +6284,18 @@
         <v>0.8</v>
       </c>
       <c r="G61" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H61" s="54" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="49" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B62" s="49" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C62" s="49" t="s">
         <v>21</v>
@@ -6303,18 +6312,18 @@
         <v>0.99</v>
       </c>
       <c r="G62" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H62" s="54" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1">
       <c r="A63" s="49" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B63" s="49" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C63" s="49" t="s">
         <v>17</v>
@@ -6331,18 +6340,18 @@
         <v>0.99</v>
       </c>
       <c r="G63" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H63" s="54" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15" customHeight="1">
       <c r="A64" s="49" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C64" s="49" t="s">
         <v>21</v>
@@ -6359,15 +6368,15 @@
         <v>0.99</v>
       </c>
       <c r="G64" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H64" s="54" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15" customHeight="1">
       <c r="A65" s="49" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B65" s="49" t="s">
         <v>260</v>
@@ -6387,18 +6396,18 @@
         <v>0.99</v>
       </c>
       <c r="G65" s="56" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H65" s="54" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15" customHeight="1">
       <c r="A66" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B66" s="49" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C66" s="49" t="s">
         <v>34</v>
@@ -6415,18 +6424,18 @@
         <v>0.66</v>
       </c>
       <c r="G66" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H66" s="54" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B67" s="49" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C67" s="49" t="s">
         <v>36</v>
@@ -6443,18 +6452,18 @@
         <v>1</v>
       </c>
       <c r="G67" s="53" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H67" s="54" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="49" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B68" s="49" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C68" s="49" t="s">
         <v>17</v>
@@ -6471,10 +6480,10 @@
         <v>0</v>
       </c>
       <c r="G68" s="53" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H68" s="54" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -6729,7 +6738,7 @@
       </c>
       <c r="B11" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A11)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A11)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A11)+SUMIFS(D5_당기기B!$E:$E,D5_당기기B!$C:$C,$A11)+SUMIFS(D6_밀기B!$E:$E,D6_밀기B!$C:$C,$A11)+SUMIFS(D7_하체B!$E:$E,D7_하체B!$C:$C,$A11)+SUMIFS(D8_어깨!$E:$E,D8_어깨!$C:$C,$A11)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11" s="58">
         <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A11),0.5)</f>
@@ -6737,11 +6746,11 @@
       </c>
       <c r="D11" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="E11" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>하한</v>
+        <v>충분</v>
       </c>
       <c r="F11" s="57" t="s">
         <v>24</v>
@@ -6749,7 +6758,7 @@
       <c r="G11" s="61"/>
       <c r="J11" s="59">
         <f t="shared" ca="1" si="2"/>
-        <v>8.1999999999999993</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1">
@@ -6868,7 +6877,7 @@
       </c>
       <c r="H15" s="60">
         <f ca="1">SUM(D15:D16,D19)</f>
-        <v>44.5</v>
+        <v>43</v>
       </c>
       <c r="J15" s="59">
         <f t="shared" ca="1" si="2"/>
@@ -6885,11 +6894,11 @@
       </c>
       <c r="C16" s="58">
         <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A16),0.5)</f>
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D16" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="E16" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6901,7 +6910,7 @@
       <c r="G16" s="61"/>
       <c r="J16" s="59">
         <f t="shared" ca="1" si="2"/>
-        <v>11.7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
@@ -6914,11 +6923,11 @@
       </c>
       <c r="C17" s="58">
         <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A17),0.5)</f>
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="D17" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="E17" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6932,11 +6941,11 @@
       </c>
       <c r="H17" s="60">
         <f ca="1">SUM(D17:D18)</f>
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="J17" s="59">
         <f t="shared" ca="1" si="2"/>
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1">
@@ -7148,7 +7157,7 @@
       </c>
       <c r="B25" s="15">
         <f>SUM(B5:B24)</f>
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C25" s="65"/>
       <c r="D25" s="66">
@@ -7315,50 +7324,50 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="68" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="67" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="68" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="68" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -7367,13 +7376,13 @@
     </row>
     <row r="8" spans="1:11" ht="84" customHeight="1">
       <c r="A8" s="68" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="67" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
@@ -7381,31 +7390,31 @@
         <v>115</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="I9" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>612</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>609</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>236</v>
@@ -7739,17 +7748,17 @@
     </row>
     <row r="23" spans="1:11" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="120" customHeight="1">
@@ -7757,27 +7766,27 @@
     </row>
     <row r="27" spans="1:11" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -7798,23 +7807,23 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="70" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -7822,21 +7831,21 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -7844,80 +7853,80 @@
         <v>23</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="71" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="71" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C10" s="73" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -7925,47 +7934,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -7991,31 +8000,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="74" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>135</v>
@@ -8024,111 +8033,111 @@
         <v>136</v>
       </c>
       <c r="G5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="75" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E6" s="75">
         <f>복귀_평일A_가슴!$E$12</f>
         <v>28</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="G6" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$15</f>
         <v>35</v>
       </c>
       <c r="F7" s="73" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="G7" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="75" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E8" s="75">
         <f>복귀_토_하체!$E$14</f>
         <v>32</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="G8" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="75" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E9" s="75">
         <f>복귀_일_등!$E$16</f>
         <v>33</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="G9" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="75" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C10" s="76" t="s">
         <v>139</v>
@@ -8143,7 +8152,7 @@
         <v>139</v>
       </c>
       <c r="G10" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
@@ -8158,7 +8167,7 @@
         <v>128</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -8179,32 +8188,32 @@
     </row>
     <row r="15" spans="1:7" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -8212,22 +8221,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -8235,32 +8244,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="67" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -8268,47 +8277,47 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="78" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -8318,27 +8327,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -8369,12 +8378,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -8449,13 +8458,13 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="K5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="L5" s="72" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="29.25" customHeight="1">
@@ -8463,7 +8472,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C6" s="71" t="s">
         <v>25</v>
@@ -8489,13 +8498,13 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="K6" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="L6" s="72" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -8503,7 +8512,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>31</v>
@@ -8528,10 +8537,10 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="K7" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -8539,7 +8548,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>31</v>
@@ -8551,7 +8560,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G8" s="57">
         <v>40</v>
@@ -8564,10 +8573,10 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="K8" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -8575,7 +8584,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>34</v>
@@ -8600,10 +8609,10 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="K9" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -8611,13 +8620,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
@@ -8636,10 +8645,10 @@
         <v>10.7</v>
       </c>
       <c r="J10" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K10" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -8647,7 +8656,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>40</v>
@@ -8672,10 +8681,10 @@
         <v>5.8</v>
       </c>
       <c r="J11" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="K11" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -8683,13 +8692,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="80" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E12" s="28">
         <v>3</v>
@@ -8708,10 +8717,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K12" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -8719,7 +8728,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -8744,16 +8753,16 @@
         <v>6.7</v>
       </c>
       <c r="J13" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="K13" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="76.5" customHeight="1">
       <c r="A14" s="12"/>
       <c r="D14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E14">
         <f>SUM(E5:E13)</f>
@@ -8770,72 +8779,72 @@
     </row>
     <row r="16" spans="1:13" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -8866,12 +8875,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -8946,10 +8955,10 @@
         <v>3.5</v>
       </c>
       <c r="J5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="K5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -8957,13 +8966,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
@@ -8982,13 +8991,13 @@
         <v>12.7</v>
       </c>
       <c r="J6" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="K6" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="L6" s="57" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -8996,7 +9005,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="93" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>14</v>
@@ -9021,10 +9030,10 @@
         <v>12.7</v>
       </c>
       <c r="J7" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="K7" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -9057,13 +9066,13 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J8" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="K8" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="L8" s="57" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="29.25" customHeight="1">
@@ -9071,13 +9080,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -9096,10 +9105,10 @@
         <v>5.8</v>
       </c>
       <c r="J9" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="K9" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9107,13 +9116,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -9132,10 +9141,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="K10" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -9143,7 +9152,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>12</v>
@@ -9168,13 +9177,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="K11" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="L11" s="57" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -9182,7 +9191,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>12</v>
@@ -9207,10 +9216,10 @@
         <v>7.3</v>
       </c>
       <c r="J12" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="K12" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
@@ -9218,13 +9227,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
       </c>
       <c r="D13" s="80" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E13" s="28">
         <v>3</v>
@@ -9243,10 +9252,10 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="K13" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -9254,7 +9263,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -9279,10 +9288,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="K14" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1">
@@ -9315,17 +9324,17 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="K15" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="23.25" customHeight="1">
       <c r="A16" s="11"/>
       <c r="C16" s="92"/>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E16">
         <f>SUM(E5:E15)</f>
@@ -9341,112 +9350,112 @@
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="67" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -9477,12 +9486,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -9531,13 +9540,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="72" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C5" s="71" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="79" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E5" s="71">
         <v>4</v>
@@ -9556,10 +9565,10 @@
         <v>10.7</v>
       </c>
       <c r="J5" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="K5" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -9567,7 +9576,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>27</v>
@@ -9592,10 +9601,10 @@
         <v>6.7</v>
       </c>
       <c r="J6" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="K6" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -9603,13 +9612,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
@@ -9628,10 +9637,10 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="K7" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -9639,7 +9648,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>29</v>
@@ -9664,10 +9673,10 @@
         <v>6.7</v>
       </c>
       <c r="J8" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="K8" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -9675,13 +9684,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -9700,10 +9709,10 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="K9" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9711,13 +9720,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -9736,10 +9745,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="K10" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -9747,19 +9756,19 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
       </c>
       <c r="D11" s="80" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G11">
         <v>40</v>
@@ -9772,10 +9781,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="K11" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -9783,7 +9792,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
@@ -9795,7 +9804,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G12">
         <v>60</v>
@@ -9808,10 +9817,10 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="K12" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
@@ -9819,7 +9828,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
@@ -9831,7 +9840,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G13">
         <v>40</v>
@@ -9844,10 +9853,10 @@
         <v>10.7</v>
       </c>
       <c r="J13" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="K13" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
@@ -9855,7 +9864,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C14" s="91" t="s">
         <v>48</v>
@@ -9867,7 +9876,7 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G14">
         <v>40</v>
@@ -9880,16 +9889,16 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="K14" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="25.5" customHeight="1">
       <c r="A15" s="11"/>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E15">
         <f>SUM(E5:E14)</f>
@@ -9902,72 +9911,72 @@
     </row>
     <row r="16" spans="1:13" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -9998,12 +10007,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -10078,13 +10087,13 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="K5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="L5" s="72" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -10092,13 +10101,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E6" s="7">
         <v>5</v>
@@ -10117,10 +10126,10 @@
         <v>15.8</v>
       </c>
       <c r="J6" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="K6" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10128,7 +10137,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>9</v>
@@ -10140,7 +10149,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G7" s="57">
         <v>40</v>
@@ -10153,10 +10162,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J7" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="K7" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10164,7 +10173,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="93" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>14</v>
@@ -10189,10 +10198,10 @@
         <v>12.7</v>
       </c>
       <c r="J8" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="K8" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -10200,7 +10209,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="93" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>14</v>
@@ -10225,10 +10234,10 @@
         <v>10.7</v>
       </c>
       <c r="J9" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="K9" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10236,7 +10245,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>44</v>
@@ -10261,10 +10270,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="K10" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10278,7 +10287,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="80" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -10297,15 +10306,15 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="K11" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="D12" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E12">
         <f>SUM(E5:E11)</f>
@@ -10332,27 +10341,27 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="C27" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
   </sheetData>
@@ -10374,166 +10383,166 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D5" s="73" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>139</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="83" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B13" s="84" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C13" s="84" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D13" s="83" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B14" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C14" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D14" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -10544,22 +10553,22 @@
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
@@ -10567,137 +10576,137 @@
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
       <c r="A23" s="67" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -10762,12 +10771,12 @@
         <v>140</v>
       </c>
       <c r="E5" s="20">
-        <f>D1_당기기A!$E$16</f>
+        <f>D1_당기기A!$E$17</f>
         <v>35</v>
       </c>
       <c r="F5" s="20" t="str">
-        <f>"약 "&amp;D1_당기기A!$I$16&amp;"분"</f>
-        <v>약 78분</v>
+        <f>"약 "&amp;D1_당기기A!$I$17&amp;"분"</f>
+        <v>약 76분</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
@@ -10848,12 +10857,12 @@
         <v>153</v>
       </c>
       <c r="E9" s="20">
-        <f>D5_당기기B!$E$16</f>
-        <v>36</v>
+        <f>D5_당기기B!$E$17</f>
+        <v>39</v>
       </c>
       <c r="F9" s="20" t="str">
-        <f>"약 "&amp;D5_당기기B!$I$16&amp;"분"</f>
-        <v>약 75분</v>
+        <f>"약 "&amp;D5_당기기B!$I$17&amp;"분"</f>
+        <v>약 80분</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
@@ -10949,11 +10958,11 @@
       <c r="D14" s="28"/>
       <c r="E14" s="27">
         <f>SUM(E5:E13)</f>
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F14" t="str">
-        <f>"약 "&amp;(D1_당기기A!$I$16+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$16+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)&amp;"분 ("&amp;INT((D1_당기기A!$I$16+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$16+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)/60)&amp;"시간 "&amp;MOD((D1_당기기A!$I$16+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$16+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18),60)&amp;"분)"</f>
-        <v>약 543분 (9시간 3분)</v>
+        <f>"약 "&amp;(D1_당기기A!$I$17+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$17+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)&amp;"분 ("&amp;INT((D1_당기기A!$I$17+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$17+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)/60)&amp;"시간 "&amp;MOD((D1_당기기A!$I$17+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$17+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18),60)&amp;"분)"</f>
+        <v>약 546분 (9시간 6분)</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.5" customHeight="1"/>
@@ -11282,17 +11291,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$51,"?")</f>
@@ -11301,41 +11310,41 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C6" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D6" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E6" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G6" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H6" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B7" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C7" t="s">
         <v>42</v>
@@ -11352,18 +11361,18 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H7" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B8" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
@@ -11380,18 +11389,18 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H8" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B9" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -11408,18 +11417,18 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B10" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
@@ -11436,15 +11445,15 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H10" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B11" t="s">
         <v>240</v>
@@ -11464,15 +11473,15 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H11" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B12" t="s">
         <v>90</v>
@@ -11492,18 +11501,18 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H12" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B13" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
@@ -11520,18 +11529,18 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H13" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C15" t="s">
         <v>44</v>
@@ -11548,18 +11557,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H15" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B16" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -11576,18 +11585,18 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H16" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B17" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C17" t="s">
         <v>44</v>
@@ -11604,15 +11613,15 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H17" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B18" t="s">
         <v>90</v>
@@ -11632,18 +11641,18 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H18" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B19" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
@@ -11660,18 +11669,18 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H19" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B20" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
@@ -11688,18 +11697,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G20" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H20" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B21" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -11716,18 +11725,18 @@
         <v>1.5</v>
       </c>
       <c r="G21" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H21" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B22" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
@@ -11744,18 +11753,18 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H22" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B23" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C23" t="s">
         <v>21</v>
@@ -11772,18 +11781,18 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H23" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B24" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
@@ -11800,18 +11809,18 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H24" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B25" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C25" t="s">
         <v>21</v>
@@ -11828,18 +11837,18 @@
         <v>1.5</v>
       </c>
       <c r="G25" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H25" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B26" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
@@ -11856,18 +11865,18 @@
         <v>1.32</v>
       </c>
       <c r="G26" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H26" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B27" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
@@ -11884,18 +11893,18 @@
         <v>0.99</v>
       </c>
       <c r="G27" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H27" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B28" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -11912,18 +11921,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H28" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B29" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
@@ -11940,15 +11949,15 @@
         <v>0.8</v>
       </c>
       <c r="G29" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H29" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B30" t="s">
         <v>88</v>
@@ -11968,15 +11977,15 @@
         <v>0.2</v>
       </c>
       <c r="G30" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H30" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B31" t="s">
         <v>240</v>
@@ -11996,18 +12005,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G31" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H31" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B32" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
@@ -12024,15 +12033,15 @@
         <v>0.8</v>
       </c>
       <c r="G32" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H32" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B33" t="s">
         <v>86</v>
@@ -12052,18 +12061,18 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H33" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B34" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C34" t="s">
         <v>23</v>
@@ -12080,18 +12089,18 @@
         <v>0.8</v>
       </c>
       <c r="G34" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H34" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B35" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
@@ -12108,15 +12117,15 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G35" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H35" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B36" t="s">
         <v>86</v>
@@ -12136,15 +12145,15 @@
         <v>2.5</v>
       </c>
       <c r="G36" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H36" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B37" t="s">
         <v>88</v>
@@ -12164,18 +12173,18 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H37" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B38" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C38" t="s">
         <v>36</v>
@@ -12192,18 +12201,18 @@
         <v>1.32</v>
       </c>
       <c r="G38" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H38" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B39" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C39" t="s">
         <v>34</v>
@@ -12220,15 +12229,15 @@
         <v>1.5</v>
       </c>
       <c r="G39" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H39" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B40" t="s">
         <v>88</v>
@@ -12248,15 +12257,15 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H40" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B41" t="s">
         <v>86</v>
@@ -12276,18 +12285,18 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H41" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B42" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C42" t="s">
         <v>50</v>
@@ -12304,18 +12313,18 @@
         <v>0.8</v>
       </c>
       <c r="G42" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H42" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B43" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C43" t="s">
         <v>46</v>
@@ -12332,18 +12341,18 @@
         <v>0.99</v>
       </c>
       <c r="G43" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H43" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B44" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C44" t="s">
         <v>46</v>
@@ -12360,15 +12369,15 @@
         <v>0.99</v>
       </c>
       <c r="G44" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H44" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B45" t="s">
         <v>90</v>
@@ -12388,18 +12397,18 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H45" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B46" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -12416,15 +12425,15 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H46" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B47" t="s">
         <v>88</v>
@@ -12444,15 +12453,15 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H47" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B48" t="s">
         <v>86</v>
@@ -12472,18 +12481,18 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H48" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B49" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C49" t="s">
         <v>40</v>
@@ -12500,18 +12509,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H49" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B50" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -12528,18 +12537,18 @@
         <v>0.8</v>
       </c>
       <c r="G50" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H50" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B51" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C51" t="s">
         <v>25</v>
@@ -12556,10 +12565,10 @@
         <v>0.8</v>
       </c>
       <c r="G51" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H51" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
   </sheetData>
@@ -12585,12 +12594,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -12613,7 +12622,7 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -12637,10 +12646,10 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="G5" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -12671,10 +12680,10 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="G6" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -12698,13 +12707,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="G7" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="H7" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -12732,10 +12741,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="G8" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -12759,10 +12768,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="G9" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -12786,10 +12795,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="G10" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -12813,10 +12822,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="G11" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -12840,10 +12849,10 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="G12" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -12867,10 +12876,10 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="G13" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -12894,10 +12903,10 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="G14" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -12921,13 +12930,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="G15" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="H15" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -12955,10 +12964,10 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="G16" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -12982,10 +12991,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="G17" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -13009,10 +13018,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="G18" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -13036,10 +13045,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="G19" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -13063,10 +13072,10 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="G20" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -13090,10 +13099,10 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="G21" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -13117,10 +13126,10 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="G22" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -13144,10 +13153,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="G23" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -13171,10 +13180,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="G24" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -13197,62 +13206,62 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
     </row>
   </sheetData>
@@ -13263,7 +13272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -13368,7 +13377,7 @@
         <v>155</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I15" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I16" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
         <v>12.7</v>
       </c>
       <c r="J6" s="21" t="s">
@@ -13690,74 +13699,111 @@
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
       <c r="A15" s="20">
-        <v>9</v>
-      </c>
-      <c r="B15" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="85" t="s">
         <v>279</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="20">
-        <v>20</v>
+      <c r="D15" s="20" t="s">
+        <v>250</v>
       </c>
       <c r="E15" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="G15" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H15" s="26">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I15" s="26">
         <f t="shared" si="0"/>
-        <v>13.5</v>
-      </c>
-      <c r="J15" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="L15" s="90" t="s">
         <v>281</v>
       </c>
-      <c r="K15" s="36" t="s">
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1">
+      <c r="A16" s="20">
+        <v>11</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="L15" s="36" t="s">
+      <c r="C16" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="20">
+        <v>20</v>
+      </c>
+      <c r="E16" s="20">
+        <v>3</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1">
-      <c r="D16" s="37" t="s">
+      <c r="G16" s="26">
+        <v>45</v>
+      </c>
+      <c r="H16" s="26">
+        <v>90</v>
+      </c>
+      <c r="I16" s="26">
+        <f t="shared" si="0"/>
+        <v>6.8</v>
+      </c>
+      <c r="J16" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="E16" s="38">
-        <f>SUM(E6:E15)</f>
+      <c r="K16" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="L16" s="36" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="15" customHeight="1">
+      <c r="D17" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="E17" s="38">
+        <f>SUM(E6:E16)</f>
         <v>35</v>
       </c>
-      <c r="I16">
-        <f>ROUND(SUM(I6:I15),0)</f>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="36"/>
-    </row>
-    <row r="34" spans="10:10">
-      <c r="J34" t="s">
-        <v>285</v>
+      <c r="I17">
+        <f>ROUND(SUM(I6:I16),0)</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" s="36"/>
+    </row>
+    <row r="35" spans="10:10">
+      <c r="J35" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="34" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N15">
+  <conditionalFormatting sqref="A6:N16">
     <cfRule type="expression" dxfId="8" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
+  <conditionalFormatting sqref="B27">
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>$E26=0</formula>
+      <formula>$E27=0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -13787,17 +13833,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
@@ -13805,7 +13851,7 @@
         <v>230</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>135</v>
@@ -13873,27 +13919,27 @@
     </row>
     <row r="11" spans="1:3" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.5" customHeight="1">
       <c r="A14" s="31" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" customHeight="1">
       <c r="A15" s="31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.5" customHeight="1">
       <c r="A16" s="31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1">
@@ -13950,7 +13996,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C20" s="42" t="s">
         <v>12</v>
@@ -13976,16 +14022,16 @@
         <v>17.5</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K20" s="41" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="L20" s="41" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1">
@@ -13993,13 +14039,13 @@
         <v>2</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E21" s="20">
         <v>4</v>
@@ -14021,10 +14067,10 @@
         <v>44</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L21" s="36" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M21" s="26" t="s">
         <v>244</v>
@@ -14035,7 +14081,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>9</v>
@@ -14047,7 +14093,7 @@
         <v>7</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G22" s="26">
         <v>40</v>
@@ -14061,10 +14107,10 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="16.5" customHeight="1">
@@ -14072,7 +14118,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C23" s="45" t="s">
         <v>12</v>
@@ -14098,10 +14144,10 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
@@ -14109,7 +14155,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>27</v>
@@ -14135,10 +14181,10 @@
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="21" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
@@ -14146,7 +14192,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C25" s="45" t="s">
         <v>29</v>
@@ -14173,7 +14219,7 @@
       <c r="J25" s="21"/>
       <c r="K25" s="21"/>
       <c r="L25" s="90" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
@@ -14187,7 +14233,7 @@
         <v>42</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E26" s="20">
         <v>3</v>
@@ -14209,15 +14255,15 @@
         <v>46</v>
       </c>
       <c r="K26" s="21" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="D27" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E27" s="27">
         <f>SUM(E20:E26)</f>
@@ -14262,17 +14308,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -14280,7 +14326,7 @@
         <v>230</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>135</v>
@@ -14348,7 +14394,7 @@
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
@@ -14405,7 +14451,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>31</v>
@@ -14431,16 +14477,16 @@
         <v>19</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K15" s="41" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L15" s="41" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M15" s="40" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -14448,7 +14494,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>31</v>
@@ -14476,10 +14522,10 @@
         <v>36</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="16.5" customHeight="1">
@@ -14499,7 +14545,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G17" s="26">
         <v>90</v>
@@ -14512,13 +14558,13 @@
         <v>12</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.5" customHeight="1">
@@ -14526,7 +14572,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>34</v>
@@ -14538,7 +14584,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G18" s="26">
         <v>40</v>
@@ -14552,10 +14598,10 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="16.5" customHeight="1">
@@ -14563,7 +14609,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>50</v>
@@ -14589,13 +14635,13 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N19" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="16.5" customHeight="1">
@@ -14603,7 +14649,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>38</v>
@@ -14629,13 +14675,13 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L20" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="N20" t="s">
         <v>343</v>
-      </c>
-      <c r="N20" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1">
@@ -14669,10 +14715,10 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1">
@@ -14680,7 +14726,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="85" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>48</v>
@@ -14706,15 +14752,15 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1">
       <c r="D23" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E23" s="27">
         <f>SUM(E15:E22)</f>
@@ -14744,7 +14790,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -14761,17 +14807,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="33" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
@@ -14828,7 +14874,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>14</v>
@@ -14849,17 +14895,17 @@
         <v>150</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I15" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I16" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
         <v>12.7</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" customHeight="1">
@@ -14867,7 +14913,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>14</v>
@@ -14892,13 +14938,13 @@
         <v>12.7</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" customHeight="1">
@@ -14906,7 +14952,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>21</v>
@@ -14931,13 +14977,13 @@
         <v>6.7</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1">
@@ -14945,7 +14991,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>29</v>
@@ -14957,7 +15003,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G9" s="26">
         <v>40</v>
@@ -14970,13 +15016,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1">
@@ -14984,7 +15030,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>42</v>
@@ -15012,10 +15058,10 @@
         <v>46</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
@@ -15023,7 +15069,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>46</v>
@@ -15049,10 +15095,10 @@
       </c>
       <c r="J11" s="21"/>
       <c r="K11" s="21" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1">
@@ -15060,7 +15106,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>46</v>
@@ -15085,13 +15131,13 @@
         <v>7.3</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
@@ -15099,7 +15145,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>17</v>
@@ -15111,7 +15157,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G13" s="26">
         <v>40</v>
@@ -15124,13 +15170,13 @@
         <v>6.5</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
@@ -15138,13 +15184,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="95" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E14" s="20">
         <v>3</v>
@@ -15164,30 +15210,30 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16.5" customHeight="1">
       <c r="A15" s="20">
-        <v>9</v>
-      </c>
-      <c r="B15" s="89" t="s">
-        <v>385</v>
+        <v>10</v>
+      </c>
+      <c r="B15" s="95" t="s">
+        <v>279</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="20">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>250</v>
       </c>
       <c r="E15" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="G15" s="26">
         <v>40</v>
@@ -15197,35 +15243,72 @@
       </c>
       <c r="I15" s="26">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>386</v>
+        <v>280</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>387</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
-      <c r="D16" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E16" s="27">
-        <f>SUM(E6:E15)</f>
-        <v>36</v>
-      </c>
-      <c r="I16">
-        <f>ROUND(SUM(I6:I15),0)</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="87"/>
+      <c r="A16" s="20">
+        <v>11</v>
+      </c>
+      <c r="B16" s="89" t="s">
+        <v>388</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="20">
+        <v>15</v>
+      </c>
+      <c r="E16" s="20">
+        <v>6</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="G16" s="26">
+        <v>40</v>
+      </c>
+      <c r="H16" s="26">
+        <v>60</v>
+      </c>
+      <c r="I16" s="26">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="15" customHeight="1">
+      <c r="D17" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E17" s="27">
+        <f>SUM(E6:E16)</f>
+        <v>39</v>
+      </c>
+      <c r="I17">
+        <f>ROUND(SUM(I6:I16),0)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="87"/>
     </row>
   </sheetData>
   <phoneticPr fontId="34" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N15">
+  <conditionalFormatting sqref="A6:N16">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
@@ -15254,17 +15337,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
@@ -15272,7 +15355,7 @@
         <v>230</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>135</v>
@@ -15340,27 +15423,27 @@
     </row>
     <row r="11" spans="1:3" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.5" customHeight="1">
       <c r="A14" s="31" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" customHeight="1">
       <c r="A15" s="31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.5" customHeight="1">
       <c r="A16" s="31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1">
@@ -15417,7 +15500,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C20" s="42" t="s">
         <v>25</v>
@@ -15443,16 +15526,16 @@
         <v>10.5</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K20" s="41" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L20" s="41" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1">
@@ -15460,7 +15543,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>25</v>
@@ -15472,7 +15555,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G21" s="26">
         <v>40</v>
@@ -15485,13 +15568,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="16.5" customHeight="1">
@@ -15499,7 +15582,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>19</v>
@@ -15527,10 +15610,10 @@
         <v>252</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="16.5" customHeight="1">
@@ -15538,7 +15621,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>12</v>
@@ -15566,10 +15649,10 @@
         <v>44</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
@@ -15577,7 +15660,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>9</v>
@@ -15602,13 +15685,13 @@
         <v>19</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
@@ -15616,7 +15699,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>29</v>
@@ -15642,10 +15725,10 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
@@ -15653,7 +15736,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>27</v>
@@ -15665,7 +15748,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G26" s="26">
         <v>70</v>
@@ -15679,10 +15762,10 @@
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="16.5" customHeight="1">
@@ -15690,13 +15773,13 @@
         <v>8</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E27" s="20">
         <v>3</v>
@@ -15715,13 +15798,13 @@
         <v>5</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
@@ -15729,7 +15812,7 @@
         <v>9</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>44</v>
@@ -15755,15 +15838,15 @@
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L28" s="21" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="D29" s="46" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E29" s="47">
         <f>SUM(E20:E28)</f>
@@ -15776,42 +15859,42 @@
     </row>
     <row r="31" spans="1:14" ht="16.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="16.5" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -15845,17 +15928,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -15863,7 +15946,7 @@
         <v>230</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>135</v>
@@ -15931,7 +16014,7 @@
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
@@ -15988,7 +16071,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>23</v>
@@ -16014,13 +16097,13 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="K15" s="41" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L15" s="41" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -16028,7 +16111,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C16" s="42" t="s">
         <v>23</v>
@@ -16054,13 +16137,13 @@
         <v>7.2</v>
       </c>
       <c r="J16" s="41" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="K16" s="41" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L16" s="41" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1">
@@ -16068,7 +16151,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>36</v>
@@ -16096,10 +16179,10 @@
         <v>34</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1">
@@ -16107,7 +16190,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>34</v>
@@ -16132,13 +16215,13 @@
         <v>9.5</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="16.5" customHeight="1">
@@ -16146,7 +16229,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>34</v>
@@ -16172,10 +16255,10 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="16.5" customHeight="1">
@@ -16183,7 +16266,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>31</v>
@@ -16195,7 +16278,7 @@
         <v>4</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G20" s="26">
         <v>40</v>
@@ -16209,10 +16292,10 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1">
@@ -16220,7 +16303,7 @@
         <v>7</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>31</v>
@@ -16249,10 +16332,10 @@
         <v>36</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1">
@@ -16260,7 +16343,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>40</v>
@@ -16286,10 +16369,10 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1">
@@ -16297,7 +16380,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>38</v>
@@ -16309,7 +16392,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G23" s="26">
         <v>80</v>
@@ -16323,15 +16406,15 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1">
       <c r="D24" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E24" s="27">
         <f>SUM(E15:E23)</f>
@@ -16376,17 +16459,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1">
       <c r="A3" s="33" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
@@ -16443,7 +16526,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="85" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>27</v>
@@ -16469,10 +16552,10 @@
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" customHeight="1">
@@ -16480,7 +16563,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="85" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>27</v>
@@ -16506,10 +16589,10 @@
       </c>
       <c r="J7" s="21"/>
       <c r="K7" s="21" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" customHeight="1">
@@ -16517,7 +16600,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>27</v>
@@ -16545,10 +16628,10 @@
         <v>17</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1">
@@ -16556,7 +16639,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="85" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>29</v>
@@ -16581,13 +16664,13 @@
         <v>5.5</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1">
@@ -16595,7 +16678,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="85" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>29</v>
@@ -16621,10 +16704,10 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
@@ -16632,7 +16715,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>29</v>
@@ -16657,13 +16740,13 @@
         <v>6</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1">
@@ -16671,19 +16754,19 @@
         <v>7</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E12" s="20">
         <v>3</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G12" s="26">
         <v>40</v>
@@ -16696,13 +16779,13 @@
         <v>8</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
@@ -16710,13 +16793,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E13" s="20">
         <v>3</v>
@@ -16738,10 +16821,10 @@
         <v>29</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
@@ -16749,13 +16832,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E14" s="20">
         <v>5</v>
@@ -16775,13 +16858,13 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N14" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1">
@@ -16789,7 +16872,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>38</v>
@@ -16815,13 +16898,13 @@
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N15" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -16829,7 +16912,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>40</v>
@@ -16855,10 +16938,10 @@
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1">
@@ -16866,7 +16949,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>42</v>
@@ -16894,15 +16977,15 @@
         <v>46</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1">
       <c r="D18" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E18" s="27">
         <f>SUM(E6:E17)</f>
@@ -16916,112 +16999,112 @@
     <row r="19" spans="1:12" ht="16.5" customHeight="1"/>
     <row r="20" spans="1:12" ht="16.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1">
       <c r="A22" s="31" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1">
       <c r="A23" s="31" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="16.5" customHeight="1">
       <c r="A24" s="31" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="16.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="16.5" customHeight="1">
       <c r="A26" s="31" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
       <c r="A27" s="31" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="16.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="16.5" customHeight="1">
       <c r="A29" s="31" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="16.5" customHeight="1">
       <c r="A30" s="31" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="16.5" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1">
       <c r="A39" s="31" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="16.5" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="31" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_8일주기_v19.xlsx
+++ b/운동프로그램_8일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_BAE21613F2167B2C6F9578C214A933A87AF2AA1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_CF12CD07A5ABFD4729CDFAEDD5541AA3521BB6C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2034" uniqueCount="1024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1031">
   <si>
     <t>근육군별 주간 세트 — 검산</t>
   </si>
@@ -976,13 +976,28 @@
     <t>어시스트 딥스 머신 / 디클라인 덤벨 프레스 / 체스트 딥스 머신  https://www.youtube.com/shorts/1tQQKeAMwr0</t>
   </si>
   <si>
+    <t>인클라인 벤치프레스(스미스)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>삼두 · 삼각근(전면)</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 흉근 상부 7세트를 플라이 하나로 채우던 것을 프레스 3 + 플라이 4로 나눴다. 플라이는 늘어난 구간에서 벌리는 자극, 프레스는 중량을 실을 수 있는 축 — 상부 흉근을 한 종류로만 때리지 않는다. 복합관절이라 플라이 앞에 둔다. 벤치 본세트·딥스 뒤 세 번째 프레스이므로 중량은 6일차 인클라인 머신보다 낮게 잡고 시작한다.</t>
+  </si>
+  <si>
+    <t>인클라인 바벨 벤치프레스 / 인클라인 덤벨 프레스 / 인클라인 벤치프레스 머신</t>
+  </si>
+  <si>
     <t>인클라인 덤벨 플라이(혹은 벡덱플라이 머신으로)</t>
   </si>
   <si>
     <t>10~12</t>
   </si>
   <si>
-    <t>프레싱 뒤 고립. 늘어난 구간에서 멈추지 말고 부드럽게 [2026-09-04 4→7] 흉근 상부 보강(주당 7.0 → 10.1). 6일차 인클라인 머신과 함께 사이클당 2회.</t>
+    <t>프레싱 뒤 고립. 늘어난 구간에서 멈추지 말고 부드럽게 [2026-09-04 4→7] 흉근 상부 보강(주당 7.0 → 10.1). 6일차 인클라인 머신과 함께 사이클당 2회. [2026-09-04 7→4] 같은 날 인클라인 벤치프레스(스미스) 3세트를 새로 두면서 나눴다. 흉근 상부 직접 합계는 그대로다.</t>
   </si>
   <si>
     <t>케이블 크로스오버 (아래→위) / 펙덱 플라이 (등받이를 눕혀 인클라인 각으로) / 인클라인 머신 플라이</t>
@@ -1684,6 +1699,12 @@
     <t>프레스 중 삼두 신전</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>프레스 중 삼두 신전 — 인클라인 벤치프레스 머신(0.5)과 같은 등급 (2026-09-04 신설)</t>
+  </si>
+  <si>
     <t>D8_어깨</t>
   </si>
   <si>
@@ -1699,13 +1720,13 @@
     <t>벤치 중 전면삼각 능동 관여 — 수평 프레스의 전면삼각 비대 근거는 인클라인(0.5)만큼 확실하지 않다 (2026-09-04 0.5→0.33)</t>
   </si>
   <si>
+    <t>인클라인은 전면삼각 관여 큼 — 인클라인 벤치프레스 머신(0.5)과 같은 등급 (2026-09-04 신설)</t>
+  </si>
+  <si>
     <t>인클라인은 전면삼각 관여 큼</t>
   </si>
   <si>
     <t>오버헤드 프레스 측면삼각 관여 — 5×5 본세트라 측면삼각이 자기 실패 근처에 못 간다 (2026-09-04 0.5→0.33)</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
   <si>
     <t>오버헤드 프레스 측면삼각 관여 — 밀리터리 본세트(0.33)와 같은 등급. 이전에는 이 행이 없었는데 제외 사유였던 '직접 전면삼각 분류'는 밀리터리에도 똑같이 해당돼 성립하지 않았다. 보조 종목이라 오히려 실패에 더 가깝다 (2026-09-04 신설)</t>
@@ -4674,7 +4695,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4688,12 +4709,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="101" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B2" s="100"/>
       <c r="C2" s="100"/>
@@ -4705,16 +4726,16 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F3">
-        <f ca="1">COUNTIF($E$7:$E$68,"?")</f>
+        <f ca="1">COUNTIF($E$7:$E$70,"?")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.75" customHeight="1">
       <c r="A4" s="99" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B4" s="100"/>
       <c r="C4" s="100"/>
@@ -4726,33 +4747,33 @@
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="48" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="G6" s="48" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B7" s="49" t="s">
         <v>240</v>
@@ -4772,15 +4793,15 @@
         <v>2</v>
       </c>
       <c r="G7" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H7" s="54" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="49" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B8" s="49" t="s">
         <v>245</v>
@@ -4800,18 +4821,18 @@
         <v>2</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H8" s="54" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="49" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C9" s="49" t="s">
         <v>42</v>
@@ -4828,18 +4849,18 @@
         <v>2</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H9" s="54" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="49" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C10" s="49" t="s">
         <v>42</v>
@@ -4856,15 +4877,15 @@
         <v>2</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="49" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B11" s="49" t="s">
         <v>298</v>
@@ -4884,15 +4905,15 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H11" s="54" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="49" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B12" s="49" t="s">
         <v>303</v>
@@ -4912,18 +4933,18 @@
         <v>2</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="49" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C13" s="49" t="s">
         <v>44</v>
@@ -4940,18 +4961,18 @@
         <v>0.99</v>
       </c>
       <c r="G13" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H13" s="54" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="49" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C14" s="49" t="s">
         <v>44</v>
@@ -4968,46 +4989,46 @@
         <v>3</v>
       </c>
       <c r="G14" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="49" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>494</v>
+        <v>307</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D15" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E15" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="G15" s="53" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H15" s="54" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="49" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>370</v>
+        <v>499</v>
       </c>
       <c r="C16" s="49" t="s">
         <v>46</v>
@@ -5024,108 +5045,108 @@
         <v>1.32</v>
       </c>
       <c r="G16" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="49" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C17" s="49" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="50">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E17" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="G17" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H17" s="54" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="49" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>298</v>
+        <v>385</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D18" s="50">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="E18" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.6500000000000001</v>
+        <v>0</v>
       </c>
       <c r="G18" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="49" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>408</v>
+        <v>298</v>
       </c>
       <c r="C19" s="49" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E19" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G19" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H19" s="54" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="49" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>394</v>
+        <v>307</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D20" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E20" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5133,46 +5154,46 @@
       </c>
       <c r="F20" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G20" s="53" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="49" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D21" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E21" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F21" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
-      </c>
-      <c r="G21" s="56" t="s">
-        <v>550</v>
+        <v>3</v>
+      </c>
+      <c r="G21" s="53" t="s">
+        <v>537</v>
       </c>
       <c r="H21" s="54" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="49" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B22" s="49" t="s">
         <v>399</v>
@@ -5191,25 +5212,25 @@
         <f t="shared" ca="1" si="1"/>
         <v>0.99</v>
       </c>
-      <c r="G22" s="56" t="s">
-        <v>550</v>
+      <c r="G22" s="53" t="s">
+        <v>537</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="49" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>255</v>
+        <v>404</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E23" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5217,27 +5238,27 @@
       </c>
       <c r="F23" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="G23" s="53" t="s">
-        <v>532</v>
+        <v>0.99</v>
+      </c>
+      <c r="G23" s="56" t="s">
+        <v>548</v>
       </c>
       <c r="H23" s="54" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="49" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D24" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E24" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5245,21 +5266,21 @@
       </c>
       <c r="F24" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.99</v>
       </c>
       <c r="G24" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H24" s="54" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="49" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>417</v>
+        <v>255</v>
       </c>
       <c r="C25" s="49" t="s">
         <v>29</v>
@@ -5276,74 +5297,74 @@
         <v>1.5</v>
       </c>
       <c r="G25" s="53" t="s">
-        <v>532</v>
-      </c>
-      <c r="H25" s="55" t="s">
-        <v>555</v>
+        <v>537</v>
+      </c>
+      <c r="H25" s="54" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="49" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>355</v>
+        <v>422</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D26" s="50">
         <v>0.5</v>
       </c>
       <c r="E26" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="G26" s="53" t="s">
-        <v>532</v>
+        <v>1.5</v>
+      </c>
+      <c r="G26" s="56" t="s">
+        <v>548</v>
       </c>
       <c r="H26" s="54" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="49" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>359</v>
+        <v>422</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D27" s="50">
         <v>0.5</v>
       </c>
       <c r="E27" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G27" s="53" t="s">
-        <v>532</v>
-      </c>
-      <c r="H27" s="54" t="s">
-        <v>556</v>
+        <v>537</v>
+      </c>
+      <c r="H27" s="55" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="49" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C28" s="49" t="s">
         <v>21</v>
@@ -5353,31 +5374,31 @@
       </c>
       <c r="E28" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F28" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H28" s="54" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="49" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>441</v>
+        <v>364</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D29" s="50">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E29" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5385,111 +5406,111 @@
       </c>
       <c r="F29" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="G29" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H29" s="54" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="49" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>435</v>
+        <v>371</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D30" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E30" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="G30" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H30" s="54" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="49" t="s">
-        <v>531</v>
+        <v>564</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>282</v>
+        <v>446</v>
       </c>
       <c r="C31" s="49" t="s">
         <v>34</v>
       </c>
       <c r="D31" s="50">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E31" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="G31" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H31" s="54" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="49" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>325</v>
+        <v>440</v>
       </c>
       <c r="C32" s="49" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D32" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E32" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F32" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5</v>
+        <v>0.33</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="49" t="s">
-        <v>561</v>
+        <v>536</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="C33" s="49" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D33" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E33" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5497,21 +5518,21 @@
       </c>
       <c r="F33" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G33" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H33" s="54" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="49" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>435</v>
+        <v>330</v>
       </c>
       <c r="C34" s="49" t="s">
         <v>36</v>
@@ -5521,31 +5542,31 @@
       </c>
       <c r="E34" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F34" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G34" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H34" s="54" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="49" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>444</v>
+        <v>335</v>
       </c>
       <c r="C35" s="49" t="s">
         <v>36</v>
       </c>
       <c r="D35" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E35" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5553,21 +5574,21 @@
       </c>
       <c r="F35" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.99</v>
       </c>
       <c r="G35" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H35" s="54" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="49" t="s">
-        <v>531</v>
+        <v>564</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>282</v>
+        <v>440</v>
       </c>
       <c r="C36" s="49" t="s">
         <v>36</v>
@@ -5577,59 +5598,59 @@
       </c>
       <c r="E36" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G36" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H36" s="54" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="49" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>325</v>
+        <v>449</v>
       </c>
       <c r="C37" s="49" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D37" s="50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E37" s="51">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G37" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H37" s="54" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
       <c r="A38" s="49" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>380</v>
+        <v>282</v>
       </c>
       <c r="C38" s="49" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D38" s="50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E38" s="51">
         <f t="shared" ca="1" si="0"/>
@@ -5637,55 +5658,55 @@
       </c>
       <c r="F38" s="52">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G38" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H38" s="54" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="49" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>444</v>
+        <v>330</v>
       </c>
       <c r="C39" s="49" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E39" s="51">
-        <f t="shared" ref="E39:E68" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
-        <v>3</v>
+        <f t="shared" ref="E39:E70" ca="1" si="2">IFERROR(INDEX(INDIRECT("'"&amp;$A39&amp;"'!$E$1:$E$45"),MATCH($B39,INDIRECT("'"&amp;$A39&amp;"'!$B$1:$B$45"),0)),"?")</f>
+        <v>5</v>
       </c>
       <c r="F39" s="52">
         <f t="shared" ref="F39:F70" ca="1" si="3">IF(ISNUMBER(E39),$D39*E39,0)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G39" s="53" t="s">
-        <v>532</v>
-      </c>
-      <c r="H39" s="55" t="s">
-        <v>569</v>
+        <v>537</v>
+      </c>
+      <c r="H39" s="54" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="49" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>32</v>
+        <v>385</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D40" s="50">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E40" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -5693,27 +5714,27 @@
       </c>
       <c r="F40" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G40" s="53" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H40" s="54" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="49" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>32</v>
+        <v>449</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D41" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E41" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -5721,105 +5742,105 @@
       </c>
       <c r="F41" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G41" s="53" t="s">
-        <v>532</v>
-      </c>
-      <c r="H41" s="54" t="s">
-        <v>571</v>
+        <v>537</v>
+      </c>
+      <c r="H41" s="55" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
       <c r="A42" s="49" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>435</v>
+        <v>32</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D42" s="50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E42" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="56" t="s">
-        <v>550</v>
+        <v>1.5</v>
+      </c>
+      <c r="G42" s="53" t="s">
+        <v>537</v>
       </c>
       <c r="H42" s="54" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="49" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>325</v>
+        <v>32</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D43" s="50">
         <v>0.33</v>
       </c>
       <c r="E43" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F43" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6500000000000001</v>
-      </c>
-      <c r="G43" s="56" t="s">
-        <v>550</v>
+        <v>0.99</v>
+      </c>
+      <c r="G43" s="53" t="s">
+        <v>537</v>
       </c>
       <c r="H43" s="54" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
       <c r="A44" s="49" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>330</v>
+        <v>440</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D44" s="50">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="E44" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="G44" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="49" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>32</v>
+        <v>330</v>
       </c>
       <c r="C45" s="49" t="s">
         <v>50</v>
@@ -5829,137 +5850,137 @@
       </c>
       <c r="E45" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F45" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G45" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H45" s="54" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
       <c r="A46" s="49" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D46" s="50">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E46" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F46" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G46" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H46" s="54" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="49" t="s">
-        <v>540</v>
+        <v>568</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>408</v>
+        <v>32</v>
       </c>
       <c r="C47" s="49" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D47" s="50">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E47" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F47" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G47" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H47" s="54" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="49" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>355</v>
+        <v>298</v>
       </c>
       <c r="C48" s="49" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D48" s="50">
         <v>0</v>
       </c>
       <c r="E48" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F48" s="52">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="G48" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H48" s="54" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="49" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="C49" s="49" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D49" s="50">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E49" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F49" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G49" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H49" s="54" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="49" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>435</v>
+        <v>360</v>
       </c>
       <c r="C50" s="49" t="s">
         <v>17</v>
@@ -5969,171 +5990,171 @@
       </c>
       <c r="E50" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50" s="52">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
       <c r="G50" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H50" s="54" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="49" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>240</v>
+        <v>399</v>
       </c>
       <c r="C51" s="49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D51" s="50">
         <v>0.2</v>
       </c>
       <c r="E51" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G51" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H51" s="54" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="49" t="s">
-        <v>535</v>
+        <v>564</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>355</v>
+        <v>440</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D52" s="50">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E52" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F52" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G52" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H52" s="54" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="49" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>317</v>
+        <v>240</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D53" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E53" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6500000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G53" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H53" s="54" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="49" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D54" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E54" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G54" s="56" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="H54" s="54" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="49" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="B55" s="49" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D55" s="50">
         <v>0.33</v>
       </c>
       <c r="E55" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F55" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="G55" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H55" s="54" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="49" t="s">
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>399</v>
+        <v>335</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D56" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E56" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -6141,27 +6162,27 @@
       </c>
       <c r="F56" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>0.99</v>
       </c>
       <c r="G56" s="56" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="H56" s="54" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="49" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>399</v>
+        <v>335</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D57" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E57" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -6169,21 +6190,21 @@
       </c>
       <c r="F57" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5</v>
+        <v>0.99</v>
       </c>
       <c r="G57" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H57" s="54" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="49" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B58" s="49" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C58" s="49" t="s">
         <v>44</v>
@@ -6200,52 +6221,52 @@
         <v>1.5</v>
       </c>
       <c r="G58" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H58" s="54" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="49" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>303</v>
+        <v>404</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D59" s="50">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E59" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G59" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H59" s="54" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
       <c r="A60" s="49" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D60" s="50">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E60" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -6253,24 +6274,24 @@
       </c>
       <c r="F60" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>1.5</v>
       </c>
       <c r="G60" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H60" s="54" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="49" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B61" s="49" t="s">
-        <v>376</v>
+        <v>303</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D61" s="50">
         <v>0.2</v>
@@ -6284,21 +6305,21 @@
         <v>0.8</v>
       </c>
       <c r="G61" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H61" s="54" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="49" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B62" s="49" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D62" s="50">
         <v>0.33</v>
@@ -6312,46 +6333,46 @@
         <v>0.99</v>
       </c>
       <c r="G62" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H62" s="54" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1">
       <c r="A63" s="49" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B63" s="49" t="s">
-        <v>471</v>
+        <v>381</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D63" s="50">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E63" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G63" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H63" s="54" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15" customHeight="1">
       <c r="A64" s="49" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>479</v>
+        <v>371</v>
       </c>
       <c r="C64" s="49" t="s">
         <v>21</v>
@@ -6368,21 +6389,21 @@
         <v>0.99</v>
       </c>
       <c r="G64" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H64" s="54" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15" customHeight="1">
       <c r="A65" s="49" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="B65" s="49" t="s">
-        <v>260</v>
+        <v>476</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D65" s="50">
         <v>0.33</v>
@@ -6396,80 +6417,80 @@
         <v>0.99</v>
       </c>
       <c r="G65" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H65" s="54" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15" customHeight="1">
       <c r="A66" s="49" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B66" s="49" t="s">
-        <v>439</v>
+        <v>484</v>
       </c>
       <c r="C66" s="49" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D66" s="50">
         <v>0.33</v>
       </c>
       <c r="E66" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.66</v>
-      </c>
-      <c r="G66" s="53" t="s">
-        <v>532</v>
+        <v>0.99</v>
+      </c>
+      <c r="G66" s="56" t="s">
+        <v>548</v>
       </c>
       <c r="H66" s="54" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15" customHeight="1">
       <c r="A67" s="49" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="B67" s="49" t="s">
-        <v>439</v>
+        <v>260</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D67" s="50">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="E67" s="51">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" s="52">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G67" s="53" t="s">
-        <v>532</v>
+        <v>0.99</v>
+      </c>
+      <c r="G67" s="56" t="s">
+        <v>548</v>
       </c>
       <c r="H67" s="54" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15" customHeight="1">
       <c r="A68" s="49" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B68" s="49" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C68" s="49" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D68" s="50">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="E68" s="51">
         <f t="shared" ca="1" si="2"/>
@@ -6477,13 +6498,69 @@
       </c>
       <c r="F68" s="52">
         <f t="shared" ca="1" si="3"/>
+        <v>0.66</v>
+      </c>
+      <c r="G68" s="53" t="s">
+        <v>537</v>
+      </c>
+      <c r="H68" s="54" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="49" t="s">
+        <v>564</v>
+      </c>
+      <c r="B69" s="49" t="s">
+        <v>444</v>
+      </c>
+      <c r="C69" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="E69" s="51">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F69" s="52">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G69" s="53" t="s">
+        <v>537</v>
+      </c>
+      <c r="H69" s="54" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="49" t="s">
+        <v>564</v>
+      </c>
+      <c r="B70" s="49" t="s">
+        <v>444</v>
+      </c>
+      <c r="C70" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="50">
         <v>0</v>
       </c>
-      <c r="G68" s="53" t="s">
-        <v>550</v>
-      </c>
-      <c r="H68" s="54" t="s">
-        <v>598</v>
+      <c r="E70" s="51">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F70" s="52">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G70" s="53" t="s">
+        <v>548</v>
+      </c>
+      <c r="H70" s="54" t="s">
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -6551,7 +6628,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A5),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A5),0.5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="59">
@@ -6590,7 +6667,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A6),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A6),0.5)</f>
         <v>0</v>
       </c>
       <c r="D6" s="59">
@@ -6619,7 +6696,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A7),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A7),0.5)</f>
         <v>0</v>
       </c>
       <c r="D7" s="59">
@@ -6654,7 +6731,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A8),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A8),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D8" s="59">
@@ -6683,7 +6760,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A9),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A9),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D9" s="59">
@@ -6712,7 +6789,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A10),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A10),0.5)</f>
         <v>7.5</v>
       </c>
       <c r="D10" s="59">
@@ -6741,7 +6818,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A11),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A11),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D11" s="59">
@@ -6770,12 +6847,12 @@
         <v>9</v>
       </c>
       <c r="C12" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A12),0.5)</f>
-        <v>6.5</v>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A12),0.5)</f>
+        <v>8</v>
       </c>
       <c r="D12" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="E12" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6787,7 +6864,7 @@
       <c r="G12" s="61"/>
       <c r="J12" s="59">
         <f t="shared" ca="1" si="2"/>
-        <v>12.1</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1">
@@ -6799,7 +6876,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A13),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A13),0.5)</f>
         <v>3</v>
       </c>
       <c r="D13" s="59">
@@ -6828,7 +6905,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A14),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A14),0.5)</f>
         <v>4.5</v>
       </c>
       <c r="D14" s="59">
@@ -6858,7 +6935,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A15),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A15),0.5)</f>
         <v>1.5</v>
       </c>
       <c r="D15" s="59">
@@ -6893,7 +6970,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A16),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A16),0.5)</f>
         <v>3.5</v>
       </c>
       <c r="D16" s="59">
@@ -6922,7 +6999,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A17),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A17),0.5)</f>
         <v>9</v>
       </c>
       <c r="D17" s="59">
@@ -6957,7 +7034,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A18),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A18),0.5)</f>
         <v>1</v>
       </c>
       <c r="D18" s="59">
@@ -6986,7 +7063,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="58">
-        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A19),0.5)</f>
+        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A19),0.5)</f>
         <v>0</v>
       </c>
       <c r="D19" s="59">
@@ -7015,7 +7092,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A20),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A20),0.5)</f>
         <v>9</v>
       </c>
       <c r="D20" s="59">
@@ -7044,12 +7121,12 @@
         <v>8</v>
       </c>
       <c r="C21" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A21),0.5)</f>
-        <v>12</v>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A21),0.5)</f>
+        <v>13.5</v>
       </c>
       <c r="D21" s="59">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>21.5</v>
       </c>
       <c r="E21" s="7" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7061,7 +7138,7 @@
       <c r="G21" s="61"/>
       <c r="J21" s="59">
         <f t="shared" ca="1" si="2"/>
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.5" customHeight="1">
@@ -7073,7 +7150,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A22),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A22),0.5)</f>
         <v>3.5</v>
       </c>
       <c r="D22" s="59">
@@ -7102,7 +7179,7 @@
         <v>13</v>
       </c>
       <c r="C23" s="58">
-        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A23),0.5)</f>
+        <f>MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A23),0.5)</f>
         <v>0</v>
       </c>
       <c r="D23" s="59">
@@ -7131,7 +7208,7 @@
         <v>9</v>
       </c>
       <c r="C24" s="58">
-        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$68,간접계수맵!$C$7:$C$68,$A24),0.5)</f>
+        <f ca="1">MROUND(SUMIFS(간접계수맵!$F$7:$F$70,간접계수맵!$C$7:$C$70,$A24),0.5)</f>
         <v>4.5</v>
       </c>
       <c r="D24" s="59">
@@ -7162,13 +7239,13 @@
       <c r="C25" s="65"/>
       <c r="D25" s="66">
         <f ca="1">SUM(D5:D24)</f>
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E25" s="65"/>
       <c r="F25" s="65"/>
       <c r="J25" s="66">
         <f t="shared" ca="1" si="2"/>
-        <v>237.2</v>
+        <v>239.6</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1">
@@ -7324,50 +7401,50 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="A5" s="68" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="67" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
       <c r="A6" s="68" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
       <c r="A7" s="68" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -7376,13 +7453,13 @@
     </row>
     <row r="8" spans="1:11" ht="84" customHeight="1">
       <c r="A8" s="68" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="67" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
@@ -7390,31 +7467,31 @@
         <v>115</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>236</v>
@@ -7748,17 +7825,17 @@
     </row>
     <row r="23" spans="1:11" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="120" customHeight="1">
@@ -7766,27 +7843,27 @@
     </row>
     <row r="27" spans="1:11" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -7807,23 +7884,23 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="70" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -7831,21 +7908,21 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -7853,80 +7930,80 @@
         <v>23</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="71" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="71" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C10" s="73" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -7934,47 +8011,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -8000,31 +8077,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="74" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>135</v>
@@ -8033,111 +8110,111 @@
         <v>136</v>
       </c>
       <c r="G5" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="75" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="E6" s="75">
         <f>복귀_평일A_가슴!$E$12</f>
         <v>28</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="G6" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$15</f>
         <v>35</v>
       </c>
       <c r="F7" s="73" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="G7" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="75" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="E8" s="75">
         <f>복귀_토_하체!$E$14</f>
         <v>32</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="G8" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="75" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="E9" s="75">
         <f>복귀_일_등!$E$16</f>
         <v>33</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="G9" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="75" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="C10" s="76" t="s">
         <v>139</v>
@@ -8152,7 +8229,7 @@
         <v>139</v>
       </c>
       <c r="G10" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
@@ -8167,7 +8244,7 @@
         <v>128</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -8188,32 +8265,32 @@
     </row>
     <row r="15" spans="1:7" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -8221,22 +8298,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -8244,32 +8321,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="67" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -8277,47 +8354,47 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="78" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -8327,27 +8404,27 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -8378,12 +8455,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -8458,10 +8535,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="K5" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="L5" s="72" t="s">
         <v>302</v>
@@ -8472,7 +8549,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="C6" s="71" t="s">
         <v>25</v>
@@ -8498,13 +8575,13 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="K6" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="L6" s="72" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -8512,7 +8589,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>31</v>
@@ -8537,10 +8614,10 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="K7" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -8548,7 +8625,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>31</v>
@@ -8560,7 +8637,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G8" s="57">
         <v>40</v>
@@ -8573,10 +8650,10 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="K8" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -8584,7 +8661,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>34</v>
@@ -8609,10 +8686,10 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="K9" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -8620,13 +8697,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
@@ -8645,10 +8722,10 @@
         <v>10.7</v>
       </c>
       <c r="J10" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="K10" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -8656,7 +8733,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>40</v>
@@ -8681,10 +8758,10 @@
         <v>5.8</v>
       </c>
       <c r="J11" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="K11" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -8692,13 +8769,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="80" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="E12" s="28">
         <v>3</v>
@@ -8717,10 +8794,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="K12" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -8728,7 +8805,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -8753,10 +8830,10 @@
         <v>6.7</v>
       </c>
       <c r="J13" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="K13" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="76.5" customHeight="1">
@@ -8779,72 +8856,72 @@
     </row>
     <row r="16" spans="1:13" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -8875,12 +8952,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -8955,10 +9032,10 @@
         <v>3.5</v>
       </c>
       <c r="J5" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="K5" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -8966,13 +9043,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
@@ -8991,13 +9068,13 @@
         <v>12.7</v>
       </c>
       <c r="J6" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="K6" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="L6" s="57" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -9005,7 +9082,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="93" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>14</v>
@@ -9030,10 +9107,10 @@
         <v>12.7</v>
       </c>
       <c r="J7" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="K7" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -9066,13 +9143,13 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J8" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="K8" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="L8" s="57" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="29.25" customHeight="1">
@@ -9080,13 +9157,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -9105,10 +9182,10 @@
         <v>5.8</v>
       </c>
       <c r="J9" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="K9" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9116,13 +9193,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -9141,10 +9218,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="K10" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -9177,13 +9254,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="K11" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="L11" s="57" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -9191,7 +9268,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>12</v>
@@ -9216,10 +9293,10 @@
         <v>7.3</v>
       </c>
       <c r="J12" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="K12" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
@@ -9227,13 +9304,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
       </c>
       <c r="D13" s="80" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E13" s="28">
         <v>3</v>
@@ -9252,10 +9329,10 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="K13" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -9263,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -9288,10 +9365,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="K14" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1">
@@ -9324,10 +9401,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="K15" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="23.25" customHeight="1">
@@ -9350,112 +9427,112 @@
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="67" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
     </row>
   </sheetData>
@@ -9486,12 +9563,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -9540,13 +9617,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="72" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C5" s="71" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="79" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E5" s="71">
         <v>4</v>
@@ -9565,10 +9642,10 @@
         <v>10.7</v>
       </c>
       <c r="J5" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="K5" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -9576,7 +9653,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>27</v>
@@ -9601,10 +9678,10 @@
         <v>6.7</v>
       </c>
       <c r="J6" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="K6" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -9612,13 +9689,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
@@ -9637,10 +9714,10 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="K7" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -9648,7 +9725,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>29</v>
@@ -9673,10 +9750,10 @@
         <v>6.7</v>
       </c>
       <c r="J8" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="K8" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -9684,13 +9761,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -9709,10 +9786,10 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="K9" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9720,13 +9797,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
@@ -9745,10 +9822,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="K10" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -9756,19 +9833,19 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
       </c>
       <c r="D11" s="80" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G11">
         <v>40</v>
@@ -9781,10 +9858,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="K11" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -9792,7 +9869,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
@@ -9804,7 +9881,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="G12">
         <v>60</v>
@@ -9817,10 +9894,10 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="K12" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
@@ -9828,7 +9905,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
@@ -9840,7 +9917,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G13">
         <v>40</v>
@@ -9853,10 +9930,10 @@
         <v>10.7</v>
       </c>
       <c r="J13" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="K13" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
@@ -9864,7 +9941,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C14" s="91" t="s">
         <v>48</v>
@@ -9889,10 +9966,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="K14" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="25.5" customHeight="1">
@@ -9911,72 +9988,72 @@
     </row>
     <row r="16" spans="1:13" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -10007,12 +10084,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
@@ -10087,10 +10164,10 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="K5" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="L5" s="72" t="s">
         <v>302</v>
@@ -10101,13 +10178,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="E6" s="7">
         <v>5</v>
@@ -10126,10 +10203,10 @@
         <v>15.8</v>
       </c>
       <c r="J6" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="K6" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10137,7 +10214,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>9</v>
@@ -10149,7 +10226,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G7" s="57">
         <v>40</v>
@@ -10162,10 +10239,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J7" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="K7" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10173,7 +10250,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="93" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>14</v>
@@ -10198,10 +10275,10 @@
         <v>12.7</v>
       </c>
       <c r="J8" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="K8" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -10209,7 +10286,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="93" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>14</v>
@@ -10234,10 +10311,10 @@
         <v>10.7</v>
       </c>
       <c r="J9" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="K9" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10245,7 +10322,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>44</v>
@@ -10270,10 +10347,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="K10" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10287,7 +10364,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="80" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
@@ -10306,10 +10383,10 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="K11" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -10341,27 +10418,27 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="C27" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
     </row>
   </sheetData>
@@ -10383,166 +10460,166 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="D5" s="73" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>139</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="83" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="B13" s="84" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="C13" s="84" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="D13" s="83" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="B14" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="C14" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="D14" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -10553,22 +10630,22 @@
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="67" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
@@ -10576,137 +10653,137 @@
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
       <c r="A23" s="67" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
     </row>
   </sheetData>
@@ -10793,12 +10870,12 @@
         <v>144</v>
       </c>
       <c r="E6" s="20">
-        <f>D2_밀기A!$E$27</f>
+        <f>D2_밀기A!$E$28</f>
         <v>33</v>
       </c>
       <c r="F6" s="20" t="str">
-        <f>"약 "&amp;D2_밀기A!$I$27&amp;"분"</f>
-        <v>약 80분</v>
+        <f>"약 "&amp;D2_밀기A!$I$28&amp;"분"</f>
+        <v>약 82분</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
@@ -10961,8 +11038,8 @@
         <v>235</v>
       </c>
       <c r="F14" t="str">
-        <f>"약 "&amp;(D1_당기기A!$I$17+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$17+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)&amp;"분 ("&amp;INT((D1_당기기A!$I$17+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$17+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)/60)&amp;"시간 "&amp;MOD((D1_당기기A!$I$17+D2_밀기A!$I$27+D3_하체A!$I$23+D5_당기기B!$I$17+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18),60)&amp;"분)"</f>
-        <v>약 546분 (9시간 6분)</v>
+        <f>"약 "&amp;(D1_당기기A!$I$17+D2_밀기A!$I$28+D3_하체A!$I$23+D5_당기기B!$I$17+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)&amp;"분 ("&amp;INT((D1_당기기A!$I$17+D2_밀기A!$I$28+D3_하체A!$I$23+D5_당기기B!$I$17+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18)/60)&amp;"시간 "&amp;MOD((D1_당기기A!$I$17+D2_밀기A!$I$28+D3_하체A!$I$23+D5_당기기B!$I$17+D6_밀기B!$I$29+D7_하체B!$I$24+D8_어깨!$I$18),60)&amp;"분)"</f>
+        <v>약 548분 (9시간 8분)</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.5" customHeight="1"/>
@@ -11291,17 +11368,17 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F3">
         <f ca="1">COUNTIF($E$7:$E$51,"?")</f>
@@ -11310,41 +11387,41 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="B6" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C6" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D6" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="E6" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="F6" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="G6" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="H6" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B7" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C7" t="s">
         <v>42</v>
@@ -11361,18 +11438,18 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H7" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B8" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
@@ -11389,18 +11466,18 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H8" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B9" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -11417,18 +11494,18 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H9" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B10" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
@@ -11445,15 +11522,15 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H10" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B11" t="s">
         <v>240</v>
@@ -11473,15 +11550,15 @@
         <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H11" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B12" t="s">
         <v>90</v>
@@ -11501,18 +11578,18 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H12" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B13" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C13" t="s">
         <v>44</v>
@@ -11529,18 +11606,18 @@
         <v>2.5</v>
       </c>
       <c r="G13" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H13" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="B15" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C15" t="s">
         <v>44</v>
@@ -11557,18 +11634,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H15" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B16" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="C16" t="s">
         <v>44</v>
@@ -11585,15 +11662,15 @@
         <v>1.5</v>
       </c>
       <c r="G16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H16" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B17" t="s">
         <v>303</v>
@@ -11613,15 +11690,15 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H17" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B18" t="s">
         <v>90</v>
@@ -11641,18 +11718,18 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H18" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B19" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
@@ -11669,15 +11746,15 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H19" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B20" t="s">
         <v>303</v>
@@ -11697,18 +11774,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G20" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H20" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B21" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -11725,18 +11802,18 @@
         <v>1.5</v>
       </c>
       <c r="G21" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H21" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B22" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
@@ -11753,18 +11830,18 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H22" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B23" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C23" t="s">
         <v>21</v>
@@ -11781,18 +11858,18 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H23" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B24" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
@@ -11809,18 +11886,18 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H24" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="B25" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C25" t="s">
         <v>21</v>
@@ -11837,18 +11914,18 @@
         <v>1.5</v>
       </c>
       <c r="G25" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H25" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="B26" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
@@ -11865,18 +11942,18 @@
         <v>1.32</v>
       </c>
       <c r="G26" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H26" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B27" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
@@ -11893,18 +11970,18 @@
         <v>0.99</v>
       </c>
       <c r="G27" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H27" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B28" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -11921,18 +11998,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H28" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B29" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
@@ -11949,15 +12026,15 @@
         <v>0.8</v>
       </c>
       <c r="G29" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H29" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B30" t="s">
         <v>88</v>
@@ -11977,15 +12054,15 @@
         <v>0.2</v>
       </c>
       <c r="G30" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H30" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B31" t="s">
         <v>240</v>
@@ -12005,18 +12082,18 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G31" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H31" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B32" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
@@ -12033,15 +12110,15 @@
         <v>0.8</v>
       </c>
       <c r="G32" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H32" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B33" t="s">
         <v>86</v>
@@ -12061,18 +12138,18 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H33" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B34" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C34" t="s">
         <v>23</v>
@@ -12089,18 +12166,18 @@
         <v>0.8</v>
       </c>
       <c r="G34" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H34" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B35" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
@@ -12117,15 +12194,15 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="G35" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H35" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B36" t="s">
         <v>86</v>
@@ -12145,15 +12222,15 @@
         <v>2.5</v>
       </c>
       <c r="G36" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H36" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B37" t="s">
         <v>88</v>
@@ -12173,18 +12250,18 @@
         <v>0.5</v>
       </c>
       <c r="G37" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H37" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B38" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C38" t="s">
         <v>36</v>
@@ -12201,18 +12278,18 @@
         <v>1.32</v>
       </c>
       <c r="G38" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H38" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="B39" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C39" t="s">
         <v>34</v>
@@ -12229,15 +12306,15 @@
         <v>1.5</v>
       </c>
       <c r="G39" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H39" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B40" t="s">
         <v>88</v>
@@ -12257,15 +12334,15 @@
         <v>0.5</v>
       </c>
       <c r="G40" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H40" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B41" t="s">
         <v>86</v>
@@ -12285,18 +12362,18 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H41" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B42" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C42" t="s">
         <v>50</v>
@@ -12313,18 +12390,18 @@
         <v>0.8</v>
       </c>
       <c r="G42" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H42" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="B43" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C43" t="s">
         <v>46</v>
@@ -12341,18 +12418,18 @@
         <v>0.99</v>
       </c>
       <c r="G43" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H43" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B44" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C44" t="s">
         <v>46</v>
@@ -12369,15 +12446,15 @@
         <v>0.99</v>
       </c>
       <c r="G44" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H44" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B45" t="s">
         <v>90</v>
@@ -12397,18 +12474,18 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H45" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B46" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -12425,15 +12502,15 @@
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H46" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="B47" t="s">
         <v>88</v>
@@ -12453,15 +12530,15 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H47" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B48" t="s">
         <v>86</v>
@@ -12481,18 +12558,18 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H48" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B49" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C49" t="s">
         <v>40</v>
@@ -12509,18 +12586,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H49" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B50" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -12537,18 +12614,18 @@
         <v>0.8</v>
       </c>
       <c r="G50" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H50" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="B51" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="C51" t="s">
         <v>25</v>
@@ -12565,10 +12642,10 @@
         <v>0.8</v>
       </c>
       <c r="G51" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H51" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
     </row>
   </sheetData>
@@ -12594,12 +12671,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -12622,7 +12699,7 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -12646,10 +12723,10 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="G5" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -12680,10 +12757,10 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="G6" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -12707,13 +12784,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="G7" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="H7" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -12741,10 +12818,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="G8" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -12768,10 +12845,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="G9" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -12795,10 +12872,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="G10" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -12822,10 +12899,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="G11" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -12849,10 +12926,10 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="G12" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -12876,10 +12953,10 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="G13" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -12903,10 +12980,10 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="G14" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -12930,13 +13007,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="G15" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="H15" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -12964,10 +13041,10 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="G16" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -12991,10 +13068,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="G17" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -13018,10 +13095,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="G18" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -13045,10 +13122,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="G19" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -13072,10 +13149,10 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="G20" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -13099,10 +13176,10 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="G21" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -13126,10 +13203,10 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="G22" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -13153,10 +13230,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="G23" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -13180,10 +13257,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="G24" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -13206,62 +13283,62 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
@@ -13816,7 +13893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -14018,7 +14095,7 @@
         <v>180</v>
       </c>
       <c r="I20" s="40">
-        <f t="shared" ref="I20:I26" si="0">IF(E20=0,0,ROUND(E20*(G20+H20)/60,1))</f>
+        <f t="shared" ref="I20:I27" si="0">IF(E20=0,0,ROUND(E20*(G20+H20)/60,1))</f>
         <v>17.5</v>
       </c>
       <c r="J20" s="41" t="s">
@@ -14080,74 +14157,77 @@
       <c r="A22" s="20">
         <v>3</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="21" t="s">
         <v>307</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="26">
-        <v>8</v>
+      <c r="D22" s="44" t="s">
+        <v>308</v>
       </c>
       <c r="E22" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>308</v>
+        <v>246</v>
       </c>
       <c r="G22" s="26">
         <v>40</v>
       </c>
       <c r="H22" s="26">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="I22" s="26">
         <f t="shared" si="0"/>
-        <v>16.899999999999999</v>
-      </c>
-      <c r="J22" s="21"/>
+        <v>9.5</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>309</v>
+      </c>
       <c r="K22" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="L22" s="21" t="s">
         <v>310</v>
       </c>
+      <c r="L22" s="36" t="s">
+        <v>311</v>
+      </c>
+      <c r="M22" s="96"/>
     </row>
     <row r="23" spans="1:14" ht="16.5" customHeight="1">
       <c r="A23" s="20">
         <v>4</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>12</v>
+      <c r="B23" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>9</v>
       </c>
       <c r="D23" s="26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="G23" s="26">
         <v>40</v>
       </c>
       <c r="H23" s="26">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I23" s="26">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
@@ -14155,36 +14235,36 @@
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>27</v>
+        <v>316</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>12</v>
       </c>
       <c r="D24" s="26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E24" s="20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="G24" s="26">
         <v>40</v>
       </c>
       <c r="H24" s="26">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I24" s="26">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="21" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
@@ -14192,16 +14272,16 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>29</v>
+        <v>319</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>27</v>
       </c>
       <c r="D25" s="26">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E25" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="26" t="s">
         <v>256</v>
@@ -14214,12 +14294,14 @@
       </c>
       <c r="I25" s="26">
         <f t="shared" si="0"/>
-        <v>9.1999999999999993</v>
+        <v>11</v>
       </c>
       <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="90" t="s">
-        <v>318</v>
+      <c r="K25" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
@@ -14227,19 +14309,19 @@
         <v>7</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>260</v>
+        <v>322</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>319</v>
+        <v>29</v>
+      </c>
+      <c r="D26" s="26">
+        <v>20</v>
       </c>
       <c r="E26" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="G26" s="26">
         <v>40</v>
@@ -14249,40 +14331,75 @@
       </c>
       <c r="I26" s="26">
         <f t="shared" si="0"/>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="90" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A27" s="20">
+        <v>8</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="E27" s="20">
+        <v>3</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="G27" s="26">
+        <v>40</v>
+      </c>
+      <c r="H27" s="26">
+        <v>70</v>
+      </c>
+      <c r="I27" s="26">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="J26" s="21" t="s">
+      <c r="J27" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K26" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="L26" s="21" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="D27" s="3" t="s">
+      <c r="K27" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="D28" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="E27" s="27">
-        <f>SUM(E20:E26)</f>
+      <c r="E28" s="27">
+        <f>SUM(E20:E27)</f>
         <v>33</v>
       </c>
-      <c r="I27">
-        <f>ROUND(SUM(I20:I26),0)</f>
-        <v>80</v>
+      <c r="I28">
+        <f>ROUND(SUM(I20:I27),0)</f>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="34" type="noConversion"/>
-  <conditionalFormatting sqref="A20:N26">
+  <conditionalFormatting sqref="A20:N27">
     <cfRule type="expression" dxfId="6" priority="1">
       <formula>$E20=0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="L25" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="L26" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -14308,17 +14425,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -14451,7 +14568,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>31</v>
@@ -14477,16 +14594,16 @@
         <v>19</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K15" s="41" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="L15" s="41" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="M15" s="40" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -14494,7 +14611,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>31</v>
@@ -14522,10 +14639,10 @@
         <v>36</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="16.5" customHeight="1">
@@ -14545,7 +14662,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G17" s="26">
         <v>90</v>
@@ -14558,13 +14675,13 @@
         <v>12</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.5" customHeight="1">
@@ -14572,7 +14689,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>34</v>
@@ -14584,7 +14701,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G18" s="26">
         <v>40</v>
@@ -14598,10 +14715,10 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="16.5" customHeight="1">
@@ -14609,7 +14726,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>50</v>
@@ -14635,13 +14752,13 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="N19" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="16.5" customHeight="1">
@@ -14649,7 +14766,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>38</v>
@@ -14675,13 +14792,13 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="N20" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1">
@@ -14715,10 +14832,10 @@
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1">
@@ -14726,7 +14843,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="85" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>48</v>
@@ -14752,10 +14869,10 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1">
@@ -14807,17 +14924,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="33" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
@@ -14874,7 +14991,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>14</v>
@@ -14899,13 +15016,13 @@
         <v>12.7</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" customHeight="1">
@@ -14913,7 +15030,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>14</v>
@@ -14938,13 +15055,13 @@
         <v>12.7</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" customHeight="1">
@@ -14952,7 +15069,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>21</v>
@@ -14977,13 +15094,13 @@
         <v>6.7</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1">
@@ -14991,7 +15108,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>29</v>
@@ -15016,13 +15133,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1">
@@ -15030,7 +15147,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>42</v>
@@ -15058,10 +15175,10 @@
         <v>46</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
@@ -15069,7 +15186,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>46</v>
@@ -15095,10 +15212,10 @@
       </c>
       <c r="J11" s="21"/>
       <c r="K11" s="21" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1">
@@ -15106,7 +15223,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>46</v>
@@ -15131,13 +15248,13 @@
         <v>7.3</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
@@ -15145,7 +15262,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>17</v>
@@ -15157,7 +15274,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G13" s="26">
         <v>40</v>
@@ -15170,13 +15287,13 @@
         <v>6.5</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
@@ -15184,13 +15301,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="95" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E14" s="20">
         <v>3</v>
@@ -15210,10 +15327,10 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1">
@@ -15258,7 +15375,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="89" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>48</v>
@@ -15284,10 +15401,10 @@
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="15" customHeight="1">
@@ -15337,17 +15454,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
@@ -15500,7 +15617,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C20" s="42" t="s">
         <v>25</v>
@@ -15526,16 +15643,16 @@
         <v>10.5</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="K20" s="41" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="L20" s="41" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1">
@@ -15543,7 +15660,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>25</v>
@@ -15568,13 +15685,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="16.5" customHeight="1">
@@ -15582,7 +15699,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>19</v>
@@ -15610,10 +15727,10 @@
         <v>252</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="16.5" customHeight="1">
@@ -15621,7 +15738,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>12</v>
@@ -15649,10 +15766,10 @@
         <v>44</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
@@ -15660,7 +15777,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>9</v>
@@ -15688,10 +15805,10 @@
         <v>299</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
@@ -15699,7 +15816,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>29</v>
@@ -15725,10 +15842,10 @@
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
@@ -15736,7 +15853,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>27</v>
@@ -15748,7 +15865,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G26" s="26">
         <v>70</v>
@@ -15762,10 +15879,10 @@
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="16.5" customHeight="1">
@@ -15773,13 +15890,13 @@
         <v>8</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E27" s="20">
         <v>3</v>
@@ -15798,13 +15915,13 @@
         <v>5</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
@@ -15812,7 +15929,7 @@
         <v>9</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>44</v>
@@ -15838,10 +15955,10 @@
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="L28" s="21" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
@@ -15859,42 +15976,42 @@
     </row>
     <row r="31" spans="1:14" ht="16.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="16.5" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -15928,17 +16045,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
@@ -16071,7 +16188,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C15" s="42" t="s">
         <v>23</v>
@@ -16097,13 +16214,13 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K15" s="41" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L15" s="41" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -16111,7 +16228,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C16" s="42" t="s">
         <v>23</v>
@@ -16137,13 +16254,13 @@
         <v>7.2</v>
       </c>
       <c r="J16" s="41" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K16" s="41" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="L16" s="41" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1">
@@ -16151,7 +16268,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>36</v>
@@ -16179,10 +16296,10 @@
         <v>34</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1">
@@ -16190,7 +16307,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>34</v>
@@ -16215,13 +16332,13 @@
         <v>9.5</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="16.5" customHeight="1">
@@ -16229,7 +16346,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>34</v>
@@ -16255,10 +16372,10 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="16.5" customHeight="1">
@@ -16266,7 +16383,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>31</v>
@@ -16278,7 +16395,7 @@
         <v>4</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G20" s="26">
         <v>40</v>
@@ -16292,10 +16409,10 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1">
@@ -16303,7 +16420,7 @@
         <v>7</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>31</v>
@@ -16332,10 +16449,10 @@
         <v>36</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1">
@@ -16343,7 +16460,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>40</v>
@@ -16369,10 +16486,10 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1">
@@ -16380,7 +16497,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>38</v>
@@ -16392,7 +16509,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="G23" s="26">
         <v>80</v>
@@ -16406,10 +16523,10 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1">
@@ -16459,17 +16576,17 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1">
       <c r="A3" s="33" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
@@ -16526,7 +16643,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="85" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>27</v>
@@ -16552,10 +16669,10 @@
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" customHeight="1">
@@ -16563,7 +16680,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="85" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>27</v>
@@ -16589,10 +16706,10 @@
       </c>
       <c r="J7" s="21"/>
       <c r="K7" s="21" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" customHeight="1">
@@ -16600,7 +16717,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>27</v>
@@ -16628,10 +16745,10 @@
         <v>17</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1">
@@ -16639,7 +16756,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="85" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>29</v>
@@ -16664,13 +16781,13 @@
         <v>5.5</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1">
@@ -16678,7 +16795,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="85" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>29</v>
@@ -16704,10 +16821,10 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
@@ -16715,7 +16832,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>29</v>
@@ -16740,13 +16857,13 @@
         <v>6</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1">
@@ -16754,13 +16871,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E12" s="20">
         <v>3</v>
@@ -16779,13 +16896,13 @@
         <v>8</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
@@ -16793,13 +16910,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E13" s="20">
         <v>3</v>
@@ -16821,10 +16938,10 @@
         <v>29</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
@@ -16832,13 +16949,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E14" s="20">
         <v>5</v>
@@ -16858,13 +16975,13 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="N14" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1">
@@ -16872,7 +16989,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>38</v>
@@ -16898,13 +17015,13 @@
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="N15" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -16912,7 +17029,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>40</v>
@@ -16938,10 +17055,10 @@
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1">
@@ -16949,7 +17066,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>42</v>
@@ -16977,10 +17094,10 @@
         <v>46</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1">
@@ -16999,112 +17116,112 @@
     <row r="19" spans="1:12" ht="16.5" customHeight="1"/>
     <row r="20" spans="1:12" ht="16.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1">
       <c r="A22" s="31" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1">
       <c r="A23" s="31" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="16.5" customHeight="1">
       <c r="A24" s="31" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="16.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="16.5" customHeight="1">
       <c r="A26" s="31" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
       <c r="A27" s="31" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="16.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="16.5" customHeight="1">
       <c r="A29" s="31" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="16.5" customHeight="1">
       <c r="A30" s="31" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="16.5" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1">
       <c r="A39" s="31" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="16.5" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="31" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/운동프로그램_8일주기_v19.xlsx
+++ b/운동프로그램_8일주기_v19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_8C360BA892AB3016F0F3AD1E5023462B0F970353" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_84D995457137F2192CD3C4D98F3BDA2391CCD4AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="1101">
   <si>
     <t>간접 세트 계수 맵 — 세트검산 간접 열(C)의 계산 원천</t>
   </si>
@@ -677,7 +677,7 @@
     <t>어깨·팔 A</t>
   </si>
   <si>
-    <t>삼각근(측면·후면) · 삼두 · 이두 · 전완 · 내전근 · 중둔근</t>
+    <t>삼각근(측면·후면) · 흉근 플라이 · 삼두 · 이두 · 전완 · 내전근 · 중둔근</t>
   </si>
   <si>
     <t>휴식</t>
@@ -686,7 +686,7 @@
     <t>당기기 B (수평)</t>
   </si>
   <si>
-    <t>광배 · 능형근 · 승모 · 이두</t>
+    <t>광배 · 능형근 · 승모 · 이두 · 종아리</t>
   </si>
   <si>
     <t>밀기 B (수직)</t>
@@ -710,7 +710,7 @@
     <t>어깨·팔 B</t>
   </si>
   <si>
-    <t>삼각근(측면·후면·전면) · 승모(하부) · 삼두 · 이두 · 전완 · 종아리</t>
+    <t>삼각근(측면·후면·전면) · 승모(하부) · 삼두 · 이두 · 전완 · 종아리 · 중둔근</t>
   </si>
   <si>
     <t>합계</t>
@@ -746,7 +746,10 @@
     <t>· 4훈련 · 휴식 · 4훈련 · 휴식. 어깨(옛 8일차 40세트)를 다른 세 패턴처럼 A/B로 나눠 4 · 9일차에 두고, 1 · 2 · 5 · 6일차의 삼두 · 이두 · 전완을 그쪽으로 옮겼다. 종목 12개 이동, 세트는 한 개도 안 늘고 안 줄었다 — 239 그대로.</t>
   </si>
   <si>
-    <t>· 세션이 27~32세트 · 57~80분으로 고르게 됐다. 9일 주기에서는 1일차 38 · 6일차 34(84분) · 8일차 40이었고 80분 넘는 날이 셋이었다. 이제 없다.</t>
+    <t>· 세션이 24~38세트 · 67~73분으로 고르게 됐다. 9일 주기에서는 1일차 38 · 6일차 34(84분) · 8일차 40이었고 80분 넘는 날이 셋이었다. 이제 없다.</t>
+  </si>
+  <si>
+    <t>· 시간 균등화(같은 날 추가): 디클라인 플라이(2일차) · 펙덱(7일차) → 4일차, 케이블 힙 외전(8일차) → 9일차, 스탠딩 카프(3일차) → 6일차. 4종목 13세트, 총량 불변. 분할 직후 57~80분이던 편차를 67~73분으로 좁혔다 — 남은 6분은 종목 하나 크기라 세트를 쪼개지 않는 한 더 못 좁힌다. 흉근이 2·4·7일차 셋으로 흩어졌고 종아리는 (1,6) 거울이 됐다.</t>
   </si>
   <si>
     <t>· 주당 환산 185.9 → 167.3. 볼륨을 뺀 게 아니라 같은 양을 하루 더 긴 달력에 편 것이다. 세트검산이 여러 부위를 '유지 미만'으로 띄우겠지만 그건 분모가 커진 산술이지 결핍이 아니다 — 총량 예산(세트검산 J2)이 239로 잠겨 있어 채워 넣을 수 없다.</t>
@@ -1163,6 +1166,135 @@
     <t>케이블 크로스오버 (아래→위) / 펙덱 플라이 (등받이를 눕혀 인클라인 각으로) / 인클라인 머신 플라이</t>
   </si>
   <si>
+    <t>레터럴 레이즈</t>
+  </si>
+  <si>
+    <t>덤벨은 아래 구간에 저항이 안 걸린다 — 원암 케이블(7일차)이 그 구간을 메운다</t>
+  </si>
+  <si>
+    <t>케이블 레터럴 레이즈 (전 구간 장력) / 레터럴 레이즈 머신 / 라잉 레터럴</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/Et70PVUQpDE</t>
+  </si>
+  <si>
+    <t>3일차 — 하체 A (무릎 지배)</t>
+  </si>
+  <si>
+    <t>스쿼트 · 레그프레스 중심. 8일차 하체 B(고관절 지배)와 5일 간격.</t>
+  </si>
+  <si>
+    <t>메인: 스쿼트</t>
+  </si>
+  <si>
+    <t>둔근·기립근</t>
+  </si>
+  <si>
+    <t>무릎 지배 메인. 데드(8일차)와 5일 간격이라 기립근이 회복된 상태에서 친다</t>
+  </si>
+  <si>
+    <t>스미스 스쿼트 / 핵 스쿼트 (대퇴사두 집중) / 프론트 스쿼트 / 벨트 스쿼트 (척추 부하 없음)</t>
+  </si>
+  <si>
+    <t>150/170/190/215/240</t>
+  </si>
+  <si>
+    <t>수/토 3+3 분할. 궤도 고정이라 대퇴사두가 확실히 한계까지 간다. 발판 위치는 중간</t>
+  </si>
+  <si>
+    <t>핵 스쿼트 / 레그 익스텐션 (완전 고립) / 프론트 스쿼트</t>
+  </si>
+  <si>
+    <t>10 (좌우)</t>
+  </si>
+  <si>
+    <t>대퇴사두·중둔근</t>
+  </si>
+  <si>
+    <t>한 다리 지지라 관상면 안정화가 함께 들어온다</t>
+  </si>
+  <si>
+    <t>덤벨 런지 / 워킹 런지 / 스텝업 / 리버스 런지 (무릎 부담 ↓)</t>
+  </si>
+  <si>
+    <t>레그 컬</t>
+  </si>
+  <si>
+    <t>무릎 굴곡. 8일차 RDL(고관절 신전)과 기능이 다르다 — 둘 다 필요</t>
+  </si>
+  <si>
+    <t>라잉 레그 컬 · 시티드 레그 컬 (시티드가 늘어난 구간을 더 씀) / 노르딕 햄 컬</t>
+  </si>
+  <si>
+    <t>이너 타이</t>
+  </si>
+  <si>
+    <t>내전근 직접 종목은 이것뿐. 스쿼트·레그프레스·불가리안이 간접 5.5를 채워 주므로 실질은 이미 하한 위다. [2026-09-04 — 아우터 타이와 슈퍼세트로 묶었다. 겸용 머신이라 패드만 뒤집으면 되어 전환이 10초다. 휴식 105 → 10초는 그 전환 시간이고, 라운드 간 휴식은 아우터 쪽 105초가 맡는다. 길항근 쌍이라 서로의 피로를 나눠 갖지 않으며, 각 근육 입장에서는 자기 세트 간격이 오히려 155초로 늘어난다]</t>
+  </si>
+  <si>
+    <t>와이드 스탠스 레그 프레스 / 코사크 스쿼트 / 케이블 힙 내전</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>아우터 타이 (힙 외전)</t>
+  </si>
+  <si>
+    <t>관상면 외전. [2026-09-04 부활 — v18에서 8일차로 보냈던 자리를 이너 타이와의 슈퍼세트로 되살렸다. 중둔근이 직접 3 · 간접 1.0으로 주당 환산 3.5, 프로그램 최하위였다. 여기 4세트로 주당 7.0 · 사이클당 2회(3일차·8일차, 간격 4일)가 된다. 8일차 케이블 힙 외전은 그대로 둔다 — 앉아서 고관절 굽힌 채(여기)와 서서 편 채(8일차)는 각도가 다르다. 반드시 양측 동시 머신으로 — 케이블 좌우 버전은 수행 80초라 40초짜리 이너와 라운드가 안 맞는다]</t>
+  </si>
+  <si>
+    <t>힙 어브덕션 머신 (겸용 머신이 없을 때) / 케이블 힙 외전 (좌우 — 슈퍼세트로는 부적합) / 밴드 몬스터 워크 / 사이드 라잉 힙 외전</t>
+  </si>
+  <si>
+    <t>앱휠 롤아웃</t>
+  </si>
+  <si>
+    <t>항신전. 다음날이 당기기 B라 브레이싱 손실이 문제되지 않는다</t>
+  </si>
+  <si>
+    <t>애브 롤아웃 / 사이드 플랭크 / 팔로프 프레스 (항회전)</t>
+  </si>
+  <si>
+    <t>4일차 — 어깨·팔 A</t>
+  </si>
+  <si>
+    <t>측면·후면 삼각근 + 흉근 플라이 + 삼두 · 이두 · 전완 + 내전근·중둔근. 약 70분. 4-1-4-1 전환으로 신설 — 옛 8일차 어깨 세션의 절반과 1·2일차의 팔, 시간 균등화로 2·7일차의 플라이가 여기로 왔다. 거울 슬롯은 9일차 어깨·팔 B.</t>
+  </si>
+  <si>
+    <t>웜업 — 케이블 외회전 2세트 × 12~15 (세트 카운트 제외): 매우 가볍게 2.5~5kg. 팔꿈치를 90도로 접어 옆구리에 붙이고 바깥으로만 회전. 대체: 밴드 외회전 / 아주 가벼운 페이스풀.</t>
+  </si>
+  <si>
+    <t>머신 레터럴 레이즈</t>
+  </si>
+  <si>
+    <t>궤도가 고정돼 반동이 안 들어간다. 중간 구간을 끝까지 쓴다. 어깨가 으쓱 따라 올라가면 승모가 대신 일하는 것 — 무게를 내린다.</t>
+  </si>
+  <si>
+    <t>덤벨 레터럴 (머신 없을 때 — 몸 옆이 아니라 살짝 앞) / 케이블 레터럴 양팔 크로스</t>
+  </si>
+  <si>
+    <t>레이즈 계열과 달리 팔꿈치를 굽힌 채 당기는 궤적이라 측면의 다른 섬유가 동원되고, 승모 상부가 같이 온다 (승모 상부는 사이클당 3세트로 하한 미달이라 이 겸용이 값을 한다). 그립은 어깨너비보다 넓게, 팔꿈치는 가슴 높이까지만 — 좁은 그립으로 턱까지 올리면 견봉하 공간이 좁아진다.</t>
+  </si>
+  <si>
+    <t>EZ바 와이드 업라이트 로우 / 스미스 업라이트 로우 / 케이블 Y 레이즈 (충돌이 느껴질 때)</t>
+  </si>
+  <si>
+    <t>중부승모·능형근</t>
+  </si>
+  <si>
+    <t>팔을 편 채 수평으로만 벌린다. 케이블이라 수축 지점에서도 장력이 유지된다. 팔꿈치가 어깨선을 크게 지나가면 후면 삼각근에서 능형근으로 넘어간다.</t>
+  </si>
+  <si>
+    <t>리버스 펙덱 (2일차와 같은 머신이면 그립만 바꿔 각도를 나눈다) / 벤트오버 케이블 크로스</t>
+  </si>
+  <si>
+    <t>팔꿈치를 어깨 높이로 벌린 채 당긴다. 4·5번이 팔을 편 수평 외전이라면 이쪽은 굽힌 채 당기기라 모멘트암과 동원 섬유가 다르다 — 한 세션에 후면 9세트를 넣으면서 자극이 겹치지 않게 하는 축이 이것이다. 팔꿈치가 몸통 옆으로 붙으면 광배 로우가 된다.</t>
+  </si>
+  <si>
+    <t>와이드 그립 시티드 케이블 로우 (팔꿈치 벌려) / 페이스풀 (외회전까지 포함) / 머신 로우 와이드 그립</t>
+  </si>
+  <si>
     <t>디클라인 케이블 플라이</t>
   </si>
   <si>
@@ -1172,85 +1304,160 @@
     <t>오버헤드 케이블 익스텐션 / 스컬크러셔 / 클로즈그립 벤치프레스 (중량 가능)</t>
   </si>
   <si>
-    <t>레터럴 레이즈</t>
-  </si>
-  <si>
-    <t>덤벨은 아래 구간에 저항이 안 걸린다 — 원암 케이블(7일차)이 그 구간을 메운다</t>
-  </si>
-  <si>
-    <t>케이블 레터럴 레이즈 (전 구간 장력) / 레터럴 레이즈 머신 / 라잉 레터럴</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/shorts/Et70PVUQpDE</t>
-  </si>
-  <si>
-    <t>3일차 — 하체 A (무릎 지배)</t>
-  </si>
-  <si>
-    <t>스쿼트 · 레그프레스 중심. 8일차 하체 B(고관절 지배)와 5일 간격.</t>
-  </si>
-  <si>
-    <t>메인: 스쿼트</t>
-  </si>
-  <si>
-    <t>둔근·기립근</t>
-  </si>
-  <si>
-    <t>무릎 지배 메인. 데드(8일차)와 5일 간격이라 기립근이 회복된 상태에서 친다</t>
-  </si>
-  <si>
-    <t>스미스 스쿼트 / 핵 스쿼트 (대퇴사두 집중) / 프론트 스쿼트 / 벨트 스쿼트 (척추 부하 없음)</t>
-  </si>
-  <si>
-    <t>150/170/190/215/240</t>
-  </si>
-  <si>
-    <t>수/토 3+3 분할. 궤도 고정이라 대퇴사두가 확실히 한계까지 간다. 발판 위치는 중간</t>
-  </si>
-  <si>
-    <t>핵 스쿼트 / 레그 익스텐션 (완전 고립) / 프론트 스쿼트</t>
-  </si>
-  <si>
-    <t>10 (좌우)</t>
-  </si>
-  <si>
-    <t>대퇴사두·중둔근</t>
-  </si>
-  <si>
-    <t>한 다리 지지라 관상면 안정화가 함께 들어온다</t>
-  </si>
-  <si>
-    <t>덤벨 런지 / 워킹 런지 / 스텝업 / 리버스 런지 (무릎 부담 ↓)</t>
-  </si>
-  <si>
-    <t>레그 컬</t>
-  </si>
-  <si>
-    <t>무릎 굴곡. 8일차 RDL(고관절 신전)과 기능이 다르다 — 둘 다 필요</t>
-  </si>
-  <si>
-    <t>라잉 레그 컬 · 시티드 레그 컬 (시티드가 늘어난 구간을 더 씀) / 노르딕 햄 컬</t>
-  </si>
-  <si>
-    <t>이너 타이</t>
-  </si>
-  <si>
-    <t>내전근 직접 종목은 이것뿐. 스쿼트·레그프레스·불가리안이 간접 5.5를 채워 주므로 실질은 이미 하한 위다. [2026-09-04 — 아우터 타이와 슈퍼세트로 묶었다. 겸용 머신이라 패드만 뒤집으면 되어 전환이 10초다. 휴식 105 → 10초는 그 전환 시간이고, 라운드 간 휴식은 아우터 쪽 105초가 맡는다. 길항근 쌍이라 서로의 피로를 나눠 갖지 않으며, 각 근육 입장에서는 자기 세트 간격이 오히려 155초로 늘어난다]</t>
-  </si>
-  <si>
-    <t>와이드 스탠스 레그 프레스 / 코사크 스쿼트 / 케이블 힙 내전</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>아우터 타이 (힙 외전)</t>
-  </si>
-  <si>
-    <t>관상면 외전. [2026-09-04 부활 — v18에서 8일차로 보냈던 자리를 이너 타이와의 슈퍼세트로 되살렸다. 중둔근이 직접 3 · 간접 1.0으로 주당 환산 3.5, 프로그램 최하위였다. 여기 4세트로 주당 7.0 · 사이클당 2회(3일차·8일차, 간격 4일)가 된다. 8일차 케이블 힙 외전은 그대로 둔다 — 앉아서 고관절 굽힌 채(여기)와 서서 편 채(8일차)는 각도가 다르다. 반드시 양측 동시 머신으로 — 케이블 좌우 버전은 수행 80초라 40초짜리 이너와 라운드가 안 맞는다]</t>
-  </si>
-  <si>
-    <t>힙 어브덕션 머신 (겸용 머신이 없을 때) / 케이블 힙 외전 (좌우 — 슈퍼세트로는 부적합) / 밴드 몬스터 워크 / 사이드 라잉 힙 외전</t>
+    <t>펙덱 플라이</t>
+  </si>
+  <si>
+    <t>25~30</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 프레싱 두 종목을 끝내고 고립으로 마무리하는 자리. 팔꿈치 각도를 고정한 채 어깨 수평 내전만 — 굽혔다 펴면 프레스가 된다. 첫날은 25kg으로 10~12회가 실패 2~3회 안에 들어오는지 보고 맞춘다. 이 종목을 넣어 흉근 합산이 주당 환산 24.1이 됐다(천장 20 초과) — 사용자가 알고 선택한 것이며, 세트 질이 떨어지면 2일차 디클라인 케이블 플라이 3세트를 먼저 뺀다.</t>
+  </si>
+  <si>
+    <t>케이블 크로스오버 / 플랫 벤치 덤벨 플라이 (가동범위 ↑) / 머신 체스트 플라이</t>
+  </si>
+  <si>
+    <t>케이블 푸쉬다운 (로프)</t>
+  </si>
+  <si>
+    <t>당기기 날에 삼두를 넣는 이유: 이 세션에서 삼두는 전혀 안 쓰이므로 완전히 신선한 상태에서 친다. 7일차 라잉 트라이셉스는 프레스 13세트를 마친 뒤라 자극당 값이 낮았고, 삼두 직접이 사이클당 1회뿐이었다 (직접 4 · 주당 환산 3.5로 MEV 6 미달). 이 3세트로 직접 7 · 사이클당 2회가 된다. 로프로 마지막에 손등을 바깥으로 벌리면 외측두가 끝까지 수축한다. 팔꿈치는 옆구리에 고정 — 어깨로 누르면 광배 종목이 된다. 7일차 라잉 익스텐션이 늘어난 구간(장두)이라 여기는 짧아진 구간(외측두·내측두)으로 축을 나눈다. [2026-08-28 — 이 자리에 있던 인클라인 덤벨 컬은 9일차로 이동]</t>
+  </si>
+  <si>
+    <t>V바 푸쉬다운 (손목이 편함) / 오버헤드 케이블 익스텐션 (장두 — 7일차와 겹치므로 차선) / 덤벨 킥백 / 벤치 딥스 (케이블이 없을 때)</t>
+  </si>
+  <si>
+    <t>20~25</t>
+  </si>
+  <si>
+    <t>밀기 날에 이두를 넣는 이유는 1일차 푸쉬다운과 같다 — 이 세션에서 이두는 전혀 안 쓰이므로 완전히 신선하다. 이두 직접이 6 → 9세트, 사이클당 2회 → 3회가 된다 (2일차 · 6일차 · 9일차, 간격 3-3-2일). 6일차 프리쳐(반동 차단 · 짧아진 구간) · 9일차 인클라인(늘어난 구간)과 달리 여기는 선 자세 전 구간이라 무게를 가장 많이 건다. 반동 쓰지 말 것 — 상체를 뒤로 젖히면 이두가 아니라 기립근 종목이 된다. 팔꿈치는 몸통 옆에 고정. [2026-08-28 추가 — 1일차에 0세트로 접혀 있던 종목을 이 자리로 되살린 것]</t>
+  </si>
+  <si>
+    <t>EZ바 컬 (손목이 편함) / 케이블 바 컬 (전 구간 장력 유지) / 머신 컬 / 덤벨 컬 양팔 동시</t>
+  </si>
+  <si>
+    <t>시티드 리스트 컬(손등 위)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>손목 신근. 타이핑으로 약해지는 쪽이라 비중을 더 준다</t>
+  </si>
+  <si>
+    <t>케이블 리버스 리스트 컬 / 리버스 EZ바 컬 (상완요골근까지) / 덤벨로 한 손씩</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 내전근을 성장 구간으로. 3일차에 4세트가 있지만 사이클당 1회라 모자랐다. 3일차와 같이 아우터 타이와 슈퍼세트로 묶는다 — 겸용 머신이라 패드만 뒤집으면 되어 전환이 10초고, 라운드 간 휴식은 아우터 쪽 105초가 맡는다. 길항근 쌍이라 서로의 피로를 나눠 갖지 않는다.</t>
+  </si>
+  <si>
+    <t>와이드 스탠스 레그 프레스 / 케이블 힙 내전</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 중둔근을 성장 구간으로. 3일차 4세트 · 8일차 케이블 힙 외전 3세트에 이어 세 번째 자리. 이너 타이와 슈퍼세트(A) — 이 105초가 두 종목의 라운드 간 휴식이다.</t>
+  </si>
+  <si>
+    <t>케이블 힙 외전 / 밴드 사이드 워크</t>
+  </si>
+  <si>
+    <t>4일차 원칙</t>
+  </si>
+  <si>
+    <t>· 2026-09-04 4-1-4-1 전환으로 신설. 옛 8일차 어깨 40세트를 A/B로 나누고 1·2일차에서 삼두 · 이두 · 전완을 가져왔다. 세트는 한 개도 안 늘었다 — 총량 예산 239 안에서 자리만 옮긴 것이다.</t>
+  </si>
+  <si>
+    <t>· 시간 균등화(같은 날)로 흉근 플라이 2종(디클라인 케이블 · 펙덱)이 2·7일차에서 왔다. 벤치 이틀 뒤 고립 6세트 — 흉근이 2·4·7일차 셋으로 흩어진다. "볼륨을 여러 날로 흩는 쪽이 낫지만 자리가 없었다"던 그 자리가 생긴 것이다.</t>
+  </si>
+  <si>
+    <t>· 3일차 스쿼트 다음 날이자 5일차 휴식 앞. 척추 부하 0 — 이 자리에 있는 이유다.</t>
+  </si>
+  <si>
+    <t>· 실패지점 1~2회 남기고 멈춘다. 세트 간 휴식 60~80초. 메인 리프트 없음 — 볼륨을 채우는 날이지 무게를 올리는 날이 아니다.</t>
+  </si>
+  <si>
+    <t>· 측면 · 후면 · 삼두 · 이두 · 전완이 9일차와 5일 간격으로 두 번 온다. 삼두 푸쉬다운은 벤치(2일차) 이틀 뒤, 9일차 라잉 익스텐션은 밀리터리(7일차) 이틀 뒤 — 대칭이다.</t>
+  </si>
+  <si>
+    <t>· 바벨 컬은 2일차 밀기에서 왔다. "당기기 뒤 지친 이두를 피한다"는 원래 이유는 팔 전용일이 생기며 해소됐고, 2일차는 82분 → 76분으로 시간 상한 안에 들어왔다.</t>
+  </si>
+  <si>
+    <t>· 이너·아우터 타이는 겸용 머신 슈퍼세트(A). 3일차와 같은 방식이고, 옛 8일차에서 그대로 옮겨 왔다.</t>
+  </si>
+  <si>
+    <t>되돌리는 법</t>
+  </si>
+  <si>
+    <t>· E열을 0으로 내리면 회색으로 접히고 합계 · 세트검산에서 빠진다. 다만 그 세트는 예산에서 사라지는 게 아니라 어딘가로 돌아가야 한다 — 잔여 예산이 양수로 뜨면 그 신호다.</t>
+  </si>
+  <si>
+    <t>6일차 — 당기기 B (수평)</t>
+  </si>
+  <si>
+    <t>로우 · 견갑골 후인 · 이두 · 전완. 1일차 당기기 A(수직)와 각도를 나눈다.</t>
+  </si>
+  <si>
+    <t>웜업 — 밴드 풀 어파트 2세트 × 15 (세트 카운트 제외): 가볍게, 견갑골 후인 프라이밍. 대체: 케이블 스캡 로우 / 아주 가벼운 페이스풀.</t>
+  </si>
+  <si>
+    <t>중부승모·이두</t>
+  </si>
+  <si>
+    <t>수평 당기기 메인. 가슴이 받쳐져 허리 부담이 없다. 그립은 넓게 · 팔꿈치는 벌려서 — 견갑 후인이 주동이라 능형근·중부승모로 계상하고 광배는 협력근이다(간접 0.5). [2026-09-04 라벨 정정: 광배 → 승모(중부)·능형근. 세트 수는 그대로 4]</t>
+  </si>
+  <si>
+    <t>체스트 서포티드 로우 / 티바 로우 / 펜들레이 로우 (척추 부하 ↑) / 바벨 로우</t>
+  </si>
+  <si>
+    <t>해머 로우와 역할을 나눈다 — 해머는 넓은 그립·팔꿈치 벌려 상부등, 이쪽은 좁은 그립·팔꿈치 붙여 광배. 이 날 유일한 광배 직접 종목이다.</t>
+  </si>
+  <si>
+    <t>원암 케이블 로우 (좌우 독립) / 덤벨 로우 / 머신 로우</t>
+  </si>
+  <si>
+    <t>시티드 케이블 로우 스캡 슈러그(두번째 크기 바)</t>
+  </si>
+  <si>
+    <t>후면 삼각근</t>
+  </si>
+  <si>
+    <t>2번 시티드 케이블 로우에서 무게만 내려 이어서 한다 (자리 이동 없음). 팔꿈치 각도를 세트 내내 고정하고 견갑골만 뒤로 — 가동범위 2~3cm, 모은 자리에서 1초 정지. 상체를 뒤로 눕히면 하부 승모 각도가 되고, 팔을 당기면 광배로 넘어간다. 케이블이라 수축 지점에서도 장력이 유지되고 핀 단위 미세 증량이 된다 (플레이트 로드 머신은 이 무게대에서 계단이 너무 큼).</t>
+  </si>
+  <si>
+    <t>해머 스트랭스 로우에서 팔 편 채 견갑골만 — 가슴 패드가 상체를 고정해줘 자세 잡기는 더 쉬우나 무게 미세 조정이 어렵다 / 리버스 펙덱을 팔 편 채로 / 켈소 슈러그 (받침 벤치가 있을 때)</t>
+  </si>
+  <si>
+    <t>후면 삼각근은 프레스로 자라지 않는다 — 반드시 별도로 센다 [v17 제외 — 후면은 2일차 4 · 7일차 3 · 9일차 9로 사이클당 3회 16세트 — 이 행은 그 재편으로 비워둔 자리다]</t>
+  </si>
+  <si>
+    <t>리버스 펙덱 (자세 유지가 쉬워 사실상 상위 호환) / 페이스풀 / 인클라인 벤치 리어델트 레이즈</t>
+  </si>
+  <si>
+    <t>반동이 차단되는 종목. 인클라인(9일차)과 각도를 나눈다</t>
+  </si>
+  <si>
+    <t>EZ바 프리처 컬 / 머신 프리처 컬 / 컨센트레이션 컬</t>
+  </si>
+  <si>
+    <t>전완 · 기립근</t>
+  </si>
+  <si>
+    <t>몸 옆에서 잡는 중립 그립이라 견갑골이 전인되지 않는다 — 바벨(몸 앞)보다 승모 상부 섬유 방향에 맞고 가동범위도 더 나온다. 어깨를 위로만, 돌리지 말 것 (회전은 가동범위를 늘리는 게 아니라 견봉하 공간만 좁힌다). 맨 위에서 1초 정지 — 정지 없이 하면 반동으로 끝난다. 턱은 당기고 목은 중립 (목을 앞으로 빼면 경추 신전근이 일한다). 그립이 승모보다 먼저 나가므로 스트랩 권장 — 전완은 이미 주 7세트 직접으로 충족돼 여기서 그립을 훈련할 이유가 없다. #8 자리인 이유: 앞의 로우 7세트 + 스캡 슈러그로 그립이 지쳐 있어 프리쳐 컬·리스트 컬보다 뒤에 와야 연쇄 피해가 없다. 7일차 오버헤드 슈러그(승모 하부·상방회전)와는 다른 근육이므로 대체가 아니라 추가다.</t>
+  </si>
+  <si>
+    <t>덤벨 슈러그 (트랩바 없을 때 — 몸 옆 그립 동일) / 스미스 슈러그 (궤도 고정) / 바벨 슈러그 (몸 앞이라 가동범위 약간 손해) / 케이블 슈러그</t>
+  </si>
+  <si>
+    <t>오버헤드 슈러그(스미스)</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 승모 하부는 실질 4.5로 가장 크게 모자랐다. 7일차에 같은 종목이 3세트 있었지만 사이클당 1회뿐이었고, 여기와 9일차를 더해 3회로 만들었다. 견갑 상방회전 — 팔을 머리 위에 둔 채 으쓱한다.</t>
+  </si>
+  <si>
+    <t>오버헤드 케이블 슈러그 / 프론 Y 레이즈</t>
   </si>
   <si>
     <t>무릎 편 상태 — 비복근 주도. 8일차 시티드(가자미근)와 역할이 다르다</t>
@@ -1259,195 +1466,6 @@
     <t>스탠딩 카프 레이즈 머신 / 레그 프레스 발판 끝에서 / 스미스 카프 레이즈</t>
   </si>
   <si>
-    <t>앱휠 롤아웃</t>
-  </si>
-  <si>
-    <t>항신전. 다음날이 당기기 B라 브레이싱 손실이 문제되지 않는다</t>
-  </si>
-  <si>
-    <t>애브 롤아웃 / 사이드 플랭크 / 팔로프 프레스 (항회전)</t>
-  </si>
-  <si>
-    <t>4일차 — 어깨·팔 A</t>
-  </si>
-  <si>
-    <t>측면·후면 삼각근 + 삼두 · 이두 · 전완 + 내전근·중둔근. 약 57분. 4-1-4-1 전환으로 신설 — 옛 8일차 어깨 세션의 절반과 1·2일차의 팔이 여기로 왔다. 거울 슬롯은 9일차 어깨·팔 B.</t>
-  </si>
-  <si>
-    <t>웜업 — 케이블 외회전 2세트 × 12~15 (세트 카운트 제외): 매우 가볍게 2.5~5kg. 팔꿈치를 90도로 접어 옆구리에 붙이고 바깥으로만 회전. 대체: 밴드 외회전 / 아주 가벼운 페이스풀.</t>
-  </si>
-  <si>
-    <t>머신 레터럴 레이즈</t>
-  </si>
-  <si>
-    <t>궤도가 고정돼 반동이 안 들어간다. 중간 구간을 끝까지 쓴다. 어깨가 으쓱 따라 올라가면 승모가 대신 일하는 것 — 무게를 내린다.</t>
-  </si>
-  <si>
-    <t>덤벨 레터럴 (머신 없을 때 — 몸 옆이 아니라 살짝 앞) / 케이블 레터럴 양팔 크로스</t>
-  </si>
-  <si>
-    <t>레이즈 계열과 달리 팔꿈치를 굽힌 채 당기는 궤적이라 측면의 다른 섬유가 동원되고, 승모 상부가 같이 온다 (승모 상부는 사이클당 3세트로 하한 미달이라 이 겸용이 값을 한다). 그립은 어깨너비보다 넓게, 팔꿈치는 가슴 높이까지만 — 좁은 그립으로 턱까지 올리면 견봉하 공간이 좁아진다.</t>
-  </si>
-  <si>
-    <t>EZ바 와이드 업라이트 로우 / 스미스 업라이트 로우 / 케이블 Y 레이즈 (충돌이 느껴질 때)</t>
-  </si>
-  <si>
-    <t>중부승모·능형근</t>
-  </si>
-  <si>
-    <t>팔을 편 채 수평으로만 벌린다. 케이블이라 수축 지점에서도 장력이 유지된다. 팔꿈치가 어깨선을 크게 지나가면 후면 삼각근에서 능형근으로 넘어간다.</t>
-  </si>
-  <si>
-    <t>리버스 펙덱 (2일차와 같은 머신이면 그립만 바꿔 각도를 나눈다) / 벤트오버 케이블 크로스</t>
-  </si>
-  <si>
-    <t>팔꿈치를 어깨 높이로 벌린 채 당긴다. 4·5번이 팔을 편 수평 외전이라면 이쪽은 굽힌 채 당기기라 모멘트암과 동원 섬유가 다르다 — 한 세션에 후면 9세트를 넣으면서 자극이 겹치지 않게 하는 축이 이것이다. 팔꿈치가 몸통 옆으로 붙으면 광배 로우가 된다.</t>
-  </si>
-  <si>
-    <t>와이드 그립 시티드 케이블 로우 (팔꿈치 벌려) / 페이스풀 (외회전까지 포함) / 머신 로우 와이드 그립</t>
-  </si>
-  <si>
-    <t>케이블 푸쉬다운 (로프)</t>
-  </si>
-  <si>
-    <t>당기기 날에 삼두를 넣는 이유: 이 세션에서 삼두는 전혀 안 쓰이므로 완전히 신선한 상태에서 친다. 7일차 라잉 트라이셉스는 프레스 13세트를 마친 뒤라 자극당 값이 낮았고, 삼두 직접이 사이클당 1회뿐이었다 (직접 4 · 주당 환산 3.5로 MEV 6 미달). 이 3세트로 직접 7 · 사이클당 2회가 된다. 로프로 마지막에 손등을 바깥으로 벌리면 외측두가 끝까지 수축한다. 팔꿈치는 옆구리에 고정 — 어깨로 누르면 광배 종목이 된다. 7일차 라잉 익스텐션이 늘어난 구간(장두)이라 여기는 짧아진 구간(외측두·내측두)으로 축을 나눈다. [2026-08-28 — 이 자리에 있던 인클라인 덤벨 컬은 9일차로 이동]</t>
-  </si>
-  <si>
-    <t>V바 푸쉬다운 (손목이 편함) / 오버헤드 케이블 익스텐션 (장두 — 7일차와 겹치므로 차선) / 덤벨 킥백 / 벤치 딥스 (케이블이 없을 때)</t>
-  </si>
-  <si>
-    <t>20~25</t>
-  </si>
-  <si>
-    <t>밀기 날에 이두를 넣는 이유는 1일차 푸쉬다운과 같다 — 이 세션에서 이두는 전혀 안 쓰이므로 완전히 신선하다. 이두 직접이 6 → 9세트, 사이클당 2회 → 3회가 된다 (2일차 · 6일차 · 9일차, 간격 3-3-2일). 6일차 프리쳐(반동 차단 · 짧아진 구간) · 9일차 인클라인(늘어난 구간)과 달리 여기는 선 자세 전 구간이라 무게를 가장 많이 건다. 반동 쓰지 말 것 — 상체를 뒤로 젖히면 이두가 아니라 기립근 종목이 된다. 팔꿈치는 몸통 옆에 고정. [2026-08-28 추가 — 1일차에 0세트로 접혀 있던 종목을 이 자리로 되살린 것]</t>
-  </si>
-  <si>
-    <t>EZ바 컬 (손목이 편함) / 케이블 바 컬 (전 구간 장력 유지) / 머신 컬 / 덤벨 컬 양팔 동시</t>
-  </si>
-  <si>
-    <t>시티드 리스트 컬(손등 위)</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>손목 신근. 타이핑으로 약해지는 쪽이라 비중을 더 준다</t>
-  </si>
-  <si>
-    <t>케이블 리버스 리스트 컬 / 리버스 EZ바 컬 (상완요골근까지) / 덤벨로 한 손씩</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>[2026-09-04 신설] 내전근을 성장 구간으로. 3일차에 4세트가 있지만 사이클당 1회라 모자랐다. 3일차와 같이 아우터 타이와 슈퍼세트로 묶는다 — 겸용 머신이라 패드만 뒤집으면 되어 전환이 10초고, 라운드 간 휴식은 아우터 쪽 105초가 맡는다. 길항근 쌍이라 서로의 피로를 나눠 갖지 않는다.</t>
-  </si>
-  <si>
-    <t>와이드 스탠스 레그 프레스 / 케이블 힙 내전</t>
-  </si>
-  <si>
-    <t>[2026-09-04 신설] 중둔근을 성장 구간으로. 3일차 4세트 · 8일차 케이블 힙 외전 3세트에 이어 세 번째 자리. 이너 타이와 슈퍼세트(A) — 이 105초가 두 종목의 라운드 간 휴식이다.</t>
-  </si>
-  <si>
-    <t>케이블 힙 외전 / 밴드 사이드 워크</t>
-  </si>
-  <si>
-    <t>4일차 원칙</t>
-  </si>
-  <si>
-    <t>· 2026-09-04 4-1-4-1 전환으로 신설. 옛 8일차 어깨 40세트를 A/B로 나누고 1·2일차에서 삼두 · 이두 · 전완을 가져왔다. 세트는 한 개도 안 늘었다 — 총량 예산 239 안에서 자리만 옮긴 것이다.</t>
-  </si>
-  <si>
-    <t>· 3일차 스쿼트 다음 날이자 5일차 휴식 앞. 척추 부하 0 — 이 자리에 있는 이유다.</t>
-  </si>
-  <si>
-    <t>· 실패지점 1~2회 남기고 멈춘다. 세트 간 휴식 60~80초. 메인 리프트 없음 — 볼륨을 채우는 날이지 무게를 올리는 날이 아니다.</t>
-  </si>
-  <si>
-    <t>· 측면 · 후면 · 삼두 · 이두 · 전완이 9일차와 5일 간격으로 두 번 온다. 삼두 푸쉬다운은 벤치(2일차) 이틀 뒤, 9일차 라잉 익스텐션은 밀리터리(7일차) 이틀 뒤 — 대칭이다.</t>
-  </si>
-  <si>
-    <t>· 바벨 컬은 2일차 밀기에서 왔다. "당기기 뒤 지친 이두를 피한다"는 원래 이유는 팔 전용일이 생기며 해소됐고, 2일차는 82분 → 76분으로 시간 상한 안에 들어왔다.</t>
-  </si>
-  <si>
-    <t>· 이너·아우터 타이는 겸용 머신 슈퍼세트(A). 3일차와 같은 방식이고, 옛 8일차에서 그대로 옮겨 왔다.</t>
-  </si>
-  <si>
-    <t>되돌리는 법</t>
-  </si>
-  <si>
-    <t>· E열을 0으로 내리면 회색으로 접히고 합계 · 세트검산에서 빠진다. 다만 그 세트는 예산에서 사라지는 게 아니라 어딘가로 돌아가야 한다 — 잔여 예산이 양수로 뜨면 그 신호다.</t>
-  </si>
-  <si>
-    <t>6일차 — 당기기 B (수평)</t>
-  </si>
-  <si>
-    <t>로우 · 견갑골 후인 · 이두 · 전완. 1일차 당기기 A(수직)와 각도를 나눈다.</t>
-  </si>
-  <si>
-    <t>웜업 — 밴드 풀 어파트 2세트 × 15 (세트 카운트 제외): 가볍게, 견갑골 후인 프라이밍. 대체: 케이블 스캡 로우 / 아주 가벼운 페이스풀.</t>
-  </si>
-  <si>
-    <t>중부승모·이두</t>
-  </si>
-  <si>
-    <t>수평 당기기 메인. 가슴이 받쳐져 허리 부담이 없다. 그립은 넓게 · 팔꿈치는 벌려서 — 견갑 후인이 주동이라 능형근·중부승모로 계상하고 광배는 협력근이다(간접 0.5). [2026-09-04 라벨 정정: 광배 → 승모(중부)·능형근. 세트 수는 그대로 4]</t>
-  </si>
-  <si>
-    <t>체스트 서포티드 로우 / 티바 로우 / 펜들레이 로우 (척추 부하 ↑) / 바벨 로우</t>
-  </si>
-  <si>
-    <t>해머 로우와 역할을 나눈다 — 해머는 넓은 그립·팔꿈치 벌려 상부등, 이쪽은 좁은 그립·팔꿈치 붙여 광배. 이 날 유일한 광배 직접 종목이다.</t>
-  </si>
-  <si>
-    <t>원암 케이블 로우 (좌우 독립) / 덤벨 로우 / 머신 로우</t>
-  </si>
-  <si>
-    <t>시티드 케이블 로우 스캡 슈러그(두번째 크기 바)</t>
-  </si>
-  <si>
-    <t>후면 삼각근</t>
-  </si>
-  <si>
-    <t>2번 시티드 케이블 로우에서 무게만 내려 이어서 한다 (자리 이동 없음). 팔꿈치 각도를 세트 내내 고정하고 견갑골만 뒤로 — 가동범위 2~3cm, 모은 자리에서 1초 정지. 상체를 뒤로 눕히면 하부 승모 각도가 되고, 팔을 당기면 광배로 넘어간다. 케이블이라 수축 지점에서도 장력이 유지되고 핀 단위 미세 증량이 된다 (플레이트 로드 머신은 이 무게대에서 계단이 너무 큼).</t>
-  </si>
-  <si>
-    <t>해머 스트랭스 로우에서 팔 편 채 견갑골만 — 가슴 패드가 상체를 고정해줘 자세 잡기는 더 쉬우나 무게 미세 조정이 어렵다 / 리버스 펙덱을 팔 편 채로 / 켈소 슈러그 (받침 벤치가 있을 때)</t>
-  </si>
-  <si>
-    <t>후면 삼각근은 프레스로 자라지 않는다 — 반드시 별도로 센다 [v17 제외 — 후면은 2일차 4 · 7일차 3 · 9일차 9로 사이클당 3회 16세트 — 이 행은 그 재편으로 비워둔 자리다]</t>
-  </si>
-  <si>
-    <t>리버스 펙덱 (자세 유지가 쉬워 사실상 상위 호환) / 페이스풀 / 인클라인 벤치 리어델트 레이즈</t>
-  </si>
-  <si>
-    <t>반동이 차단되는 종목. 인클라인(9일차)과 각도를 나눈다</t>
-  </si>
-  <si>
-    <t>EZ바 프리처 컬 / 머신 프리처 컬 / 컨센트레이션 컬</t>
-  </si>
-  <si>
-    <t>전완 · 기립근</t>
-  </si>
-  <si>
-    <t>몸 옆에서 잡는 중립 그립이라 견갑골이 전인되지 않는다 — 바벨(몸 앞)보다 승모 상부 섬유 방향에 맞고 가동범위도 더 나온다. 어깨를 위로만, 돌리지 말 것 (회전은 가동범위를 늘리는 게 아니라 견봉하 공간만 좁힌다). 맨 위에서 1초 정지 — 정지 없이 하면 반동으로 끝난다. 턱은 당기고 목은 중립 (목을 앞으로 빼면 경추 신전근이 일한다). 그립이 승모보다 먼저 나가므로 스트랩 권장 — 전완은 이미 주 7세트 직접으로 충족돼 여기서 그립을 훈련할 이유가 없다. #8 자리인 이유: 앞의 로우 7세트 + 스캡 슈러그로 그립이 지쳐 있어 프리쳐 컬·리스트 컬보다 뒤에 와야 연쇄 피해가 없다. 7일차 오버헤드 슈러그(승모 하부·상방회전)와는 다른 근육이므로 대체가 아니라 추가다.</t>
-  </si>
-  <si>
-    <t>덤벨 슈러그 (트랩바 없을 때 — 몸 옆 그립 동일) / 스미스 슈러그 (궤도 고정) / 바벨 슈러그 (몸 앞이라 가동범위 약간 손해) / 케이블 슈러그</t>
-  </si>
-  <si>
-    <t>오버헤드 슈러그(스미스)</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>[2026-09-04 신설] 승모 하부는 실질 4.5로 가장 크게 모자랐다. 7일차에 같은 종목이 3세트 있었지만 사이클당 1회뿐이었고, 여기와 9일차를 더해 3회로 만들었다. 견갑 상방회전 — 팔을 머리 위에 둔 채 으쓱한다.</t>
-  </si>
-  <si>
-    <t>오버헤드 케이블 슈러그 / 프론 Y 레이즈</t>
-  </si>
-  <si>
     <t>중량 크런치</t>
   </si>
   <si>
@@ -1505,18 +1523,6 @@
     <t>인클라인 스미스 프레스 / 인클라인 덤벨 프레스 (가동범위 ↑) / 인클라인 체스트 프레스 머신</t>
   </si>
   <si>
-    <t>펙덱 플라이</t>
-  </si>
-  <si>
-    <t>25~30</t>
-  </si>
-  <si>
-    <t>[2026-09-04 신설] 프레싱 두 종목을 끝내고 고립으로 마무리하는 자리. 팔꿈치 각도를 고정한 채 어깨 수평 내전만 — 굽혔다 펴면 프레스가 된다. 첫날은 25kg으로 10~12회가 실패 2~3회 안에 들어오는지 보고 맞춘다. 이 종목을 넣어 흉근 합산이 주당 환산 24.1이 됐다(천장 20 초과) — 사용자가 알고 선택한 것이며, 세트 질이 떨어지면 2일차 디클라인 케이블 플라이 3세트를 먼저 뺀다.</t>
-  </si>
-  <si>
-    <t>케이블 크로스오버 / 플랫 벤치 덤벨 플라이 (가동범위 ↑) / 머신 체스트 플라이</t>
-  </si>
-  <si>
     <t>벤트오버 레터럴 레이즈 머신</t>
   </si>
   <si>
@@ -1637,6 +1643,84 @@
     <t>시티드 카프 레이즈 머신 (1순위) / 레그 프레스에서 무릎 굽힌 채 / 덤벨을 무릎에 올리고</t>
   </si>
   <si>
+    <t>9일차 — 어깨·팔 B</t>
+  </si>
+  <si>
+    <t>측면 · 후면 · 전면 삼각근 + 하부 승모 + 삼두 · 이두 · 전완 + 종아리 · 중둔근. 약 67분. 옛 8일차 어깨 세션의 절반 — 나머지 절반은 4일차 어깨·팔 A. 8일차 데드 다음 날이라 척추 부하 0은 그대로다.</t>
+  </si>
+  <si>
+    <t>리닝 원암 케이블 레터럴 레이즈</t>
+  </si>
+  <si>
+    <t>기둥을 잡고 몸을 반대로 기울여 늘어난 위치부터 부하가 걸린다 — 머신·덤벨이 못 거는 구간이다. 좌우 각 2세트. 7일차에도 같은 종목이 있지만 5일 간격이라 겹치지 않는다.</t>
+  </si>
+  <si>
+    <t>케이블 비하인드백 레터럴 / 로우 풀리 원암 레터럴 / 인클라인 벤치에 옆으로 누워 덤벨 레터럴</t>
+  </si>
+  <si>
+    <t>인클라인 벤치 프론 리어 델트 레이즈</t>
+  </si>
+  <si>
+    <t>가슴을 벤치에 대고 엎드려 상체를 고정한다 — 반동과 기립근 개입이 통째로 차단돼 후면만 남는다. 자유중량이라 궤도가 고정된 4번과 다른 안정화 요구가 붙는다. 아주 가볍게, 무게보다 정지 1초.</t>
+  </si>
+  <si>
+    <t>프론 덤벨 리어 레이즈 (평벤치) / 시티드 벤트오버 덤벨 리어 레이즈 / 리버스 펙덱</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 전면삼각 직접이 6세트(7일차 밀리터리 3 + 머신 숄더 3)뿐이라 측면 18 · 후면 17에 견주면 얇았다. 9일 주기 전환으로 주당 9.7까지 내려와 이 자리를 만들었다. 레터럴·리어 6종목 뒤에 두는 이유: 앞에 두면 프레스 피로로 레이즈 중량이 눌린다. 여기 목적은 근력이 아니라 볼륨이므로 중량이 7일차보다 낮아도 된다.</t>
+  </si>
+  <si>
+    <t>덤벨 숄더 프레스 / 스미스 오버헤드 프레스</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 승모 하부 세 번째 자리. 7일차에서 0세트로 꺼져 있던 종목을 그쪽에서 켜고 여기에도 뒀다. 견갑 하강 + 상방회전. 엎드려 팔을 Y자로 — 중량보다 견갑이 먼저 움직이는지가 중요하다.</t>
+  </si>
+  <si>
+    <t>인클라인 벤치 프론 Y / 케이블 로 투 하이 (한 팔)</t>
+  </si>
+  <si>
+    <t>라잉 트라이셉스 익스텐션</t>
+  </si>
+  <si>
+    <t>늘어난 구간 삼두 — 2일차에서 이동 (v18). 푸쉬다운 제외로 2일차 고정 사유가 소멸, 유일한 삼두 고립을 프레싱 전부 마친 뒤 마지막에. 팔꿈치 시큰하면 EZ바나 오버헤드 케이블로. (이 자리의 케이블 푸쉬다운은 v17 제외 — 삼두 간접 9로 충족)</t>
+  </si>
+  <si>
+    <t>오버헤드 케이블 익스텐션 / 스컬크러셔 / EZ바 라잉 익스텐션</t>
+  </si>
+  <si>
+    <t>1일차에서 옮겨 왔다 (2026-08-28). 그 날은 친업 4 + 랫풀다운 3으로 이두가 간접 3.5세트분 지친 뒤였는데, 이 날은 어깨만 치므로 이두가 완전히 신선하다. 같은 3세트라도 자극당 값이 다르다. 인클라인 벤치에 기대 팔을 뒤로 늘어뜨린다 — 이두 장두가 늘어난 위치에서 시작하는 것이 이 종목의 전부다. 6일차 프리쳐 컬(짧아진 구간)과 각도를 나눈다. 어깨를 앞으로 말면 늘어난 구간이 사라진다.</t>
+  </si>
+  <si>
+    <t>케이블 컬 (뒤로 물러서서 스트레치 확보) / 스파이더 컬 (반대 각도) / 드래그 컬</t>
+  </si>
+  <si>
+    <t>리버스 리스트익스텐션 컬(손등 아래)</t>
+  </si>
+  <si>
+    <t>손목 굴근. 1일차 리버스와 대항쌍 [v17 감량 4→3 — 전완 실질 8로 자체 하한 유지]</t>
+  </si>
+  <si>
+    <t>덤벨 리스트 컬 (한 손씩) / 케이블 리스트 컬 / 비하인드백 리스트 컬</t>
+  </si>
+  <si>
+    <t>이두(상완근)</t>
+  </si>
+  <si>
+    <t>오버핸드(엎침) 그립 컬 — 상완요골근·상완근이 주동이다. 언더핸드 프리쳐 컬(#5)과 그립을 나눠 같은 굴곡 패턴을 다른 축으로 친다. 손목은 중립으로 고정하고 반동 금지 — 손목을 위로 꺾으면 리스트 컬(#6)이 되고 상완요골근에서 빠진다. 회외가 없어 이두가 짧아진 자리에서 힘을 못 쓰므로 언더핸드 컬보다 30~40% 가벼운 것이 정상이다. #7 자리인 이유: 그립을 쓰는 종목이라 컬 계열 바로 뒤에 붙이고, 스트랩을 쓰는 트랩바 슈러그를 뒤로 보낸다. [2026-08-28 추가 — 전완 직접 6→9세트]</t>
+  </si>
+  <si>
+    <t>EZ바 리버스 컬 (손목 부담 ↓ — 1순위) / 케이블 리버스 컬 (수축 지점까지 장력 유지 · 핀 단위 미세 증량) / 리버스 프리쳐 컬 (반동 차단) / 해머 컬 (중립 그립 — 상완요골근 같은 계열이나 자극 각도가 다르다)</t>
+  </si>
+  <si>
+    <t>[2026-09-04 신설] 무릎 굽힌 상태 — 가자미근. 1일차 스탠딩(비복근)과 각도를 나눈다. 8일차에 같은 종목이 4세트 있고 여기 2세트를 더해 종아리를 주당 10으로 올린다.</t>
+  </si>
+  <si>
+    <t>레그 프레스 카프 / 스탠딩 카프 (기계가 찼을 때)</t>
+  </si>
+  <si>
     <t>케이블 힙 외전</t>
   </si>
   <si>
@@ -1646,84 +1730,6 @@
     <t>밴드 몬스터 워크 / 사이드 라잉 힙 외전 / 힙 어브덕션 머신</t>
   </si>
   <si>
-    <t>9일차 — 어깨·팔 B</t>
-  </si>
-  <si>
-    <t>측면 · 후면 · 전면 삼각근 + 하부 승모 + 삼두 · 이두 · 전완 + 종아리. 약 59분. 옛 8일차 어깨 세션의 절반 — 나머지 절반은 4일차 어깨·팔 A. 8일차 데드 다음 날이라 척추 부하 0은 그대로다.</t>
-  </si>
-  <si>
-    <t>리닝 원암 케이블 레터럴 레이즈</t>
-  </si>
-  <si>
-    <t>기둥을 잡고 몸을 반대로 기울여 늘어난 위치부터 부하가 걸린다 — 머신·덤벨이 못 거는 구간이다. 좌우 각 2세트. 7일차에도 같은 종목이 있지만 5일 간격이라 겹치지 않는다.</t>
-  </si>
-  <si>
-    <t>케이블 비하인드백 레터럴 / 로우 풀리 원암 레터럴 / 인클라인 벤치에 옆으로 누워 덤벨 레터럴</t>
-  </si>
-  <si>
-    <t>인클라인 벤치 프론 리어 델트 레이즈</t>
-  </si>
-  <si>
-    <t>가슴을 벤치에 대고 엎드려 상체를 고정한다 — 반동과 기립근 개입이 통째로 차단돼 후면만 남는다. 자유중량이라 궤도가 고정된 4번과 다른 안정화 요구가 붙는다. 아주 가볍게, 무게보다 정지 1초.</t>
-  </si>
-  <si>
-    <t>프론 덤벨 리어 레이즈 (평벤치) / 시티드 벤트오버 덤벨 리어 레이즈 / 리버스 펙덱</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>[2026-09-04 신설] 전면삼각 직접이 6세트(7일차 밀리터리 3 + 머신 숄더 3)뿐이라 측면 18 · 후면 17에 견주면 얇았다. 9일 주기 전환으로 주당 9.7까지 내려와 이 자리를 만들었다. 레터럴·리어 6종목 뒤에 두는 이유: 앞에 두면 프레스 피로로 레이즈 중량이 눌린다. 여기 목적은 근력이 아니라 볼륨이므로 중량이 7일차보다 낮아도 된다.</t>
-  </si>
-  <si>
-    <t>덤벨 숄더 프레스 / 스미스 오버헤드 프레스</t>
-  </si>
-  <si>
-    <t>[2026-09-04 신설] 승모 하부 세 번째 자리. 7일차에서 0세트로 꺼져 있던 종목을 그쪽에서 켜고 여기에도 뒀다. 견갑 하강 + 상방회전. 엎드려 팔을 Y자로 — 중량보다 견갑이 먼저 움직이는지가 중요하다.</t>
-  </si>
-  <si>
-    <t>인클라인 벤치 프론 Y / 케이블 로 투 하이 (한 팔)</t>
-  </si>
-  <si>
-    <t>라잉 트라이셉스 익스텐션</t>
-  </si>
-  <si>
-    <t>늘어난 구간 삼두 — 2일차에서 이동 (v18). 푸쉬다운 제외로 2일차 고정 사유가 소멸, 유일한 삼두 고립을 프레싱 전부 마친 뒤 마지막에. 팔꿈치 시큰하면 EZ바나 오버헤드 케이블로. (이 자리의 케이블 푸쉬다운은 v17 제외 — 삼두 간접 9로 충족)</t>
-  </si>
-  <si>
-    <t>오버헤드 케이블 익스텐션 / 스컬크러셔 / EZ바 라잉 익스텐션</t>
-  </si>
-  <si>
-    <t>1일차에서 옮겨 왔다 (2026-08-28). 그 날은 친업 4 + 랫풀다운 3으로 이두가 간접 3.5세트분 지친 뒤였는데, 이 날은 어깨만 치므로 이두가 완전히 신선하다. 같은 3세트라도 자극당 값이 다르다. 인클라인 벤치에 기대 팔을 뒤로 늘어뜨린다 — 이두 장두가 늘어난 위치에서 시작하는 것이 이 종목의 전부다. 6일차 프리쳐 컬(짧아진 구간)과 각도를 나눈다. 어깨를 앞으로 말면 늘어난 구간이 사라진다.</t>
-  </si>
-  <si>
-    <t>케이블 컬 (뒤로 물러서서 스트레치 확보) / 스파이더 컬 (반대 각도) / 드래그 컬</t>
-  </si>
-  <si>
-    <t>리버스 리스트익스텐션 컬(손등 아래)</t>
-  </si>
-  <si>
-    <t>손목 굴근. 1일차 리버스와 대항쌍 [v17 감량 4→3 — 전완 실질 8로 자체 하한 유지]</t>
-  </si>
-  <si>
-    <t>덤벨 리스트 컬 (한 손씩) / 케이블 리스트 컬 / 비하인드백 리스트 컬</t>
-  </si>
-  <si>
-    <t>이두(상완근)</t>
-  </si>
-  <si>
-    <t>오버핸드(엎침) 그립 컬 — 상완요골근·상완근이 주동이다. 언더핸드 프리쳐 컬(#5)과 그립을 나눠 같은 굴곡 패턴을 다른 축으로 친다. 손목은 중립으로 고정하고 반동 금지 — 손목을 위로 꺾으면 리스트 컬(#6)이 되고 상완요골근에서 빠진다. 회외가 없어 이두가 짧아진 자리에서 힘을 못 쓰므로 언더핸드 컬보다 30~40% 가벼운 것이 정상이다. #7 자리인 이유: 그립을 쓰는 종목이라 컬 계열 바로 뒤에 붙이고, 스트랩을 쓰는 트랩바 슈러그를 뒤로 보낸다. [2026-08-28 추가 — 전완 직접 6→9세트]</t>
-  </si>
-  <si>
-    <t>EZ바 리버스 컬 (손목 부담 ↓ — 1순위) / 케이블 리버스 컬 (수축 지점까지 장력 유지 · 핀 단위 미세 증량) / 리버스 프리쳐 컬 (반동 차단) / 해머 컬 (중립 그립 — 상완요골근 같은 계열이나 자극 각도가 다르다)</t>
-  </si>
-  <si>
-    <t>[2026-09-04 신설] 무릎 굽힌 상태 — 가자미근. 1일차 스탠딩(비복근)과 각도를 나눈다. 8일차에 같은 종목이 4세트 있고 여기 2세트를 더해 종아리를 주당 10으로 올린다.</t>
-  </si>
-  <si>
-    <t>레그 프레스 카프 / 스탠딩 카프 (기계가 찼을 때)</t>
-  </si>
-  <si>
     <t>어깨·팔 B (2026-09-04 4-1-4-1 전환)</t>
   </si>
   <si>
@@ -1731,6 +1737,9 @@
   </si>
   <si>
     <t>· 세트는 한 개도 안 늘었다. 40 → 30이 된 것은 10세트가 4일차로 간 것이지 뺀 게 아니다.</t>
+  </si>
+  <si>
+    <t>· 시간 균등화로 8일차 케이블 힙 외전 3세트가 왔다. 4일차 아우터 타이와 짝 — 중둔근이 3·4·9일차. 케이블이라 척추 부하는 없다.</t>
   </si>
   <si>
     <t>· 아래 서술은 통합 시절(옛 8일차 · 40세트 · 6종목 분할) 기준이라 세트 수와 종목 번호가 지금과 다르다. 기록으로 남긴다.</t>
@@ -4083,7 +4092,7 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4106,16 +4115,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF95A5A6"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5001,7 +5000,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -5018,66 +5017,66 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1">
       <c r="A3" s="33" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" s="35" t="s">
         <v>140</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E5" s="35" t="s">
         <v>195</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" customHeight="1">
@@ -5085,7 +5084,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>50</v>
@@ -5097,7 +5096,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G6" s="26">
         <v>80</v>
@@ -5106,15 +5105,15 @@
         <v>70</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I14" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I15" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
         <v>7.5</v>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="L6" s="21" t="s">
         <v>533</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" customHeight="1">
@@ -5122,7 +5121,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>56</v>
@@ -5134,7 +5133,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G7" s="26">
         <v>40</v>
@@ -5148,10 +5147,10 @@
       </c>
       <c r="J7" s="21"/>
       <c r="K7" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="L7" s="21" t="s">
         <v>536</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" customHeight="1">
@@ -5165,13 +5164,13 @@
         <v>46</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E8" s="20">
         <v>3</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G8" s="26">
         <v>40</v>
@@ -5184,13 +5183,13 @@
         <v>8</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="K8" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="L8" s="21" t="s">
         <v>539</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1">
@@ -5204,13 +5203,13 @@
         <v>106</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E9" s="20">
         <v>3</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G9" s="26">
         <v>40</v>
@@ -5226,10 +5225,10 @@
         <v>56</v>
       </c>
       <c r="K9" s="21" t="s">
+        <v>540</v>
+      </c>
+      <c r="L9" s="21" t="s">
         <v>541</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1">
@@ -5237,7 +5236,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>26</v>
@@ -5249,7 +5248,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G10" s="26">
         <v>40</v>
@@ -5263,10 +5262,10 @@
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
+        <v>543</v>
+      </c>
+      <c r="L10" s="21" t="s">
         <v>544</v>
-      </c>
-      <c r="L10" s="21" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
@@ -5286,7 +5285,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G11" s="26">
         <v>40</v>
@@ -5302,10 +5301,10 @@
         <v>40</v>
       </c>
       <c r="K11" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="L11" s="21" t="s">
         <v>546</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1">
@@ -5313,7 +5312,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>40</v>
@@ -5325,7 +5324,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G12" s="26">
         <v>40</v>
@@ -5339,10 +5338,10 @@
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="L12" s="21" t="s">
         <v>549</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
@@ -5362,7 +5361,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G13" s="26">
         <v>40</v>
@@ -5375,13 +5374,13 @@
         <v>7.3</v>
       </c>
       <c r="J13" s="21" t="s">
+        <v>550</v>
+      </c>
+      <c r="K13" s="21" t="s">
         <v>551</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="L13" s="21" t="s">
         <v>552</v>
-      </c>
-      <c r="L13" s="21" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
@@ -5389,19 +5388,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E14" s="20">
         <v>2</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G14" s="26">
         <v>40</v>
@@ -5415,160 +5414,202 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
+        <v>553</v>
+      </c>
+      <c r="L14" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="L14" s="21" t="s">
+    </row>
+    <row r="15" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A15" s="20">
+        <v>10</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.5" customHeight="1">
-      <c r="D15" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E15" s="27">
-        <f>SUM(E6:E14)</f>
-        <v>30</v>
-      </c>
-      <c r="I15">
-        <f>ROUND(SUM(I6:I14),0)</f>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="16.5" customHeight="1"/>
-    <row r="17" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A17" s="108" t="s">
+      <c r="C15" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="26">
+        <v>15</v>
+      </c>
+      <c r="E15" s="20">
+        <v>3</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="G15" s="26">
+        <v>80</v>
+      </c>
+      <c r="H15" s="26">
+        <v>75</v>
+      </c>
+      <c r="I15" s="26">
+        <f t="shared" si="0"/>
+        <v>7.8</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21" t="s">
         <v>556</v>
       </c>
-    </row>
+      <c r="L15" s="21" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="16.5" customHeight="1">
+      <c r="D16" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E16" s="27">
+        <f>SUM(E6:E15)</f>
+        <v>33</v>
+      </c>
+      <c r="I16">
+        <f>ROUND(SUM(I6:I15),0)</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="18" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A18" t="s">
-        <v>557</v>
+      <c r="A18" s="108" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="16.5" customHeight="1">
       <c r="A19" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="16.5" customHeight="1">
       <c r="A20" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="16.5" customHeight="1"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A21" t="s">
+        <v>561</v>
+      </c>
+    </row>
     <row r="22" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A23" s="31" t="s">
-        <v>561</v>
-      </c>
-    </row>
+      <c r="A22" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A24" s="31" t="s">
-        <v>562</v>
+      <c r="A24" s="3" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" s="31" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" s="31" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>565</v>
+      <c r="A27" s="31" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" s="31" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A29" s="31" t="s">
-        <v>567</v>
+      <c r="A29" s="3" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>568</v>
+      <c r="A30" s="31" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="16.5" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A32" s="31" t="s">
-        <v>570</v>
+      <c r="A32" s="3" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>573</v>
+      <c r="A35" s="31" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A37" s="31" t="s">
-        <v>575</v>
+      <c r="A37" s="3" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="16.5" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="16.5" customHeight="1">
       <c r="A39" s="31" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A40" s="3" t="s">
-        <v>439</v>
+      <c r="A40" s="31" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="31" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="31" t="s">
-        <v>579</v>
+      <c r="A42" s="3" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="31" t="s">
-        <v>580</v>
+        <v>581</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="31" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="31" t="s">
+        <v>583</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N14">
+  <conditionalFormatting sqref="A6:N15">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
@@ -7529,30 +7570,30 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="G1" s="93" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="G2" s="94" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H2" s="95">
         <v>10</v>
       </c>
       <c r="I2" s="94" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="J2" s="95">
         <v>239</v>
       </c>
       <c r="K2" s="94" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="L2" s="96">
         <f>B25</f>
@@ -7565,21 +7606,21 @@
         <v/>
       </c>
       <c r="G3" s="94" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="H3" s="98">
         <f>$J$2-$L$2</f>
         <v>0</v>
       </c>
       <c r="I3" s="94" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="J3" s="98">
         <f>ROUND($L$2*7/$H$2,1)</f>
         <v>167.3</v>
       </c>
       <c r="K3" s="94" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="L3" s="98" t="str">
         <f>IF($H$3&lt;0,"INVALID","VALID")</f>
@@ -7588,22 +7629,22 @@
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="J4" s="99" t="str">
         <f>"주당 환산 (×7/"&amp;$H$2&amp;")"</f>
@@ -7631,10 +7672,10 @@
         <v>유지</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="G5" s="113" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="H5" s="56">
         <f ca="1">SUM(D5:D6)</f>
@@ -7674,7 +7715,7 @@
         <v>성장</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="G6" s="114"/>
       <c r="J6" s="55">
@@ -7707,10 +7748,10 @@
         <v>성장</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="G7" s="113" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="H7" s="56">
         <f ca="1">SUM(D7:D10)</f>
@@ -7746,7 +7787,7 @@
         <v>유지 미만</v>
       </c>
       <c r="F8" s="53" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="G8" s="114"/>
       <c r="J8" s="55">
@@ -7779,7 +7820,7 @@
         <v>유지</v>
       </c>
       <c r="F9" s="53" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="G9" s="114"/>
       <c r="J9" s="55">
@@ -7812,7 +7853,7 @@
         <v>성장</v>
       </c>
       <c r="F10" s="53" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="G10" s="114"/>
       <c r="J10" s="55">
@@ -7845,7 +7886,7 @@
         <v>유지</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="G11" s="57"/>
       <c r="J11" s="55">
@@ -7878,7 +7919,7 @@
         <v>성장</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="G12" s="57"/>
       <c r="J12" s="55">
@@ -7911,7 +7952,7 @@
         <v>성장</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="G13" s="57"/>
       <c r="J13" s="55">
@@ -7944,7 +7985,7 @@
         <v>성장</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G14" s="57"/>
       <c r="H14" s="56"/>
@@ -7981,7 +8022,7 @@
         <v>88</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H15" s="56">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -8017,7 +8058,7 @@
         <v>유지</v>
       </c>
       <c r="F16" s="53" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="G16" s="57"/>
       <c r="J16" s="55">
@@ -8050,7 +8091,7 @@
         <v>성장</v>
       </c>
       <c r="F17" s="53" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="G17" s="113" t="s">
         <v>76</v>
@@ -8089,7 +8130,7 @@
         <v>유지</v>
       </c>
       <c r="F18" s="53" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="G18" s="114"/>
       <c r="J18" s="55">
@@ -8103,7 +8144,7 @@
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1">
       <c r="A19" s="53" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B19" s="7">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A19)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A19)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A19)+SUMIFS(D4_어깨팔A!$E:$E,D4_어깨팔A!$C:$C,$A19)+SUMIFS(D6_당기기B!$E:$E,D6_당기기B!$C:$C,$A19)+SUMIFS(D7_밀기B!$E:$E,D7_밀기B!$C:$C,$A19)+SUMIFS(D8_하체B!$E:$E,D8_하체B!$C:$C,$A19)+SUMIFS(D9_어깨팔B!$E:$E,D9_어깨팔B!$C:$C,$A19)</f>
@@ -8122,7 +8163,7 @@
         <v>유지</v>
       </c>
       <c r="F19" s="53" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="G19" s="57"/>
       <c r="J19" s="55">
@@ -8155,7 +8196,7 @@
         <v>성장</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="G20" s="57"/>
       <c r="J20" s="55">
@@ -8188,7 +8229,7 @@
         <v>성장</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="G21" s="57"/>
       <c r="J21" s="55">
@@ -8221,7 +8262,7 @@
         <v>성장</v>
       </c>
       <c r="F22" s="53" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="G22" s="57"/>
       <c r="J22" s="55">
@@ -8235,7 +8276,7 @@
     </row>
     <row r="23" spans="1:12" ht="24" customHeight="1">
       <c r="A23" s="53" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B23" s="59">
         <f>SUMIFS(D1_당기기A!$E:$E,D1_당기기A!$C:$C,$A23)+SUMIFS(D2_밀기A!$E:$E,D2_밀기A!$C:$C,$A23)+SUMIFS(D3_하체A!$E:$E,D3_하체A!$C:$C,$A23)+SUMIFS(D4_어깨팔A!$E:$E,D4_어깨팔A!$C:$C,$A23)+SUMIFS(D6_당기기B!$E:$E,D6_당기기B!$C:$C,$A23)+SUMIFS(D7_밀기B!$E:$E,D7_밀기B!$C:$C,$A23)+SUMIFS(D8_하체B!$E:$E,D8_하체B!$C:$C,$A23)+SUMIFS(D9_어깨팔B!$E:$E,D9_어깨팔B!$C:$C,$A23)</f>
@@ -8254,7 +8295,7 @@
         <v>유지</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="G23" s="57"/>
       <c r="J23" s="55">
@@ -8287,7 +8328,7 @@
         <v>유지</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="G24" s="57"/>
       <c r="J24" s="55">
@@ -8301,7 +8342,7 @@
     </row>
     <row r="25" spans="1:12" ht="36" customHeight="1">
       <c r="A25" s="60" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B25" s="15">
         <f>SUM(B5:B24)</f>
@@ -8325,22 +8366,22 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="36" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="48" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="48" customHeight="1">
@@ -8348,22 +8389,22 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="48" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="48" customHeight="1">
       <c r="A34" s="11" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1">
@@ -8371,124 +8412,124 @@
     </row>
     <row r="36" spans="1:1" ht="48" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="77.25" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="48" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="39" customHeight="1">
       <c r="A39" s="63" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="45" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="48" customHeight="1">
       <c r="A41" s="11" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="48" customHeight="1">
       <c r="A42" s="11" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="48" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="48" customHeight="1">
       <c r="A44" s="90" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="51.75" customHeight="1">
       <c r="A45" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="90" customHeight="1">
       <c r="A46" s="11" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="51.75" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="48" customHeight="1">
       <c r="A48" s="11" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="48" customHeight="1">
       <c r="A49" s="11" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="48" customHeight="1">
       <c r="A50" s="11" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="93" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="100" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B58" s="100" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C58" s="100" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D58" s="100" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E58" s="100" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -8502,7 +8543,7 @@
         <v>239</v>
       </c>
       <c r="D59" s="102" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E59" s="102" t="s">
         <v>198</v>
@@ -8519,45 +8560,45 @@
         <v>239</v>
       </c>
       <c r="D60" s="107" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E60" s="107" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="104" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>
@@ -8607,50 +8648,50 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="64" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
       <c r="A6" s="64" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="63" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="A7" s="64" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C7" s="4">
         <v>2.25</v>
       </c>
       <c r="D7" s="63" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="H7">
         <f>SUM(D7:D10)</f>
@@ -8659,13 +8700,13 @@
     </row>
     <row r="8" spans="1:13" ht="84" customHeight="1">
       <c r="A8" s="64" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C8" s="4">
         <v>1.25</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -8673,40 +8714,40 @@
         <v>175</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="I9" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>675</v>
-      </c>
       <c r="K9" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L9" s="100" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="M9" s="100" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9061,17 +9102,17 @@
     </row>
     <row r="23" spans="1:13" ht="108" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="84" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="84" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="120" customHeight="1">
@@ -9079,52 +9120,52 @@
     </row>
     <row r="27" spans="1:13" ht="96" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="108" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="108" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="156" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="96" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -9145,45 +9186,45 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="66" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -9191,80 +9232,80 @@
         <v>84</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="67" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="67" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="36" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1">
@@ -9272,47 +9313,47 @@
     </row>
     <row r="19" spans="1:1" ht="36" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="36" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="48" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16.5" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16.5" customHeight="1">
       <c r="A25" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16.5" customHeight="1">
       <c r="A26" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16.5" customHeight="1">
       <c r="A27" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="16.5" customHeight="1">
       <c r="A28" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="16.5" customHeight="1">
       <c r="A30" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>
@@ -9338,31 +9379,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" s="70" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>195</v>
@@ -9371,111 +9412,111 @@
         <v>196</v>
       </c>
       <c r="G5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="71" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D6" s="71" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E6" s="71">
         <f>복귀_평일A_가슴!$E$12</f>
         <v>28</v>
       </c>
       <c r="F6" s="73" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="G6" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="E7" s="7">
         <f>복귀_평일B_어깨!$E$15</f>
         <v>35</v>
       </c>
       <c r="F7" s="69" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="G7" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
       <c r="A8" s="71" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B8" s="72" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D8" s="71" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E8" s="71">
         <f>복귀_토_하체!$E$14</f>
         <v>32</v>
       </c>
       <c r="F8" s="73" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="G8" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
       <c r="A9" s="71" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B9" s="72" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D9" s="71" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="E9" s="71">
         <f>복귀_일_등!$E$16</f>
         <v>33</v>
       </c>
       <c r="F9" s="73" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="G9" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="71" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C10" s="72" t="s">
         <v>198</v>
@@ -9490,7 +9531,7 @@
         <v>198</v>
       </c>
       <c r="G10" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
@@ -9505,7 +9546,7 @@
         <v>128</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -9526,32 +9567,32 @@
     </row>
     <row r="15" spans="1:7" ht="48" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="141" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="126" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="77.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="115.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="48" customHeight="1">
@@ -9559,22 +9600,22 @@
     </row>
     <row r="22" spans="1:1" ht="141" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="77.25" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="90" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="128.25" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="128.25" customHeight="1">
@@ -9582,32 +9623,32 @@
     </row>
     <row r="27" spans="1:1" ht="15" customHeight="1">
       <c r="A27" s="63" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="48" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="75" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="102.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="90" customHeight="1">
       <c r="A31" s="11" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="128.25" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="144" customHeight="1">
@@ -9615,77 +9656,77 @@
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1">
       <c r="A34" s="74" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
   </sheetData>
@@ -9716,53 +9757,53 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>140</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>195</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="29.25" customHeight="1">
@@ -9796,13 +9837,13 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="K5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="L5" s="68" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="29.25" customHeight="1">
@@ -9810,7 +9851,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C6" s="67" t="s">
         <v>46</v>
@@ -9836,13 +9877,13 @@
         <v>10.5</v>
       </c>
       <c r="J6" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="K6" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="L6" s="68" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -9862,7 +9903,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G7" s="53">
         <v>45</v>
@@ -9875,10 +9916,10 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="K7" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -9886,7 +9927,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>89</v>
@@ -9898,7 +9939,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G8" s="53">
         <v>40</v>
@@ -9911,10 +9952,10 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="K8" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -9922,7 +9963,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>68</v>
@@ -9947,10 +9988,10 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="K9" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -9958,19 +9999,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>94</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G10" s="53">
         <v>40</v>
@@ -9983,10 +10024,10 @@
         <v>10.7</v>
       </c>
       <c r="J10" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="K10" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -9994,10 +10035,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D11" s="77" t="s">
         <v>198</v>
@@ -10006,7 +10047,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G11" s="53">
         <v>40</v>
@@ -10019,10 +10060,10 @@
         <v>5.8</v>
       </c>
       <c r="J11" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="K11" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -10030,19 +10071,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="87" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C12" t="s">
         <v>56</v>
       </c>
       <c r="D12" s="76" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E12" s="28">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G12">
         <v>40</v>
@@ -10055,10 +10096,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="K12" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -10066,19 +10107,19 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C13" t="s">
         <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G13">
         <v>40</v>
@@ -10091,16 +10132,16 @@
         <v>6.7</v>
       </c>
       <c r="J13" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="K13" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="76.5" customHeight="1">
       <c r="A14" s="12"/>
       <c r="D14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E14">
         <f>SUM(E5:E13)</f>
@@ -10117,72 +10158,72 @@
     </row>
     <row r="16" spans="1:13" ht="293.25" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
   </sheetData>
@@ -10213,53 +10254,53 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>140</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>195</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="29.25" customHeight="1">
@@ -10293,10 +10334,10 @@
         <v>3.5</v>
       </c>
       <c r="J5" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="K5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -10304,19 +10345,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="89" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>63</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G6" s="53">
         <v>40</v>
@@ -10329,13 +10370,13 @@
         <v>12.7</v>
       </c>
       <c r="J6" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="K6" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="L6" s="53" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10343,7 +10384,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="89" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>61</v>
@@ -10355,7 +10396,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G7" s="53">
         <v>40</v>
@@ -10368,10 +10409,10 @@
         <v>12.7</v>
       </c>
       <c r="J7" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="K7" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10385,13 +10426,13 @@
         <v>61</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E8" s="7">
         <v>3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G8" s="53">
         <v>35</v>
@@ -10404,13 +10445,13 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J8" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="K8" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="L8" s="53" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="29.25" customHeight="1">
@@ -10418,19 +10459,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>63</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G9" s="53">
         <v>40</v>
@@ -10443,10 +10484,10 @@
         <v>5.8</v>
       </c>
       <c r="J9" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="K9" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -10454,19 +10495,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>106</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G10" s="53">
         <v>40</v>
@@ -10479,10 +10520,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="K10" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -10496,13 +10537,13 @@
         <v>100</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E11" s="7">
         <v>3</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G11" s="53">
         <v>40</v>
@@ -10515,13 +10556,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="K11" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="L11" s="53" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
@@ -10529,19 +10570,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>100</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E12" s="7">
         <v>3</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G12" s="53">
         <v>40</v>
@@ -10554,10 +10595,10 @@
         <v>7.3</v>
       </c>
       <c r="J12" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="K12" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
@@ -10571,13 +10612,13 @@
         <v>14</v>
       </c>
       <c r="D13" s="76" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E13" s="28">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G13">
         <v>40</v>
@@ -10590,10 +10631,10 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="K13" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -10601,7 +10642,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C14" t="s">
         <v>40</v>
@@ -10613,7 +10654,7 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G14">
         <v>40</v>
@@ -10626,10 +10667,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="K14" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="17.25" customHeight="1">
@@ -10637,7 +10678,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C15" t="s">
         <v>40</v>
@@ -10649,7 +10690,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G15">
         <v>40</v>
@@ -10662,17 +10703,17 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="K15" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="23.25" customHeight="1">
       <c r="A16" s="11"/>
       <c r="C16" s="88"/>
       <c r="D16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E16">
         <f>SUM(E5:E15)</f>
@@ -10688,112 +10729,112 @@
     </row>
     <row r="18" spans="1:1" ht="278.25" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1">
       <c r="A19" s="63" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="95.25" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="252.75" customHeight="1">
       <c r="A21" s="11" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="237.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="265.5" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="C44" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -10824,53 +10865,53 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>140</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>195</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
@@ -10884,13 +10925,13 @@
         <v>46</v>
       </c>
       <c r="D5" s="75" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E5" s="67">
         <v>4</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G5" s="68">
         <v>40</v>
@@ -10903,10 +10944,10 @@
         <v>10.7</v>
       </c>
       <c r="J5" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="K5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -10914,19 +10955,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>50</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G6" s="53">
         <v>40</v>
@@ -10939,10 +10980,10 @@
         <v>6.7</v>
       </c>
       <c r="J6" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="K6" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -10950,19 +10991,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>50</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G7" s="53">
         <v>60</v>
@@ -10975,10 +11016,10 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="K7" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -10986,19 +11027,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>56</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E8" s="7">
         <v>4</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G8" s="53">
         <v>40</v>
@@ -11011,10 +11052,10 @@
         <v>6.7</v>
       </c>
       <c r="J8" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="K8" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -11028,13 +11069,13 @@
         <v>56</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G9" s="53">
         <v>40</v>
@@ -11047,10 +11088,10 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="K9" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -11064,13 +11105,13 @@
         <v>14</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G10" s="53">
         <v>40</v>
@@ -11083,10 +11124,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="K10" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -11100,13 +11141,13 @@
         <v>76</v>
       </c>
       <c r="D11" s="76" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G11">
         <v>40</v>
@@ -11119,10 +11160,10 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="K11" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -11130,19 +11171,19 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="C12" t="s">
         <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G12">
         <v>60</v>
@@ -11155,10 +11196,10 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="K12" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
@@ -11166,7 +11207,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C13" t="s">
         <v>68</v>
@@ -11178,7 +11219,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G13">
         <v>40</v>
@@ -11191,10 +11232,10 @@
         <v>10.7</v>
       </c>
       <c r="J13" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="K13" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
@@ -11202,10 +11243,10 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D14">
         <v>2.5</v>
@@ -11214,7 +11255,7 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G14">
         <v>40</v>
@@ -11227,16 +11268,16 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="K14" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="25.5" customHeight="1">
       <c r="A15" s="11"/>
       <c r="D15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E15">
         <f>SUM(E5:E14)</f>
@@ -11249,72 +11290,72 @@
     </row>
     <row r="16" spans="1:13" ht="237.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -11345,53 +11386,53 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>140</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>195</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
@@ -11412,7 +11453,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G5" s="68">
         <v>30</v>
@@ -11425,13 +11466,13 @@
         <v>17.5</v>
       </c>
       <c r="J5" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="K5" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="L5" s="68" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
@@ -11445,13 +11486,13 @@
         <v>98</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E6" s="7">
         <v>5</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G6" s="53">
         <v>40</v>
@@ -11464,10 +11505,10 @@
         <v>15.8</v>
       </c>
       <c r="J6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="K6" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
@@ -11475,19 +11516,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>98</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G7" s="53">
         <v>40</v>
@@ -11500,10 +11541,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J7" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="K7" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
@@ -11523,7 +11564,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G8" s="53">
         <v>40</v>
@@ -11536,10 +11577,10 @@
         <v>12.7</v>
       </c>
       <c r="J8" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="K8" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
@@ -11547,7 +11588,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="89" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>61</v>
@@ -11559,7 +11600,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G9" s="53">
         <v>40</v>
@@ -11572,10 +11613,10 @@
         <v>10.7</v>
       </c>
       <c r="J9" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="K9" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
@@ -11583,19 +11624,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E10" s="7">
         <v>3</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G10" s="53">
         <v>40</v>
@@ -11608,10 +11649,10 @@
         <v>5.8</v>
       </c>
       <c r="J10" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="K10" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
@@ -11619,19 +11660,19 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="76" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E11" s="28">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G11">
         <v>40</v>
@@ -11644,15 +11685,15 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="K11" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="D12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E12">
         <f>SUM(E5:E11)</f>
@@ -11679,27 +11720,27 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="C27" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -11711,7 +11752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -11787,11 +11828,11 @@
       </c>
       <c r="E6" s="20">
         <f>INDEX(D2_밀기A!$E:$E,MATCH("세트 합계",D2_밀기A!$D:$D,0))</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F6" s="20" t="str">
         <f>"약 "&amp;INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))&amp;"분"</f>
-        <v>약 76분</v>
+        <v>약 70분</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
@@ -11809,11 +11850,11 @@
       </c>
       <c r="E7" s="20">
         <f>INDEX(D3_하체A!$E:$E,MATCH("세트 합계",D3_하체A!$D:$D,0))</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F7" s="20" t="str">
         <f>"약 "&amp;INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))&amp;"분"</f>
-        <v>약 77분</v>
+        <v>약 70분</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
@@ -11831,11 +11872,11 @@
       </c>
       <c r="E8" s="20">
         <f>INDEX(D4_어깨팔A!$E:$E,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))</f>
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F8" s="20" t="str">
         <f>"약 "&amp;INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))&amp;"분"</f>
-        <v>약 57분</v>
+        <v>약 70분</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
@@ -11873,11 +11914,11 @@
       </c>
       <c r="E10" s="20">
         <f>INDEX(D6_당기기B!$E:$E,MATCH("세트 합계",D6_당기기B!$D:$D,0))</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F10" s="20" t="str">
         <f>"약 "&amp;INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))&amp;"분"</f>
-        <v>약 63분</v>
+        <v>약 71분</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
@@ -11895,11 +11936,11 @@
       </c>
       <c r="E11" s="20">
         <f>INDEX(D7_밀기B!$E:$E,MATCH("세트 합계",D7_밀기B!$D:$D,0))</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F11" s="20" t="str">
         <f>"약 "&amp;INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))&amp;"분"</f>
-        <v>약 76분</v>
+        <v>약 70분</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
@@ -11917,11 +11958,11 @@
       </c>
       <c r="E12" s="20">
         <f>INDEX(D8_하체B!$E:$E,MATCH("세트 합계",D8_하체B!$D:$D,0))</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F12" s="20" t="str">
         <f>"약 "&amp;INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))&amp;"분"</f>
-        <v>약 80분</v>
+        <v>약 73분</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
@@ -11939,11 +11980,11 @@
       </c>
       <c r="E13" s="20">
         <f>INDEX(D9_어깨팔B!$E:$E,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F13" s="20" t="str">
         <f>"약 "&amp;INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))&amp;"분"</f>
-        <v>약 59분</v>
+        <v>약 67분</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -11979,7 +12020,7 @@
       </c>
       <c r="F15" t="str">
         <f>"약 "&amp;(INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))+INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))+INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))+INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))+INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))+INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))+INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))+INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0)))&amp;"분 ("&amp;INT((INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))+INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))+INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))+INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))+INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))+INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))+INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))+INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0)))/60)&amp;"시간 "&amp;MOD((INDEX(D1_당기기A!$I:$I,MATCH("세트 합계",D1_당기기A!$D:$D,0))+INDEX(D2_밀기A!$I:$I,MATCH("세트 합계",D2_밀기A!$D:$D,0))+INDEX(D3_하체A!$I:$I,MATCH("세트 합계",D3_하체A!$D:$D,0))+INDEX(D4_어깨팔A!$I:$I,MATCH("세트 합계",D4_어깨팔A!$D:$D,0))+INDEX(D6_당기기B!$I:$I,MATCH("세트 합계",D6_당기기B!$D:$D,0))+INDEX(D7_밀기B!$I:$I,MATCH("세트 합계",D7_밀기B!$D:$D,0))+INDEX(D8_하체B!$I:$I,MATCH("세트 합계",D8_하체B!$D:$D,0))+INDEX(D9_어깨팔B!$I:$I,MATCH("세트 합계",D9_어깨팔B!$D:$D,0))),60)&amp;"분)"</f>
-        <v>약 558분 (9시간 18분)</v>
+        <v>약 561분 (9시간 21분)</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="89.25" customHeight="1"/>
@@ -12066,14 +12107,14 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="15" customHeight="1"/>
-    <row r="35" spans="1:1" ht="90" customHeight="1">
-      <c r="A35" s="13" t="s">
+    <row r="34" spans="1:1" ht="15" customHeight="1">
+      <c r="A34" t="s">
         <v>236</v>
       </c>
     </row>
+    <row r="35" spans="1:1" ht="90" customHeight="1"/>
     <row r="36" spans="1:1" ht="51.75" customHeight="1">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="13" t="s">
         <v>237</v>
       </c>
     </row>
@@ -12098,15 +12139,15 @@
       </c>
     </row>
     <row r="41" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A41" s="30"/>
+      <c r="A41" s="30" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="42" spans="1:1" ht="242.25" customHeight="1">
-      <c r="A42" s="13" t="s">
-        <v>242</v>
-      </c>
+      <c r="A42" s="30"/>
     </row>
     <row r="43" spans="1:1" ht="270.75" customHeight="1">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="13" t="s">
         <v>243</v>
       </c>
     </row>
@@ -12136,15 +12177,15 @@
       </c>
     </row>
     <row r="49" spans="1:1" ht="327.75" customHeight="1">
-      <c r="A49" s="32"/>
+      <c r="A49" s="30" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="50" spans="1:1" ht="256.5" customHeight="1">
-      <c r="A50" s="13" t="s">
-        <v>249</v>
-      </c>
+      <c r="A50" s="32"/>
     </row>
     <row r="51" spans="1:1" ht="409.5" customHeight="1">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="13" t="s">
         <v>250</v>
       </c>
     </row>
@@ -12164,15 +12205,15 @@
       </c>
     </row>
     <row r="55" spans="1:1" ht="185.25" customHeight="1">
-      <c r="A55" s="31"/>
+      <c r="A55" s="30" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="56" spans="1:1" ht="60" customHeight="1">
-      <c r="A56" s="13" t="s">
-        <v>254</v>
-      </c>
+      <c r="A56" s="31"/>
     </row>
     <row r="57" spans="1:1" ht="256.5" customHeight="1">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="13" t="s">
         <v>255</v>
       </c>
     </row>
@@ -12202,12 +12243,12 @@
       </c>
     </row>
     <row r="63" spans="1:1" ht="90" customHeight="1">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="30" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="313.5" customHeight="1">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="13" t="s">
         <v>262</v>
       </c>
     </row>
@@ -12216,14 +12257,14 @@
         <v>263</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="285" customHeight="1"/>
-    <row r="67" spans="1:1" ht="370.5" customHeight="1">
-      <c r="A67" s="13" t="s">
+    <row r="66" spans="1:1" ht="285" customHeight="1">
+      <c r="A66" s="30" t="s">
         <v>264</v>
       </c>
     </row>
+    <row r="67" spans="1:1" ht="370.5" customHeight="1"/>
     <row r="68" spans="1:1" ht="256.5" customHeight="1">
-      <c r="A68" s="30" t="s">
+      <c r="A68" s="13" t="s">
         <v>265</v>
       </c>
     </row>
@@ -12242,14 +12283,14 @@
         <v>268</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="327.75" customHeight="1"/>
-    <row r="73" spans="1:1" ht="90" customHeight="1">
-      <c r="A73" s="13" t="s">
+    <row r="72" spans="1:1" ht="327.75" customHeight="1">
+      <c r="A72" s="30" t="s">
         <v>269</v>
       </c>
     </row>
+    <row r="73" spans="1:1" ht="90" customHeight="1"/>
     <row r="74" spans="1:1" ht="75" customHeight="1">
-      <c r="A74" s="30" t="s">
+      <c r="A74" s="13" t="s">
         <v>270</v>
       </c>
     </row>
@@ -12293,13 +12334,14 @@
         <v>278</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="75" customHeight="1">
-      <c r="A84" s="13" t="s">
+    <row r="83" spans="1:1" ht="327.75">
+      <c r="A83" s="30" t="s">
         <v>279</v>
       </c>
     </row>
+    <row r="84" spans="1:1" ht="75" customHeight="1"/>
     <row r="85" spans="1:1" ht="327.75" customHeight="1">
-      <c r="A85" s="30" t="s">
+      <c r="A85" s="13" t="s">
         <v>280</v>
       </c>
     </row>
@@ -12326,6 +12368,11 @@
     <row r="90" spans="1:1" ht="242.25" customHeight="1">
       <c r="A90" s="30" t="s">
         <v>285</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="242.25">
+      <c r="A91" s="30" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -12347,166 +12394,166 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="D5" s="69" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D8" s="53" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>198</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1">
       <c r="A13" s="79" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B13" s="80" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C13" s="80" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D13" s="79" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B14" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C14" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D14" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
@@ -12517,22 +12564,22 @@
     </row>
     <row r="17" spans="1:1" ht="51.75" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="39" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="39" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="51.75" customHeight="1">
@@ -12540,137 +12587,137 @@
     </row>
     <row r="22" spans="1:1" ht="39" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1">
       <c r="A23" s="63" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="51.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="39" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
   </sheetData>
@@ -12696,12 +12743,12 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -12715,12 +12762,12 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
@@ -12746,7 +12793,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -12769,15 +12816,15 @@
         <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B8" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -12797,15 +12844,15 @@
         <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B9" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -12825,15 +12872,15 @@
         <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B10" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -12853,12 +12900,12 @@
         <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -12881,12 +12928,12 @@
         <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B12" t="s">
         <v>150</v>
@@ -12909,12 +12956,12 @@
         <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -12937,12 +12984,12 @@
         <v>36</v>
       </c>
       <c r="H13" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B15" t="s">
         <v>52</v>
@@ -12965,15 +13012,15 @@
         <v>36</v>
       </c>
       <c r="H15" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B16" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
@@ -12993,12 +13040,12 @@
         <v>36</v>
       </c>
       <c r="H16" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B17" t="s">
         <v>28</v>
@@ -13021,12 +13068,12 @@
         <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B18" t="s">
         <v>150</v>
@@ -13049,12 +13096,12 @@
         <v>36</v>
       </c>
       <c r="H18" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -13077,12 +13124,12 @@
         <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
@@ -13105,15 +13152,15 @@
         <v>36</v>
       </c>
       <c r="H20" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B21" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C21" t="s">
         <v>50</v>
@@ -13133,12 +13180,12 @@
         <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
@@ -13161,15 +13208,15 @@
         <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B23" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C23" t="s">
         <v>61</v>
@@ -13189,15 +13236,15 @@
         <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B24" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C24" t="s">
         <v>63</v>
@@ -13217,12 +13264,12 @@
         <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B25" t="s">
         <v>65</v>
@@ -13245,15 +13292,15 @@
         <v>36</v>
       </c>
       <c r="H25" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B26" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C26" t="s">
         <v>63</v>
@@ -13273,15 +13320,15 @@
         <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B27" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C27" t="s">
         <v>63</v>
@@ -13301,15 +13348,15 @@
         <v>36</v>
       </c>
       <c r="H27" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B28" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C28" t="s">
         <v>102</v>
@@ -13329,15 +13376,15 @@
         <v>36</v>
       </c>
       <c r="H28" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B29" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C29" t="s">
         <v>102</v>
@@ -13357,12 +13404,12 @@
         <v>36</v>
       </c>
       <c r="H29" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B30" t="s">
         <v>148</v>
@@ -13385,12 +13432,12 @@
         <v>36</v>
       </c>
       <c r="H30" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -13413,15 +13460,15 @@
         <v>36</v>
       </c>
       <c r="H31" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B32" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C32" t="s">
         <v>106</v>
@@ -13441,12 +13488,12 @@
         <v>36</v>
       </c>
       <c r="H32" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B33" t="s">
         <v>146</v>
@@ -13469,15 +13516,15 @@
         <v>36</v>
       </c>
       <c r="H33" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B34" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C34" t="s">
         <v>84</v>
@@ -13497,15 +13544,15 @@
         <v>36</v>
       </c>
       <c r="H34" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B35" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C35" t="s">
         <v>84</v>
@@ -13525,12 +13572,12 @@
         <v>36</v>
       </c>
       <c r="H35" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B36" t="s">
         <v>146</v>
@@ -13558,7 +13605,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B37" t="s">
         <v>148</v>
@@ -13581,12 +13628,12 @@
         <v>36</v>
       </c>
       <c r="H37" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B38" t="s">
         <v>78</v>
@@ -13614,7 +13661,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B39" t="s">
         <v>67</v>
@@ -13637,12 +13684,12 @@
         <v>36</v>
       </c>
       <c r="H39" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B40" t="s">
         <v>148</v>
@@ -13665,12 +13712,12 @@
         <v>36</v>
       </c>
       <c r="H40" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B41" t="s">
         <v>146</v>
@@ -13693,12 +13740,12 @@
         <v>36</v>
       </c>
       <c r="H41" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B42" t="s">
         <v>78</v>
@@ -13721,12 +13768,12 @@
         <v>36</v>
       </c>
       <c r="H42" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B43" t="s">
         <v>39</v>
@@ -13754,7 +13801,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B44" t="s">
         <v>42</v>
@@ -13782,7 +13829,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B45" t="s">
         <v>150</v>
@@ -13805,12 +13852,12 @@
         <v>36</v>
       </c>
       <c r="H45" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B46" t="s">
         <v>33</v>
@@ -13833,12 +13880,12 @@
         <v>36</v>
       </c>
       <c r="H46" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B47" t="s">
         <v>148</v>
@@ -13861,18 +13908,18 @@
         <v>36</v>
       </c>
       <c r="H47" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B48" t="s">
         <v>146</v>
       </c>
       <c r="C48" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -13889,18 +13936,18 @@
         <v>36</v>
       </c>
       <c r="H48" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B49" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C49" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -13917,15 +13964,15 @@
         <v>36</v>
       </c>
       <c r="H49" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B50" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C50" t="s">
         <v>100</v>
@@ -13945,15 +13992,15 @@
         <v>36</v>
       </c>
       <c r="H50" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B51" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C51" t="s">
         <v>46</v>
@@ -13973,7 +14020,7 @@
         <v>36</v>
       </c>
       <c r="H51" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
   </sheetData>
@@ -13999,35 +14046,35 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B4" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D4" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F4" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="G4" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -14051,13 +14098,13 @@
         <v>충분</v>
       </c>
       <c r="F5" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="G5" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="H5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="I5">
         <f ca="1">SUM(D5:D6)</f>
@@ -14085,10 +14132,10 @@
         <v>충분</v>
       </c>
       <c r="F6" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="G6" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -14112,13 +14159,13 @@
         <v>충분</v>
       </c>
       <c r="F7" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="G7" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="H7" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="I7">
         <f ca="1">SUM(D7:D10)</f>
@@ -14146,10 +14193,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F8" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="G8" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -14173,10 +14220,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F9" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="G9" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -14200,10 +14247,10 @@
         <v>충분</v>
       </c>
       <c r="F10" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="G10" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -14227,10 +14274,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F11" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="G11" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -14254,10 +14301,10 @@
         <v>충분</v>
       </c>
       <c r="F12" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="G12" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -14281,10 +14328,10 @@
         <v>충분</v>
       </c>
       <c r="F13" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="G13" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -14308,10 +14355,10 @@
         <v>충분</v>
       </c>
       <c r="F14" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="G14" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -14335,13 +14382,13 @@
         <v>충분</v>
       </c>
       <c r="F15" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="G15" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="H15" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="I15">
         <f ca="1">SUM(D15:D16,D19)</f>
@@ -14369,10 +14416,10 @@
         <v>하한</v>
       </c>
       <c r="F16" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="G16" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -14396,10 +14443,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F17" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="G17" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -14423,15 +14470,15 @@
         <v>보완 필요</v>
       </c>
       <c r="F18" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="G18" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B19">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A19)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A19)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A19)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A19)</f>
@@ -14450,10 +14497,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F19" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="G19" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -14477,10 +14524,10 @@
         <v>충분</v>
       </c>
       <c r="F20" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="G20" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -14504,10 +14551,10 @@
         <v>충분</v>
       </c>
       <c r="F21" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="G21" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -14531,15 +14578,15 @@
         <v>하한</v>
       </c>
       <c r="F22" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="G22" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B23">
         <f>SUMIFS(복귀_평일A_가슴!$E:$E,복귀_평일A_가슴!$C:$C,$A23)+SUMIFS(복귀_평일B_어깨!$E:$E,복귀_평일B_어깨!$C:$C,$A23)+SUMIFS(복귀_토_하체!$E:$E,복귀_토_하체!$C:$C,$A23)+SUMIFS(복귀_일_등!$E:$E,복귀_일_등!$C:$C,$A23)</f>
@@ -14558,10 +14605,10 @@
         <v>보완 필요</v>
       </c>
       <c r="F23" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="G23" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -14585,15 +14632,15 @@
         <v>보완 필요</v>
       </c>
       <c r="F24" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="G24" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B25">
         <f>SUM(B5:B24)</f>
@@ -14606,67 +14653,67 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -14694,66 +14741,66 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="33" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" s="35" t="s">
         <v>140</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E5" s="35" t="s">
         <v>195</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" customHeight="1">
@@ -14773,7 +14820,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G6" s="26">
         <v>35</v>
@@ -14789,13 +14836,13 @@
         <v>14</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" customHeight="1">
@@ -14815,7 +14862,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G7" s="26">
         <v>40</v>
@@ -14831,10 +14878,10 @@
         <v>14</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" customHeight="1">
@@ -14848,13 +14895,13 @@
         <v>63</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E8" s="20">
         <v>4</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G8" s="26">
         <v>40</v>
@@ -14867,13 +14914,13 @@
         <v>10.7</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1">
@@ -14893,7 +14940,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G9" s="26">
         <v>45</v>
@@ -14906,13 +14953,13 @@
         <v>5.3</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1">
@@ -14926,13 +14973,13 @@
         <v>14</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E10" s="20">
         <v>0</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G10" s="26">
         <v>40</v>
@@ -14948,10 +14995,10 @@
         <v>40</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
@@ -14959,19 +15006,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="81" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E11" s="20">
         <v>4</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G11" s="26">
         <v>40</v>
@@ -14985,10 +15032,10 @@
       </c>
       <c r="J11" s="21"/>
       <c r="K11" s="21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L11" s="86" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1">
@@ -14996,19 +15043,19 @@
         <v>7</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E12" s="20">
         <v>3</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G12" s="26">
         <v>70</v>
@@ -15022,10 +15069,10 @@
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L12" s="86" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
@@ -15033,19 +15080,19 @@
         <v>8</v>
       </c>
       <c r="B13" s="81" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E13" s="20">
         <v>3</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G13" s="26">
         <v>40</v>
@@ -15059,10 +15106,10 @@
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L13" s="86" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
@@ -15082,7 +15129,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G14" s="26">
         <v>45</v>
@@ -15095,13 +15142,13 @@
         <v>6.8</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L14" s="36" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -15109,19 +15156,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>84</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E15" s="20">
         <v>3</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G15" s="26">
         <v>40</v>
@@ -15135,10 +15182,10 @@
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="36" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -15146,7 +15193,7 @@
       <c r="B16" s="21"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E16" s="20">
         <f>SUM(E6:E15)</f>
@@ -15169,13 +15216,13 @@
     </row>
     <row r="33" spans="10:10">
       <c r="J33" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="A6:N15">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15206,25 +15253,25 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>195</v>
@@ -15292,76 +15339,76 @@
     </row>
     <row r="11" spans="1:3" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.5" customHeight="1">
       <c r="A14" s="31" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" customHeight="1">
       <c r="A15" s="31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.5" customHeight="1">
       <c r="A16" s="31" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="16.5" customHeight="1">
       <c r="A19" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B19" s="35" t="s">
         <v>140</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E19" s="35" t="s">
         <v>195</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I19" s="35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J19" s="35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K19" s="35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L19" s="35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M19" s="35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N19" s="35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="16.5" customHeight="1">
@@ -15382,7 +15429,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G20" s="38">
         <v>30</v>
@@ -15391,20 +15438,20 @@
         <v>180</v>
       </c>
       <c r="I20" s="38">
-        <f t="shared" ref="I20:I26" si="0">IF(E20=0,0,ROUND(E20*(G20+H20)/60,1))</f>
+        <f t="shared" ref="I20:I25" si="0">IF(E20=0,0,ROUND(E20*(G20+H20)/60,1))</f>
         <v>17.5</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K20" s="39" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L20" s="39" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M20" s="38" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1">
@@ -15418,13 +15465,13 @@
         <v>100</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E21" s="20">
         <v>4</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G21" s="26">
         <v>40</v>
@@ -15440,13 +15487,13 @@
         <v>26</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L21" s="36" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M21" s="26" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="16.5" customHeight="1">
@@ -15460,13 +15507,13 @@
         <v>98</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E22" s="20">
         <v>3</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G22" s="26">
         <v>40</v>
@@ -15479,13 +15526,13 @@
         <v>9.5</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M22" s="92"/>
     </row>
@@ -15494,7 +15541,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>98</v>
@@ -15506,7 +15553,7 @@
         <v>4</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G23" s="26">
         <v>40</v>
@@ -15520,10 +15567,10 @@
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
@@ -15531,36 +15578,36 @@
         <v>5</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>100</v>
+        <v>370</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="D24" s="26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E24" s="20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="G24" s="26">
         <v>40</v>
       </c>
       <c r="H24" s="26">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="I24" s="26">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="J24" s="21"/>
       <c r="K24" s="21" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
@@ -15568,19 +15615,19 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>50</v>
+        <v>109</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="D25" s="26">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E25" s="20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G25" s="26">
         <v>40</v>
@@ -15590,74 +15637,35 @@
       </c>
       <c r="I25" s="26">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J25" s="21"/>
-      <c r="K25" s="21" t="s">
+      <c r="K25" s="21"/>
+      <c r="L25" s="86" t="s">
         <v>373</v>
       </c>
-      <c r="L25" s="21" t="s">
-        <v>374</v>
-      </c>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A26" s="20">
-        <v>7</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="26">
-        <v>20</v>
-      </c>
-      <c r="E26" s="20">
-        <v>5</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="G26" s="26">
-        <v>40</v>
-      </c>
-      <c r="H26" s="26">
+      <c r="D26" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E26" s="27">
+        <f>SUM(E20:E25)</f>
+        <v>27</v>
+      </c>
+      <c r="I26">
+        <f>ROUND(SUM(I20:I25),0)</f>
         <v>70</v>
       </c>
-      <c r="I26" s="26">
-        <f t="shared" si="0"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="86" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="16.5" customHeight="1">
-      <c r="D27" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E27" s="27">
-        <f>SUM(E20:E26)</f>
-        <v>30</v>
-      </c>
-      <c r="I27">
-        <f>ROUND(SUM(I20:I26),0)</f>
-        <v>76</v>
-      </c>
-    </row>
+    </row>
+    <row r="27" spans="1:14" ht="16.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A20:N26">
-    <cfRule type="expression" dxfId="10" priority="1">
+  <conditionalFormatting sqref="A20:N25">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$E20=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="L26" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -15682,25 +15690,25 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>195</v>
@@ -15768,56 +15776,56 @@
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
       <c r="A14" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>140</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E14" s="35" t="s">
         <v>195</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K14" s="35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L14" s="35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M14" s="35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N14" s="35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1">
@@ -15838,7 +15846,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G15" s="38">
         <v>35</v>
@@ -15847,20 +15855,20 @@
         <v>193</v>
       </c>
       <c r="I15" s="38">
-        <f t="shared" ref="I15:I22" si="0">IF(E15=0,0,ROUND(E15*(G15+H15)/60,1))</f>
+        <f t="shared" ref="I15:I21" si="0">IF(E15=0,0,ROUND(E15*(G15+H15)/60,1))</f>
         <v>19</v>
       </c>
       <c r="J15" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="K15" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="L15" s="39" t="s">
         <v>379</v>
       </c>
-      <c r="K15" s="39" t="s">
+      <c r="M15" s="38" t="s">
         <v>380</v>
-      </c>
-      <c r="L15" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="M15" s="38" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -15880,7 +15888,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G16" s="26">
         <v>45</v>
@@ -15896,10 +15904,10 @@
         <v>76</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="16.5" customHeight="1">
@@ -15913,13 +15921,13 @@
         <v>76</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E17" s="20">
         <v>3</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G17" s="26">
         <v>90</v>
@@ -15932,13 +15940,13 @@
         <v>12</v>
       </c>
       <c r="J17" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="L17" s="21" t="s">
         <v>386</v>
-      </c>
-      <c r="K17" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="L17" s="21" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.5" customHeight="1">
@@ -15946,7 +15954,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>68</v>
@@ -15958,7 +15966,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G18" s="26">
         <v>40</v>
@@ -15972,10 +15980,10 @@
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="16.5" customHeight="1">
@@ -15983,7 +15991,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>94</v>
@@ -15995,7 +16003,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G19" s="26">
         <v>40</v>
@@ -16009,13 +16017,13 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="N19" t="s">
         <v>393</v>
-      </c>
-      <c r="L19" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="N19" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="16.5" customHeight="1">
@@ -16023,19 +16031,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>91</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E20" s="20">
         <v>4</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G20" s="26">
         <v>40</v>
@@ -16049,112 +16057,71 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1">
       <c r="A21" s="20">
         <v>7</v>
       </c>
-      <c r="B21" s="21" t="s">
-        <v>330</v>
+      <c r="B21" s="81" t="s">
+        <v>397</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="D21" s="26">
+        <v>323</v>
+      </c>
+      <c r="D21" s="82" t="s">
+        <v>310</v>
+      </c>
+      <c r="E21" s="20">
+        <v>3</v>
+      </c>
+      <c r="F21" s="26">
         <v>10</v>
-      </c>
-      <c r="E21" s="20">
-        <v>4</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>314</v>
       </c>
       <c r="G21" s="26">
         <v>40</v>
       </c>
       <c r="H21" s="26">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I21" s="26">
         <f t="shared" si="0"/>
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="L21" s="21" t="s">
         <v>399</v>
       </c>
-      <c r="L21" s="21" t="s">
-        <v>400</v>
-      </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1">
-      <c r="A22" s="20">
-        <v>8</v>
-      </c>
-      <c r="B22" s="81" t="s">
-        <v>401</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="D22" s="82" t="s">
-        <v>309</v>
-      </c>
-      <c r="E22" s="20">
-        <v>3</v>
-      </c>
-      <c r="F22" s="26">
-        <v>10</v>
-      </c>
-      <c r="G22" s="26">
-        <v>40</v>
-      </c>
-      <c r="H22" s="26">
-        <v>60</v>
-      </c>
-      <c r="I22" s="26">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="L22" s="21" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1">
-      <c r="D23" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E23" s="27">
-        <f>SUM(E15:E22)</f>
-        <v>30</v>
-      </c>
-      <c r="I23">
-        <f>ROUND(SUM(I15:I22),0)</f>
-        <v>77</v>
-      </c>
-    </row>
+      <c r="D22" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E22" s="27">
+        <f>SUM(E15:E21)</f>
+        <v>26</v>
+      </c>
+      <c r="I22">
+        <f>ROUND(SUM(I15:I21),0)</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A15:N21 A22 C22:N22">
-    <cfRule type="expression" dxfId="9" priority="1">
+  <conditionalFormatting sqref="A15:N21">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$E15=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="expression" dxfId="8" priority="2">
-      <formula>$E22=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -16181,66 +16148,66 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1">
       <c r="A3" s="33" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" s="35" t="s">
         <v>140</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E5" s="35" t="s">
         <v>195</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" customHeight="1">
@@ -16248,7 +16215,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>50</v>
@@ -16260,7 +16227,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G6" s="26">
         <v>40</v>
@@ -16269,15 +16236,15 @@
         <v>70</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I14" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I16" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
         <v>5.5</v>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" customHeight="1">
@@ -16297,7 +16264,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G7" s="26">
         <v>40</v>
@@ -16313,10 +16280,10 @@
         <v>102</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" customHeight="1">
@@ -16330,13 +16297,13 @@
         <v>56</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E8" s="20">
         <v>3</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G8" s="26">
         <v>40</v>
@@ -16349,13 +16316,13 @@
         <v>5.5</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1">
@@ -16375,7 +16342,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G9" s="26">
         <v>40</v>
@@ -16388,13 +16355,13 @@
         <v>6</v>
       </c>
       <c r="J9" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="L9" s="21" t="s">
         <v>412</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>415</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1">
@@ -16402,36 +16369,36 @@
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>417</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>26</v>
+        <v>413</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>100</v>
       </c>
       <c r="D10" s="26">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E10" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="G10" s="26">
         <v>40</v>
       </c>
       <c r="H10" s="26">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I10" s="26">
         <f t="shared" si="0"/>
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
@@ -16439,115 +16406,114 @@
         <v>6</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>14</v>
+        <v>416</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E11" s="20">
         <v>3</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>306</v>
+        <v>367</v>
       </c>
       <c r="G11" s="26">
         <v>40</v>
       </c>
       <c r="H11" s="26">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I11" s="26">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1">
       <c r="A12" s="20">
         <v>7</v>
       </c>
-      <c r="B12" s="81" t="s">
-        <v>423</v>
+      <c r="B12" s="21" t="s">
+        <v>420</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="20">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="D12" s="26">
+        <v>20</v>
       </c>
       <c r="E12" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>424</v>
+        <v>327</v>
       </c>
       <c r="G12" s="26">
         <v>40</v>
       </c>
       <c r="H12" s="26">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I12" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
       <c r="A13" s="20">
         <v>8</v>
       </c>
-      <c r="B13" s="81" t="s">
-        <v>392</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>427</v>
+      <c r="B13" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>423</v>
       </c>
       <c r="E13" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="G13" s="26">
         <v>40</v>
       </c>
       <c r="H13" s="26">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="I13" s="26">
         <f t="shared" si="0"/>
-        <v>4.2</v>
-      </c>
-      <c r="J13" s="21"/>
+        <v>5.5</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>40</v>
+      </c>
       <c r="K13" s="21" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>429</v>
-      </c>
-      <c r="N13" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
@@ -16555,107 +16521,186 @@
         <v>9</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>318</v>
+        <v>40</v>
+      </c>
+      <c r="D14" s="20">
+        <v>10</v>
       </c>
       <c r="E14" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>314</v>
+        <v>427</v>
       </c>
       <c r="G14" s="26">
         <v>40</v>
       </c>
       <c r="H14" s="26">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="I14" s="26">
         <f t="shared" si="0"/>
-        <v>12.1</v>
+        <v>5</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A15" s="20">
+        <v>10</v>
+      </c>
+      <c r="B15" s="81" t="s">
+        <v>390</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>430</v>
       </c>
-      <c r="L14" s="21" t="s">
+      <c r="E15" s="20">
+        <v>5</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="G15" s="26">
+        <v>40</v>
+      </c>
+      <c r="H15" s="26">
+        <v>10</v>
+      </c>
+      <c r="I15" s="26">
+        <f t="shared" si="0"/>
+        <v>4.2</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="N14" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.5" customHeight="1">
-      <c r="D15" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E15" s="27">
-        <f>SUM(E6:E14)</f>
-        <v>32</v>
-      </c>
-      <c r="I15">
-        <f>ROUND(SUM(I6:I14),0)</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="16.5" customHeight="1"/>
-    <row r="17" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A17" s="108" t="s">
+      <c r="L15" s="21" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A18" s="109" t="s">
+      <c r="N15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A16" s="20">
+        <v>11</v>
+      </c>
+      <c r="B16" s="81" t="s">
+        <v>394</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="E16" s="20">
+        <v>5</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="G16" s="26">
+        <v>40</v>
+      </c>
+      <c r="H16" s="26">
+        <v>105</v>
+      </c>
+      <c r="I16" s="26">
+        <f t="shared" si="0"/>
+        <v>12.1</v>
+      </c>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A19" s="109" t="s">
+      <c r="L16" s="21" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" ht="16.5" customHeight="1">
+      <c r="N16" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="16.5" customHeight="1">
+      <c r="D17" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E17" s="27">
+        <f>SUM(E6:E16)</f>
+        <v>38</v>
+      </c>
+      <c r="I17">
+        <f>ROUND(SUM(I6:I16),0)</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="19" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A19" s="108" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="16.5" customHeight="1">
       <c r="A20" s="109" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A21" s="109" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16.5" customHeight="1">
+    <row r="21" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A21" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="16.5" customHeight="1">
       <c r="A22" s="109" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="16.5" customHeight="1">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="16.5" customHeight="1">
       <c r="A23" s="109" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A24" s="108" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="16.5" customHeight="1">
+    <row r="24" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A24" s="109" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="16.5" customHeight="1">
       <c r="A25" s="109" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="27" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="28" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="29" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="30" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="31" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="32" spans="1:1" ht="16.5" customHeight="1"/>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A26" s="109" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A27" s="108" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A28" s="109" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="30" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="31" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="32" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="33" ht="16.5" customHeight="1"/>
     <row r="34" ht="16.5" customHeight="1"/>
     <row r="35" ht="16.5" customHeight="1"/>
@@ -16666,7 +16711,7 @@
     <row r="40" ht="16.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N14">
+  <conditionalFormatting sqref="A6:N16">
     <cfRule type="expression" dxfId="7" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
@@ -16677,7 +16722,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -16694,66 +16739,66 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="33" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B5" s="35" t="s">
         <v>140</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E5" s="35" t="s">
         <v>195</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" customHeight="1">
@@ -16773,7 +16818,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G6" s="26">
         <v>40</v>
@@ -16782,17 +16827,17 @@
         <v>150</v>
       </c>
       <c r="I6" s="26">
-        <f t="shared" ref="I6:I14" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
+        <f t="shared" ref="I6:I15" si="0">IF(E6=0,0,ROUND(E6*(G6+H6)/60,1))</f>
         <v>12.7</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" customHeight="1">
@@ -16812,7 +16857,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G7" s="26">
         <v>40</v>
@@ -16825,13 +16870,13 @@
         <v>12.7</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" customHeight="1">
@@ -16839,7 +16884,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>63</v>
@@ -16851,7 +16896,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G8" s="26">
         <v>40</v>
@@ -16864,13 +16909,13 @@
         <v>6.7</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.5" customHeight="1">
@@ -16884,13 +16929,13 @@
         <v>56</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E9" s="20">
         <v>0</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G9" s="26">
         <v>40</v>
@@ -16903,13 +16948,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" customHeight="1">
@@ -16929,7 +16974,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G10" s="26">
         <v>40</v>
@@ -16945,10 +16990,10 @@
         <v>40</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
@@ -16968,7 +17013,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G11" s="26">
         <v>40</v>
@@ -16981,13 +17026,13 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1">
@@ -16995,19 +17040,19 @@
         <v>7</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>106</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E12" s="20">
         <v>3</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G12" s="26">
         <v>40</v>
@@ -17021,47 +17066,47 @@
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1">
       <c r="A13" s="20">
         <v>8</v>
       </c>
-      <c r="B13" s="85" t="s">
-        <v>464</v>
+      <c r="B13" s="21" t="s">
+        <v>331</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="D13" s="20">
-        <v>15</v>
+        <v>332</v>
+      </c>
+      <c r="D13" s="26">
+        <v>10</v>
       </c>
       <c r="E13" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="G13" s="26">
         <v>40</v>
       </c>
       <c r="H13" s="26">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I13" s="26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7.7</v>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
@@ -17069,19 +17114,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>339</v>
+        <v>470</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>309</v>
+        <v>323</v>
+      </c>
+      <c r="D14" s="20">
+        <v>15</v>
       </c>
       <c r="E14" s="20">
         <v>3</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="G14" s="26">
         <v>40</v>
@@ -17095,33 +17140,69 @@
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16.5" customHeight="1">
+      <c r="A15" s="20">
+        <v>10</v>
+      </c>
+      <c r="B15" s="85" t="s">
         <v>340</v>
       </c>
-      <c r="L14" s="21" t="s">
+      <c r="C15" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="E15" s="20">
+        <v>3</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="G15" s="26">
+        <v>40</v>
+      </c>
+      <c r="H15" s="26">
+        <v>60</v>
+      </c>
+      <c r="I15" s="26">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.5" customHeight="1">
-      <c r="D15" s="3" t="s">
+      <c r="L15" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="E15" s="27">
-        <f>SUM(E6:E14)</f>
-        <v>29</v>
-      </c>
-      <c r="I15">
-        <f>ROUND(SUM(I6:I14),0)</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1">
+      <c r="D16" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E16" s="27">
+        <f>SUM(E6:E15)</f>
+        <v>33</v>
+      </c>
+      <c r="I16">
+        <f>ROUND(SUM(I6:I15),0)</f>
+        <v>71</v>
+      </c>
+    </row>
     <row r="17" spans="2:2" ht="15" customHeight="1"/>
-    <row r="21" spans="2:2">
-      <c r="B21" s="83"/>
+    <row r="22" spans="2:2">
+      <c r="B22" s="83"/>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A6:N14">
+  <conditionalFormatting sqref="A6:N15">
     <cfRule type="expression" dxfId="6" priority="1">
       <formula>$E6=0</formula>
     </cfRule>
@@ -17150,25 +17231,25 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>195</v>
@@ -17236,76 +17317,76 @@
     </row>
     <row r="11" spans="1:3" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.5" customHeight="1">
       <c r="A14" s="31" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" customHeight="1">
       <c r="A15" s="31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.5" customHeight="1">
       <c r="A16" s="31" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="16.5" customHeight="1">
       <c r="A19" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B19" s="35" t="s">
         <v>140</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E19" s="35" t="s">
         <v>195</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I19" s="35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J19" s="35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K19" s="35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L19" s="35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M19" s="35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N19" s="35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="16.5" customHeight="1">
@@ -17326,7 +17407,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G20" s="38">
         <v>30</v>
@@ -17335,20 +17416,20 @@
         <v>180</v>
       </c>
       <c r="I20" s="38">
-        <f t="shared" ref="I20:I28" si="0">IF(E20=0,0,ROUND(E20*(G20+H20)/60,1))</f>
+        <f t="shared" ref="I20:I27" si="0">IF(E20=0,0,ROUND(E20*(G20+H20)/60,1))</f>
         <v>10.5</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="K20" s="39" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="L20" s="39" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="M20" s="38" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16.5" customHeight="1">
@@ -17368,7 +17449,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G21" s="26">
         <v>40</v>
@@ -17381,13 +17462,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="21" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="16.5" customHeight="1">
@@ -17395,7 +17476,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>106</v>
@@ -17407,7 +17488,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G22" s="26">
         <v>40</v>
@@ -17420,13 +17501,13 @@
         <v>5</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="16.5" customHeight="1">
@@ -17446,7 +17527,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G23" s="26">
         <v>40</v>
@@ -17462,10 +17543,10 @@
         <v>26</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16.5" customHeight="1">
@@ -17485,7 +17566,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G24" s="26">
         <v>40</v>
@@ -17498,13 +17579,13 @@
         <v>19</v>
       </c>
       <c r="J24" s="21" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" customHeight="1">
@@ -17512,38 +17593,36 @@
         <v>6</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>484</v>
+        <v>56</v>
+      </c>
+      <c r="D25" s="26">
+        <v>15</v>
       </c>
       <c r="E25" s="20">
         <v>3</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="G25" s="26">
         <v>40</v>
       </c>
       <c r="H25" s="26">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="I25" s="26">
         <f t="shared" si="0"/>
-        <v>6.5</v>
-      </c>
-      <c r="J25" s="21" t="s">
-        <v>46</v>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="J25" s="21"/>
       <c r="K25" s="21" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16.5" customHeight="1">
@@ -17551,36 +17630,36 @@
         <v>7</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D26" s="26">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E26" s="20">
         <v>3</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="G26" s="26">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H26" s="26">
         <v>70</v>
       </c>
       <c r="I26" s="26">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="16.5" customHeight="1">
@@ -17588,143 +17667,107 @@
         <v>8</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>490</v>
+        <v>58</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="26">
-        <v>5</v>
+        <v>106</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>495</v>
       </c>
       <c r="E27" s="20">
         <v>3</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="G27" s="26">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H27" s="26">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I27" s="26">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="J27" s="21"/>
+        <v>5</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>454</v>
+      </c>
       <c r="K27" s="21" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="20">
-        <v>9</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>106</v>
-      </c>
+      <c r="A28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="20"/>
       <c r="D28" s="26" t="s">
-        <v>493</v>
+        <v>343</v>
       </c>
       <c r="E28" s="20">
-        <v>3</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="G28" s="26">
-        <v>40</v>
-      </c>
-      <c r="H28" s="26">
-        <v>60</v>
-      </c>
+        <f>SUM(E20:E27)</f>
+        <v>27</v>
+      </c>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
       <c r="I28" s="26">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="J28" s="21" t="s">
-        <v>450</v>
-      </c>
-      <c r="K28" s="21" t="s">
-        <v>494</v>
-      </c>
-      <c r="L28" s="21" t="s">
-        <v>495</v>
-      </c>
+        <f>ROUND(SUM(I20:I27),0)</f>
+        <v>70</v>
+      </c>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
-      <c r="A29" s="20"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="E29" s="20">
-        <f>SUM(E20:E28)</f>
-        <v>30</v>
-      </c>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26">
-        <f>ROUND(SUM(I20:I28),0)</f>
-        <v>76</v>
-      </c>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
+      <c r="A29" s="3" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="3" t="s">
-        <v>496</v>
+      <c r="A30" s="31" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="16.5" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="16.5" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="16.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="16.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="16.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" ht="16.5" customHeight="1">
-      <c r="A37" s="31" t="s">
-        <v>503</v>
-      </c>
-    </row>
+        <v>505</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="16.5" customHeight="1"/>
     <row r="38" spans="1:1" ht="16.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A20:N28">
+  <conditionalFormatting sqref="A20:N27">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>$E20=0</formula>
     </cfRule>
@@ -17736,7 +17779,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
@@ -17753,25 +17796,25 @@
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>195</v>
@@ -17839,56 +17882,56 @@
     </row>
     <row r="11" spans="1:14" ht="16.5" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1">
       <c r="A14" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>140</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E14" s="35" t="s">
         <v>195</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K14" s="35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L14" s="35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M14" s="35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N14" s="35" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1">
@@ -17909,7 +17952,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G15" s="38">
         <v>35</v>
@@ -17918,17 +17961,17 @@
         <v>240</v>
       </c>
       <c r="I15" s="38">
-        <f t="shared" ref="I15:I23" si="0">IF(E15=0,0,ROUND(E15*(G15+H15)/60,1))</f>
+        <f t="shared" ref="I15:I22" si="0">IF(E15=0,0,ROUND(E15*(G15+H15)/60,1))</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L15" s="39" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1">
@@ -17949,7 +17992,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G16" s="38">
         <v>35</v>
@@ -17962,13 +18005,13 @@
         <v>7.2</v>
       </c>
       <c r="J16" s="39" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L16" s="39" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1">
@@ -17988,7 +18031,7 @@
         <v>4</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G17" s="26">
         <v>45</v>
@@ -18004,10 +18047,10 @@
         <v>68</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="16.5" customHeight="1">
@@ -18027,7 +18070,7 @@
         <v>3</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G18" s="26">
         <v>40</v>
@@ -18040,13 +18083,13 @@
         <v>9.5</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="16.5" customHeight="1">
@@ -18054,7 +18097,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>68</v>
@@ -18066,7 +18109,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G19" s="26">
         <v>80</v>
@@ -18080,10 +18123,10 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="16.5" customHeight="1">
@@ -18091,7 +18134,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>89</v>
@@ -18103,7 +18146,7 @@
         <v>4</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G20" s="26">
         <v>40</v>
@@ -18117,10 +18160,10 @@
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="21" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" customHeight="1">
@@ -18141,7 +18184,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G21" s="26">
         <v>45</v>
@@ -18157,10 +18200,10 @@
         <v>76</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="16.5" customHeight="1">
@@ -18168,10 +18211,10 @@
         <v>8</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D22" s="26">
         <v>8</v>
@@ -18180,7 +18223,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G22" s="26">
         <v>40</v>
@@ -18194,68 +18237,32 @@
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A23" s="20">
-        <v>9</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="26">
-        <v>15</v>
-      </c>
-      <c r="E23" s="20">
-        <v>3</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="G23" s="26">
-        <v>80</v>
-      </c>
-      <c r="H23" s="26">
-        <v>75</v>
-      </c>
-      <c r="I23" s="26">
-        <f t="shared" si="0"/>
-        <v>7.8</v>
-      </c>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21" t="s">
-        <v>528</v>
-      </c>
-      <c r="L23" s="21" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1">
-      <c r="D24" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E24" s="27">
-        <f>SUM(E15:E23)</f>
-        <v>27</v>
-      </c>
-      <c r="I24">
-        <f>ROUND(SUM(I15:I23),0)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="83"/>
+      <c r="D23" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E23" s="27">
+        <f>SUM(E15:E22)</f>
+        <v>24</v>
+      </c>
+      <c r="I23">
+        <f>ROUND(SUM(I15:I22),0)</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1"/>
+    <row r="33" spans="2:2">
+      <c r="B33" s="83"/>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A15:N23">
+  <conditionalFormatting sqref="A15:N22">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>$E15=0</formula>
     </cfRule>

--- a/운동프로그램_8일주기_v19.xlsx
+++ b/운동프로그램_8일주기_v19.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_56CBE09B577CB57806506320C7833877887CCA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="883" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시작중량_설정" sheetId="1" r:id="rId1"/>
@@ -7517,7 +7517,7 @@
         <v>5</v>
       </c>
       <c r="F71">
-        <f t="shared" ref="F71:F102" ca="1" si="4">IF(ISNUMBER(E71),$D71*E71,0)</f>
+        <f t="shared" ref="F71:F72" ca="1" si="4">IF(ISNUMBER(E71),$D71*E71,0)</f>
         <v>2.5</v>
       </c>
       <c r="G71" t="s">
